--- a/data/global/2026-03-week03/titles.xlsx
+++ b/data/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>נטע ברזילי – גם זה יגיע</v>
       </c>
       <c r="B2" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-15</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%92%d7%9d-%d7%96%d7%94-%d7%99%d7%92%d7%99%d7%a2/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-15</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 days ago</v>
+        <v>את נטע ברזילי מעולם לא שמענו כל כך נרגשת וכאובה. “גם זה יגיע” הוא שיר החמצה שנשען על פרדוקס כואב מאוד: יש רצון לאהוב, יש אפילו הבטחה לאהוב, אבל אין יכולת ממשית לממש את האהבה בהווה. זה מה שהופך אותו</v>
       </c>
       <c r="G2" t="str">
-        <v>4:09</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Mei Semones</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>נטע ברזילי – גם זה יגיע</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B3" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-15</v>
@@ -492,10 +492,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:08</v>
+        <v>4:09</v>
       </c>
       <c r="H3" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-15</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:57</v>
+        <v>2:08</v>
       </c>
       <c r="H4" t="str">
-        <v>Natalie Jane</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-15</v>
@@ -568,10 +568,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:13</v>
+        <v>2:57</v>
       </c>
       <c r="H5" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B6" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-15</v>
@@ -606,10 +606,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:12</v>
+        <v>3:13</v>
       </c>
       <c r="H6" t="str">
-        <v>David Gilmour</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B7" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-15</v>
@@ -644,10 +644,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:57</v>
+        <v>4:12</v>
       </c>
       <c r="H7" t="str">
-        <v>Far Caspian</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B8" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-15</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:34</v>
+        <v>3:57</v>
       </c>
       <c r="H8" t="str">
-        <v>Celine Dion</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B9" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-15</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:48</v>
+        <v>3:34</v>
       </c>
       <c r="H9" t="str">
-        <v>Harry Styles</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B10" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-15</v>
@@ -758,10 +758,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:58</v>
+        <v>3:48</v>
       </c>
       <c r="H10" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-15</v>
@@ -796,10 +796,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:33</v>
+        <v>4:58</v>
       </c>
       <c r="H11" t="str">
-        <v>Ellise</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-15</v>
@@ -834,10 +834,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>5:01</v>
+        <v>2:33</v>
       </c>
       <c r="H12" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Ellise</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B13" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-15</v>
@@ -872,10 +872,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:56</v>
+        <v>5:01</v>
       </c>
       <c r="H13" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B14" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-15</v>
@@ -910,10 +910,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:54</v>
+        <v>4:56</v>
       </c>
       <c r="H14" t="str">
-        <v>Bebe Rexha</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B15" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-15</v>
@@ -948,10 +948,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:46</v>
+        <v>2:54</v>
       </c>
       <c r="H15" t="str">
-        <v>NathanEvanss</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B16" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-15</v>
@@ -986,10 +986,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:56</v>
+        <v>2:46</v>
       </c>
       <c r="H16" t="str">
-        <v>R3HAB</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-15</v>
@@ -1024,10 +1024,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:21</v>
+        <v>2:56</v>
       </c>
       <c r="H17" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>R3HAB</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B18" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-15</v>
@@ -1062,10 +1062,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:16</v>
+        <v>3:21</v>
       </c>
       <c r="H18" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B19" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-15</v>
@@ -1100,10 +1100,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:41</v>
+        <v>3:16</v>
       </c>
       <c r="H19" t="str">
-        <v>Johnny Orlando</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B20" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-15</v>
@@ -1138,10 +1138,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:29</v>
+        <v>2:41</v>
       </c>
       <c r="H20" t="str">
-        <v>Russell Dickerson</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B21" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-15</v>
@@ -1176,10 +1176,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:43</v>
+        <v>2:29</v>
       </c>
       <c r="H21" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B22" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-15</v>
@@ -1214,10 +1214,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:46</v>
+        <v>2:43</v>
       </c>
       <c r="H22" t="str">
-        <v>Matt Hansen</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B23" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-15</v>
@@ -1252,10 +1252,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:01</v>
+        <v>3:46</v>
       </c>
       <c r="H23" t="str">
-        <v>Mike Posner</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-15</v>
@@ -1290,10 +1290,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:23</v>
+        <v>4:01</v>
       </c>
       <c r="H24" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B25" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-15</v>
@@ -1328,10 +1328,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:39</v>
+        <v>3:23</v>
       </c>
       <c r="H25" t="str">
-        <v>almost monday</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B26" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-15</v>
@@ -1366,10 +1366,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:04</v>
+        <v>3:39</v>
       </c>
       <c r="H26" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>almost monday</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-15</v>
@@ -1404,10 +1404,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:25</v>
+        <v>3:04</v>
       </c>
       <c r="H27" t="str">
-        <v>vaultboy</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-15</v>
@@ -1442,10 +1442,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:49</v>
+        <v>3:25</v>
       </c>
       <c r="H28" t="str">
-        <v>The Warning</v>
+        <v>vaultboy</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B29" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-15</v>
@@ -1480,10 +1480,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:14</v>
+        <v>3:49</v>
       </c>
       <c r="H29" t="str">
-        <v>aron!</v>
+        <v>The Warning</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B30" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-15</v>
@@ -1518,10 +1518,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:43</v>
+        <v>2:14</v>
       </c>
       <c r="H30" t="str">
-        <v>Bazzi</v>
+        <v>aron!</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-15</v>
@@ -1556,10 +1556,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H31" t="str">
-        <v>Sting</v>
+        <v>Bazzi</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B32" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-15</v>
@@ -1594,10 +1594,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:44</v>
+        <v>4:43</v>
       </c>
       <c r="H32" t="str">
-        <v>Dean Lewis</v>
+        <v>Sting</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-15</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:37</v>
+        <v>2:44</v>
       </c>
       <c r="H33" t="str">
-        <v>Jessie Ware</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-15</v>
@@ -1670,10 +1670,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:52</v>
+        <v>4:37</v>
       </c>
       <c r="H34" t="str">
-        <v>Cannons</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B35" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-15</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:13</v>
+        <v>4:52</v>
       </c>
       <c r="H35" t="str">
-        <v>Kim Petras</v>
+        <v>Cannons</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B36" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-15</v>
@@ -1746,10 +1746,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:19</v>
+        <v>2:13</v>
       </c>
       <c r="H36" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B37" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-15</v>
@@ -1784,10 +1784,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:31</v>
+        <v>3:19</v>
       </c>
       <c r="H37" t="str">
-        <v>Kiana Ledé</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B38" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-15</v>
@@ -1822,10 +1822,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:43</v>
+        <v>2:31</v>
       </c>
       <c r="H38" t="str">
-        <v>Ringo Starr</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-15</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:10</v>
+        <v>2:43</v>
       </c>
       <c r="H39" t="str">
-        <v>Maya Hawke</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B40" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-15</v>
@@ -1898,10 +1898,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:55</v>
+        <v>3:10</v>
       </c>
       <c r="H40" t="str">
-        <v>Armin van Buuren</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B41" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-15</v>
@@ -1936,10 +1936,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:52</v>
+        <v>3:55</v>
       </c>
       <c r="H41" t="str">
-        <v>Demi Lovato</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B42" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-15</v>
@@ -1974,10 +1974,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:53</v>
+        <v>3:52</v>
       </c>
       <c r="H42" t="str">
-        <v>Peter Gabriel</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B43" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-15</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:30</v>
+        <v>2:53</v>
       </c>
       <c r="H43" t="str">
-        <v>Jessie J</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B44" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-15</v>
@@ -2050,10 +2050,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G44" t="str">
-        <v>5:18</v>
+        <v>4:30</v>
       </c>
       <c r="H44" t="str">
-        <v>Harry Styles</v>
+        <v>Jessie J</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B45" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-15</v>
@@ -2088,10 +2088,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G45" t="str">
-        <v>7:20</v>
+        <v>5:18</v>
       </c>
       <c r="H45" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B46" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-15</v>
@@ -2126,10 +2126,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:01</v>
+        <v>7:20</v>
       </c>
       <c r="H46" t="str">
-        <v>BRITs</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B47" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-15</v>
@@ -2164,10 +2164,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:31</v>
+        <v>3:01</v>
       </c>
       <c r="H47" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B48" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-15</v>
@@ -2202,10 +2202,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:00</v>
+        <v>3:31</v>
       </c>
       <c r="H48" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B49" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-15</v>
@@ -2240,10 +2240,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:11</v>
+        <v>3:00</v>
       </c>
       <c r="H49" t="str">
-        <v>The Kiffness</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B50" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-15</v>
@@ -2278,10 +2278,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:32</v>
+        <v>3:11</v>
       </c>
       <c r="H50" t="str">
-        <v>Lauv</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B51" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-15</v>
@@ -2316,10 +2316,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
-        <v>5:03</v>
+        <v>3:32</v>
       </c>
       <c r="H51" t="str">
-        <v>RAYE</v>
+        <v>Lauv</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B52" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-15</v>
@@ -2354,10 +2354,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:50</v>
+        <v>5:03</v>
       </c>
       <c r="H52" t="str">
-        <v>Armik</v>
+        <v>RAYE</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B53" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-15</v>
@@ -2392,10 +2392,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:53</v>
+        <v>4:50</v>
       </c>
       <c r="H53" t="str">
-        <v>Scorpions</v>
+        <v>Armik</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-15</v>
@@ -2430,10 +2430,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:04</v>
+        <v>4:53</v>
       </c>
       <c r="H54" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Scorpions</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-15</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:32</v>
+        <v>3:04</v>
       </c>
       <c r="H55" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-15</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:47</v>
+        <v>4:32</v>
       </c>
       <c r="H56" t="str">
-        <v>Girl Tones</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-15</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:40</v>
+        <v>3:47</v>
       </c>
       <c r="H57" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-15</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:05</v>
+        <v>3:40</v>
       </c>
       <c r="H58" t="str">
-        <v>HAUSER</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-15</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:59</v>
+        <v>4:05</v>
       </c>
       <c r="H59" t="str">
-        <v>Queen Official</v>
+        <v>HAUSER</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-15</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:55</v>
+        <v>2:59</v>
       </c>
       <c r="H60" t="str">
-        <v>Tenille Townes</v>
+        <v>Queen Official</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-15</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>5:12</v>
+        <v>3:55</v>
       </c>
       <c r="H61" t="str">
-        <v>Self Esteem</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-15</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:47</v>
+        <v>5:12</v>
       </c>
       <c r="H62" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-15</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:18</v>
+        <v>3:47</v>
       </c>
       <c r="H63" t="str">
-        <v>Em Beihold</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-15</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:50</v>
+        <v>3:18</v>
       </c>
       <c r="H64" t="str">
-        <v>Michael Bublé</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-15</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:24</v>
+        <v>3:50</v>
       </c>
       <c r="H65" t="str">
-        <v>MyKey</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-15</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:36</v>
+        <v>3:24</v>
       </c>
       <c r="H66" t="str">
-        <v>Max McNown</v>
+        <v>MyKey</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-15</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:34</v>
+        <v>2:36</v>
       </c>
       <c r="H67" t="str">
-        <v>Megan Moroney</v>
+        <v>Max McNown</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-15</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:03</v>
+        <v>3:34</v>
       </c>
       <c r="H68" t="str">
-        <v>ERNEST</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-15</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:31</v>
+        <v>4:03</v>
       </c>
       <c r="H69" t="str">
-        <v>Bruno Mars</v>
+        <v>ERNEST</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-15</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:22</v>
+        <v>3:31</v>
       </c>
       <c r="H70" t="str">
-        <v>BLACKPINK</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-15</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>5:49</v>
+        <v>3:22</v>
       </c>
       <c r="H71" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-15</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:47</v>
+        <v>5:49</v>
       </c>
       <c r="H72" t="str">
-        <v>Nessa Barrett</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-15</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:20</v>
+        <v>3:47</v>
       </c>
       <c r="H73" t="str">
-        <v>Towa Bird</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-15</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:18</v>
+        <v>2:20</v>
       </c>
       <c r="H74" t="str">
-        <v>Ty Myers</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-15</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:39</v>
+        <v>4:18</v>
       </c>
       <c r="H75" t="str">
-        <v>kenzie</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-15</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:52</v>
+        <v>2:39</v>
       </c>
       <c r="H76" t="str">
-        <v>Leanna Crawford</v>
+        <v>kenzie</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-15</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:01</v>
+        <v>3:52</v>
       </c>
       <c r="H77" t="str">
-        <v>Bryan Adams</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-15</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:54</v>
+        <v>4:01</v>
       </c>
       <c r="H78" t="str">
-        <v>CHESCA</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-15</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:03</v>
+        <v>2:54</v>
       </c>
       <c r="H79" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CHESCA</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-15</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:50</v>
+        <v>4:03</v>
       </c>
       <c r="H80" t="str">
-        <v>earMUSIC</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-15</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:06</v>
+        <v>4:50</v>
       </c>
       <c r="H81" t="str">
-        <v>Y2K</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-15</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:43</v>
+        <v>3:06</v>
       </c>
       <c r="H82" t="str">
-        <v>Lainey Wilson</v>
+        <v>Y2K</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-15</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>6:21</v>
+        <v>2:43</v>
       </c>
       <c r="H83" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-15</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:46</v>
+        <v>6:21</v>
       </c>
       <c r="H84" t="str">
-        <v>Bryan Ferry</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-15</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H85" t="str">
-        <v>Saint Harison</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-15</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:04</v>
+        <v>2:42</v>
       </c>
       <c r="H86" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-15</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:59</v>
+        <v>3:04</v>
       </c>
       <c r="H87" t="str">
-        <v>Catie Turner</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-15</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:22</v>
+        <v>2:59</v>
       </c>
       <c r="H88" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-15</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:53</v>
+        <v>2:22</v>
       </c>
       <c r="H89" t="str">
-        <v>Roxette</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-15</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:28</v>
+        <v>3:53</v>
       </c>
       <c r="H90" t="str">
-        <v>Marcin</v>
+        <v>Roxette</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-15</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:47</v>
+        <v>2:28</v>
       </c>
       <c r="H91" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Marcin</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-15</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:40</v>
+        <v>2:47</v>
       </c>
       <c r="H92" t="str">
-        <v>Laufey</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-15</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:49</v>
+        <v>3:40</v>
       </c>
       <c r="H93" t="str">
-        <v>Ava Max</v>
+        <v>Laufey</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-15</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>4:49</v>
+        <v>2:49</v>
       </c>
       <c r="H94" t="str">
-        <v>U2</v>
+        <v>Ava Max</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-15</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:35</v>
+        <v>4:49</v>
       </c>
       <c r="H95" t="str">
-        <v>Taylor Swift</v>
+        <v>U2</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-15</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:59</v>
+        <v>3:35</v>
       </c>
       <c r="H96" t="str">
-        <v>Kiana Ledé</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-15</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:38</v>
+        <v>2:59</v>
       </c>
       <c r="H97" t="str">
-        <v>Jessie Ware</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-15</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:46</v>
+        <v>4:38</v>
       </c>
       <c r="H98" t="str">
-        <v>Madison Beer</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-15</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:08</v>
+        <v>3:46</v>
       </c>
       <c r="H99" t="str">
-        <v>Sean Stemaly</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-15</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:32</v>
+        <v>3:08</v>
       </c>
       <c r="H100" t="str">
-        <v>earMUSIC</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-15</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:39</v>
+        <v>5:32</v>
       </c>
       <c r="H101" t="str">
-        <v>georgemichael</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Porch Light</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-15</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>The Great Divide</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>4:22</v>
+        <v>4:39</v>
       </c>
       <c r="H102" t="str">
-        <v>Noah Kahan</v>
+        <v>georgemichael</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Porch Light - Noah Kahan</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Dry Spell</v>
+        <v>Porch Light</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
+        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-15</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Middle of Nowhere</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G103" t="str">
-        <v>3:17</v>
+        <v>4:22</v>
       </c>
       <c r="H103" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
+        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
       </c>
       <c r="L103" t="str">
-        <v>Dry Spell - Kacey Musgraves</v>
+        <v>Porch Light - Noah Kahan</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>The Visitor</v>
+        <v>Dry Spell</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
+        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-15</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Visitor - Single</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G104" t="str">
-        <v>3:48</v>
+        <v>3:17</v>
       </c>
       <c r="H104" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
+        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
       </c>
       <c r="L104" t="str">
-        <v>The Visitor - SIENNA SPIRO</v>
+        <v>Dry Spell - Kacey Musgraves</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>I Ain't No Cowboy</v>
+        <v>The Visitor</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
+        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-15</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Way I Am</v>
+        <v>The Visitor - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:13</v>
+        <v>3:48</v>
       </c>
       <c r="H105" t="str">
-        <v>Luke Combs</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
+        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
       </c>
       <c r="L105" t="str">
-        <v>I Ain't No Cowboy - Luke Combs</v>
+        <v>The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Can't Sit Still</v>
+        <v>I Ain't No Cowboy</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
+        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-15</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Can't Sit Still - Single</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G106" t="str">
-        <v>3:35</v>
+        <v>3:13</v>
       </c>
       <c r="H106" t="str">
-        <v>Lainey Wilson</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
+        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
       </c>
       <c r="L106" t="str">
-        <v>Can't Sit Still - Lainey Wilson</v>
+        <v>I Ain't No Cowboy - Luke Combs</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías)</v>
+        <v>Can't Sit Still</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
+        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-15</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
+        <v>Can't Sit Still - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:43</v>
+        <v>3:35</v>
       </c>
       <c r="H107" t="str">
-        <v>beabadoobee</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
+        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
       </c>
       <c r="L107" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
+        <v>Can't Sit Still - Lainey Wilson</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Blow My Mind</v>
+        <v>All I Did Was Dream of You (feat. The Marías)</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
+        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-15</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Sexistential</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:57</v>
+        <v>3:43</v>
       </c>
       <c r="H108" t="str">
-        <v>Robyn</v>
+        <v>beabadoobee</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
+        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
       </c>
       <c r="L108" t="str">
-        <v>Blow My Mind - Robyn</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SATA</v>
+        <v>Blow My Mind</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/sata/1874015489</v>
+        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-15</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>Sexistential</v>
       </c>
       <c r="G109" t="str">
-        <v>3:02</v>
+        <v>2:57</v>
       </c>
       <c r="H109" t="str">
-        <v>John Summit</v>
+        <v>Robyn</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/sata/1874015470</v>
+        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
       </c>
       <c r="L109" t="str">
-        <v>SATA - John Summit</v>
+        <v>Blow My Mind - Robyn</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Una Aventura</v>
+        <v>SATA</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
+        <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-15</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Una Aventura - Single</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G110" t="str">
-        <v>3:00</v>
+        <v>3:02</v>
       </c>
       <c r="H110" t="str">
-        <v>Ozuna</v>
+        <v>John Summit</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
+        <v>https://music.apple.com/us/album/sata/1874015470</v>
       </c>
       <c r="L110" t="str">
-        <v>Una Aventura - Ozuna</v>
+        <v>SATA - John Summit</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>Una Aventura</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-15</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Una Aventura - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:44</v>
+        <v>3:00</v>
       </c>
       <c r="H111" t="str">
-        <v>Charlie Puth</v>
+        <v>Ozuna</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
       </c>
       <c r="L111" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>Una Aventura - Ozuna</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>dirty wedding dress</v>
+        <v>Home (feat. Hikaru Utada)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-15</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G112" t="str">
-        <v>4:49</v>
+        <v>3:44</v>
       </c>
       <c r="H112" t="str">
-        <v>Bleachers</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
       </c>
       <c r="L112" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>dirty wedding dress</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-15</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Age of the Ram</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G113" t="str">
-        <v>3:07</v>
+        <v>4:49</v>
       </c>
       <c r="H113" t="str">
-        <v>Charley Crockett</v>
+        <v>Bleachers</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
       </c>
       <c r="L113" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>dirty wedding dress - Bleachers</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-15</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G114" t="str">
-        <v>3:13</v>
+        <v>3:07</v>
       </c>
       <c r="H114" t="str">
-        <v>Grupo Frontera</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L114" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Trade Places</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-15</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Monica</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:02</v>
+        <v>3:13</v>
       </c>
       <c r="H115" t="str">
-        <v>Jack Harlow</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L115" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Motion Party</v>
+        <v>Trade Places</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-15</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Motion Party - Single</v>
+        <v>Monica</v>
       </c>
       <c r="G116" t="str">
-        <v>1:35</v>
+        <v>3:02</v>
       </c>
       <c r="H116" t="str">
-        <v>Bossman Dlow</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L116" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Woman</v>
+        <v>Motion Party</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-15</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Woman - Single</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:46</v>
+        <v>1:35</v>
       </c>
       <c r="H117" t="str">
-        <v>Kane Brown</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L117" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Sunburn</v>
+        <v>Woman</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-15</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Sunburn - Single</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:05</v>
+        <v>2:46</v>
       </c>
       <c r="H118" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L118" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Que Te Costó</v>
+        <v>Sunburn</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-15</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Metamorfosis</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H119" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L119" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>oooshxt!</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-15</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>oooshxt! - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G120" t="str">
-        <v>2:15</v>
+        <v>2:54</v>
       </c>
       <c r="H120" t="str">
-        <v>Samara Cyn</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L120" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-15</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:26</v>
+        <v>2:15</v>
       </c>
       <c r="H121" t="str">
-        <v>Holly Humberstone</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L121" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Star</v>
+        <v>Cruel World</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-15</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Star - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G122" t="str">
-        <v>3:25</v>
+        <v>3:26</v>
       </c>
       <c r="H122" t="str">
-        <v>Iceage</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L122" t="str">
-        <v>Star - Iceage</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Get Go</v>
+        <v>Star</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-15</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Star - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:22</v>
+        <v>3:25</v>
       </c>
       <c r="H123" t="str">
-        <v>Arlo Parks</v>
+        <v>Iceage</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L123" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>ThunderWave</v>
+        <v>Get Go</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-15</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Distracted</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G124" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H124" t="str">
-        <v>Thundercat</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L124" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Club Song</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-15</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Club Song - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G125" t="str">
-        <v>2:27</v>
+        <v>3:14</v>
       </c>
       <c r="H125" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>Thundercat</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L125" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Better Man</v>
+        <v>Club Song</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-15</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Better Man - Single</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:53</v>
+        <v>2:27</v>
       </c>
       <c r="H126" t="str">
-        <v>jxdn</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L126" t="str">
-        <v>Better Man - jxdn</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>sabotage</v>
+        <v>Better Man</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-15</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>sabotage - Single</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:58</v>
+        <v>2:53</v>
       </c>
       <c r="H127" t="str">
-        <v>Natalie Jane</v>
+        <v>jxdn</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L127" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>sabotage</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-15</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H128" t="str">
-        <v>WHATMORE</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L128" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Naked</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-15</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Naked - Single</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:39</v>
+        <v>2:56</v>
       </c>
       <c r="H129" t="str">
-        <v>Kenya Grace</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L129" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Catharina</v>
+        <v>Naked</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-15</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Catharina - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:27</v>
+        <v>3:39</v>
       </c>
       <c r="H130" t="str">
-        <v>Martin Garrix</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L130" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>Catharina</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-15</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:00</v>
+        <v>3:27</v>
       </c>
       <c r="H131" t="str">
-        <v>Chase &amp; Status</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L131" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-15</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:33</v>
+        <v>3:00</v>
       </c>
       <c r="H132" t="str">
-        <v>James Blake</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L132" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>595</v>
+        <v>Trying Times</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-15</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Trying Times</v>
       </c>
       <c r="G133" t="str">
-        <v>2:29</v>
+        <v>4:33</v>
       </c>
       <c r="H133" t="str">
-        <v>Violet Grohl</v>
+        <v>James Blake</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L133" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>595</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-15</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Soft 2</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G134" t="str">
-        <v>3:50</v>
+        <v>2:29</v>
       </c>
       <c r="H134" t="str">
-        <v>LANY</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L134" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>CALL ME</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-15</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>CALL ME - Single</v>
+        <v>Soft 2</v>
       </c>
       <c r="G135" t="str">
-        <v>2:10</v>
+        <v>3:50</v>
       </c>
       <c r="H135" t="str">
-        <v>ALTÉGO</v>
+        <v>LANY</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L135" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Mi Amor</v>
+        <v>CALL ME</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-15</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Free (Deluxe)</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:00</v>
+        <v>2:10</v>
       </c>
       <c r="H136" t="str">
-        <v>Nasty C</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L136" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>BOBA</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-15</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>BOBA - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G137" t="str">
-        <v>3:00</v>
+        <v>2:00</v>
       </c>
       <c r="H137" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Nasty C</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L137" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Video Shoot</v>
+        <v>BOBA</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-15</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Skeletor</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:38</v>
+        <v>3:00</v>
       </c>
       <c r="H138" t="str">
-        <v>Chief Keef</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L138" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-15</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G139" t="str">
-        <v>2:06</v>
+        <v>2:38</v>
       </c>
       <c r="H139" t="str">
-        <v>Shenseea</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L139" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Just Believe</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-15</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Just Believe - Single</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:41</v>
+        <v>2:06</v>
       </c>
       <c r="H140" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Shenseea</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L140" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Knife In The Heart</v>
+        <v>Just Believe</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-15</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>The Afterparty</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:57</v>
+        <v>2:41</v>
       </c>
       <c r="H141" t="str">
-        <v>Lykke Li</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L141" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>The Way We Touch</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-15</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G142" t="str">
-        <v>3:09</v>
+        <v>2:57</v>
       </c>
       <c r="H142" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L142" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>DANGEROUS</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-15</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>4:06</v>
+        <v>3:09</v>
       </c>
       <c r="H143" t="str">
-        <v>Magnolia Park</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L143" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>When I Wake Up</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-15</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Dear God</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G144" t="str">
-        <v>3:33</v>
+        <v>4:06</v>
       </c>
       <c r="H144" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L144" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Breathe</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-15</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Breathe - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G145" t="str">
-        <v>2:56</v>
+        <v>3:33</v>
       </c>
       <c r="H145" t="str">
-        <v>Malcolm Todd</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L145" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Minty</v>
+        <v>Breathe</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-15</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>1:47</v>
+        <v>2:56</v>
       </c>
       <c r="H146" t="str">
-        <v>MIKE</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L146" t="str">
-        <v>Minty - MIKE</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Earth</v>
+        <v>Minty</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-15</v>
@@ -5964,33 +5964,33 @@
         <v>POMPEII // UTILITY</v>
       </c>
       <c r="G147" t="str">
-        <v>1:37</v>
+        <v>1:47</v>
       </c>
       <c r="H147" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>MIKE</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L147" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drink The Water</v>
+        <v>Earth</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-15</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G148" t="str">
-        <v>3:42</v>
+        <v>1:37</v>
       </c>
       <c r="H148" t="str">
-        <v>Jack Johnson</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L148" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-15</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G149" t="str">
-        <v>4:32</v>
+        <v>3:42</v>
       </c>
       <c r="H149" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L149" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-15</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:32</v>
+        <v>4:32</v>
       </c>
       <c r="H150" t="str">
-        <v>Carly Pearce</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L150" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Muchacho Alegre</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-15</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:08</v>
+        <v>3:32</v>
       </c>
       <c r="H151" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L151" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Real Slow</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-15</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Work of Heart</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:22</v>
+        <v>3:08</v>
       </c>
       <c r="H152" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L152" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Mountain Girl</v>
+        <v>Real Slow</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-15</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>As Is</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G153" t="str">
-        <v>2:42</v>
+        <v>3:22</v>
       </c>
       <c r="H153" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L153" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Like a Spark</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-15</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>American Stories</v>
+        <v>As Is</v>
       </c>
       <c r="G154" t="str">
-        <v>3:31</v>
+        <v>2:42</v>
       </c>
       <c r="H154" t="str">
-        <v>Rostam</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L154" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Cheesecake</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-15</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>American Stories</v>
       </c>
       <c r="G155" t="str">
-        <v>3:29</v>
+        <v>3:31</v>
       </c>
       <c r="H155" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Rostam</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L155" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-15</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>KINDA HARD</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G156" t="str">
-        <v>3:04</v>
+        <v>3:29</v>
       </c>
       <c r="H156" t="str">
-        <v>Bilmuri</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L156" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Freakin’ Out</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-15</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G157" t="str">
-        <v>3:37</v>
+        <v>3:04</v>
       </c>
       <c r="H157" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L157" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Name in Vein</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-15</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Name in Vein - Single</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:03</v>
+        <v>3:37</v>
       </c>
       <c r="H158" t="str">
-        <v>VOILÀ</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L158" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-15</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Into Oblivion</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>4:05</v>
+        <v>3:03</v>
       </c>
       <c r="H159" t="str">
-        <v>Lamb of God</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L159" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Undefeated Champion</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-15</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Sweat</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G160" t="str">
-        <v>3:34</v>
+        <v>4:05</v>
       </c>
       <c r="H160" t="str">
-        <v>Melanie C</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L160" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Pull Up</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-15</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Pull Up - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G161" t="str">
-        <v>2:35</v>
+        <v>3:34</v>
       </c>
       <c r="H161" t="str">
-        <v>Collect 200</v>
+        <v>Melanie C</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L161" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Ranjha</v>
+        <v>Pull Up</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-15</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Ranjha - Single</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:04</v>
+        <v>2:35</v>
       </c>
       <c r="H162" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>Collect 200</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L162" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>zombies in love</v>
+        <v>Ranjha</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-15</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>zombies in love - Single</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:53</v>
+        <v>3:04</v>
       </c>
       <c r="H163" t="str">
-        <v>paris jackson</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L163" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Days Of Us</v>
+        <v>zombies in love</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-15</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Full Circle</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>4:39</v>
+        <v>2:53</v>
       </c>
       <c r="H164" t="str">
-        <v>Tom Misch</v>
+        <v>paris jackson</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L164" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Life Of A Man</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-15</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G165" t="str">
-        <v>3:15</v>
+        <v>4:39</v>
       </c>
       <c r="H165" t="str">
-        <v>1Ski OG</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L165" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Ya No</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-15</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Ya No - Single</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:40</v>
+        <v>3:15</v>
       </c>
       <c r="H166" t="str">
-        <v>Marca MP</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L166" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Ya No</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-15</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:48</v>
+        <v>3:40</v>
       </c>
       <c r="H167" t="str">
-        <v>Spacey Jane</v>
+        <v>Marca MP</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L167" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Relieve You</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-15</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Relieve You - Single</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:19</v>
+        <v>3:48</v>
       </c>
       <c r="H168" t="str">
-        <v>4Fargo</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L168" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Safety</v>
+        <v>Relieve You</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-15</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Safety - Single</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:18</v>
+        <v>2:19</v>
       </c>
       <c r="H169" t="str">
-        <v>Lekan</v>
+        <v>4Fargo</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L169" t="str">
-        <v>Safety - Lekan</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Starlet</v>
+        <v>Safety</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-15</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>LK99</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:56</v>
+        <v>3:18</v>
       </c>
       <c r="H170" t="str">
-        <v>Leven Kali</v>
+        <v>Lekan</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L170" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Physical</v>
+        <v>Starlet</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-15</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Physical - Single</v>
+        <v>LK99</v>
       </c>
       <c r="G171" t="str">
-        <v>3:52</v>
+        <v>2:56</v>
       </c>
       <c r="H171" t="str">
-        <v>Jacquees</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L171" t="str">
-        <v>Physical - Jacquees</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Physical</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-15</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:29</v>
+        <v>3:52</v>
       </c>
       <c r="H172" t="str">
-        <v>Casper Sage</v>
+        <v>Jacquees</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L172" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Regalito</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-15</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>TRESCENDER</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:41</v>
+        <v>4:29</v>
       </c>
       <c r="H173" t="str">
-        <v>Piso 21</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L173" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Cruel Streak</v>
+        <v>Regalito</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-15</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>A Pound of Feathers</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G174" t="str">
-        <v>4:09</v>
+        <v>2:41</v>
       </c>
       <c r="H174" t="str">
-        <v>The Black Crowes</v>
+        <v>Piso 21</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L174" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Die Young</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-15</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Little Wide Open</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G175" t="str">
-        <v>3:52</v>
+        <v>4:09</v>
       </c>
       <c r="H175" t="str">
-        <v>Kevin Morby</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L175" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Island Girl</v>
+        <v>Die Young</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-15</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Island Girl - Single</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G176" t="str">
-        <v>3:27</v>
+        <v>3:52</v>
       </c>
       <c r="H176" t="str">
-        <v>Pia Mia</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L176" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Island Girl</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-15</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:20</v>
+        <v>3:27</v>
       </c>
       <c r="H177" t="str">
-        <v>Claudia Valentina</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L177" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-15</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:22</v>
+        <v>2:20</v>
       </c>
       <c r="H178" t="str">
-        <v>Shaggy</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L178" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Tommy’s Song</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-15</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Lovers - Single</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:44</v>
+        <v>3:22</v>
       </c>
       <c r="H179" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Shaggy</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L179" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Rainbows</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-15</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Rainbows - Single</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:25</v>
+        <v>3:44</v>
       </c>
       <c r="H180" t="str">
-        <v>Allison Russell</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L180" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>butterflies</v>
+        <v>Rainbows</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-15</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:48</v>
+        <v>3:25</v>
       </c>
       <c r="H181" t="str">
-        <v>runo plum</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L181" t="str">
-        <v>butterflies - runo plum</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You're Right</v>
+        <v>butterflies</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-15</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>You're Right - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G182" t="str">
-        <v>3:00</v>
+        <v>2:48</v>
       </c>
       <c r="H182" t="str">
-        <v>Emma Harner</v>
+        <v>runo plum</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L182" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Bible Belt</v>
+        <v>You're Right</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-15</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Bible Belt - Single</v>
+        <v>You're Right - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H183" t="str">
-        <v>Baby Bugs</v>
+        <v>Emma Harner</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
       </c>
       <c r="L183" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>You're Right - Emma Harner</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Daze</v>
+        <v>Bible Belt</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-15</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Daze - Single</v>
+        <v>Bible Belt - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:22</v>
+        <v>3:34</v>
       </c>
       <c r="H184" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Baby Bugs</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
       </c>
       <c r="L184" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>Bible Belt - Baby Bugs</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Passionfruit</v>
+        <v>Daze</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-15</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Passionfruit - Single</v>
+        <v>Daze - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:57</v>
+        <v>3:22</v>
       </c>
       <c r="H185" t="str">
-        <v>Anish Kumar</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
       </c>
       <c r="L185" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>Daze - Olympia Vitalis</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Madan</v>
+        <v>Passionfruit</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-15</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Madan - Single</v>
+        <v>Passionfruit - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:56</v>
+        <v>3:57</v>
       </c>
       <c r="H186" t="str">
-        <v>Jonas Blue</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
       </c>
       <c r="L186" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Passionfruit - Anish Kumar</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Bad Bitch</v>
+        <v>Madan</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-15</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Madan - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:28</v>
+        <v>2:56</v>
       </c>
       <c r="H187" t="str">
-        <v>41</v>
+        <v>Jonas Blue</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
       </c>
       <c r="L187" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Madan - Jonas Blue</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Shame</v>
+        <v>Bad Bitch</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-15</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>Bad Bitch - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:36</v>
+        <v>2:28</v>
       </c>
       <c r="H188" t="str">
-        <v>Sunday (1994)</v>
+        <v>41</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
       </c>
       <c r="L188" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>Bad Bitch - 41</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>teach you to love me</v>
+        <v>Shame</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-15</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>teach you to love me - Single</v>
+        <v>Devotion [Deluxe]</v>
       </c>
       <c r="G189" t="str">
-        <v>3:09</v>
+        <v>3:36</v>
       </c>
       <c r="H189" t="str">
-        <v>Hailey Picardi</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
       </c>
       <c r="L189" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>Shame - Sunday (1994)</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>The Fix</v>
+        <v>teach you to love me</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-15</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>The Fix - Single</v>
+        <v>teach you to love me - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H190" t="str">
-        <v>Baby J</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
       </c>
       <c r="L190" t="str">
-        <v>The Fix - Baby J</v>
+        <v>teach you to love me - Hailey Picardi</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Hanging on Hope</v>
+        <v>The Fix</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-15</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>The Fix - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:43</v>
+        <v>2:42</v>
       </c>
       <c r="H191" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Baby J</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
       </c>
       <c r="L191" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>The Fix - Baby J</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>I Know What to Say Now</v>
+        <v>Hanging on Hope</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-15</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Hanging on Hope - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:18</v>
+        <v>3:43</v>
       </c>
       <c r="H192" t="str">
-        <v>Active Child</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
       </c>
       <c r="L192" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Feel Something</v>
+        <v>I Know What to Say Now</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-15</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Feel Something - Single</v>
+        <v>I Know What to Say Now - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:09</v>
+        <v>3:18</v>
       </c>
       <c r="H193" t="str">
-        <v>Baby Queen</v>
+        <v>Active Child</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
       </c>
       <c r="L193" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>I Know What to Say Now - Active Child</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>You Or Me</v>
+        <v>Feel Something</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-15</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Feel Something - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>5:28</v>
+        <v>3:09</v>
       </c>
       <c r="H194" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
       </c>
       <c r="L194" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>Feel Something - Baby Queen</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Mortercheyn</v>
+        <v>You Or Me</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-15</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Coronach</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G195" t="str">
-        <v>4:18</v>
+        <v>5:28</v>
       </c>
       <c r="H195" t="str">
-        <v>Hellripper</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
       </c>
       <c r="L195" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>You Or Me - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Rip The God</v>
+        <v>Mortercheyn</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-15</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Coronach</v>
       </c>
       <c r="G196" t="str">
-        <v>5:20</v>
+        <v>4:18</v>
       </c>
       <c r="H196" t="str">
-        <v>Melvins</v>
+        <v>Hellripper</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
       </c>
       <c r="L196" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Mortercheyn - Hellripper</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Who We Are</v>
+        <v>Rip The God</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-15</v>
@@ -7861,68 +7861,106 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Who We Are - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G197" t="str">
-        <v>2:10</v>
+        <v>5:20</v>
       </c>
       <c r="H197" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Melvins</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
       </c>
       <c r="L197" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
+        <v>Rip The God - Melvins</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
+        <v>Who We Are</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>Who We Are - Single</v>
+      </c>
+      <c r="G198" t="str">
+        <v>2:10</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Kaleena Zanders</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+      </c>
+      <c r="L198" t="str">
+        <v>Who We Are - Kaleena Zanders</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
         <v>Reels in 360</v>
       </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
-      <c r="D198" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
+      <c r="D199" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
         <v>Dying Is The Internet</v>
       </c>
-      <c r="G198" t="str">
+      <c r="G199" t="str">
         <v>4:37</v>
       </c>
-      <c r="H198" t="str">
+      <c r="H199" t="str">
         <v>Simo Cell</v>
       </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
         <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
-      <c r="K198" t="str">
+      <c r="K199" t="str">
         <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
-      <c r="L198" t="str">
+      <c r="L199" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week03/titles.xlsx
+++ b/data/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נטע ברזילי – גם זה יגיע</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-15</v>
+        <v>4 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%92%d7%9d-%d7%96%d7%94-%d7%99%d7%92%d7%99%d7%a2/</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-15</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>את נטע ברזילי מעולם לא שמענו כל כך נרגשת וכאובה. “גם זה יגיע” הוא שיר החמצה שנשען על פרדוקס כואב מאוד: יש רצון לאהוב, יש אפילו הבטחה לאהוב, אבל אין יכולת ממשית לממש את האהבה בהווה. זה מה שהופך אותו</v>
+        <v>4 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>4:09</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Mei Semones</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נטע ברזילי – גם זה יגיע</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-15</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:09</v>
+        <v>2:08</v>
       </c>
       <c r="H3" t="str">
-        <v>Mei Semones</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-15</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:08</v>
+        <v>2:57</v>
       </c>
       <c r="H4" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B5" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-15</v>
@@ -568,10 +568,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:57</v>
+        <v>3:13</v>
       </c>
       <c r="H5" t="str">
-        <v>Natalie Jane</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B6" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-15</v>
@@ -606,10 +606,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:13</v>
+        <v>4:12</v>
       </c>
       <c r="H6" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B7" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-15</v>
@@ -644,10 +644,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:12</v>
+        <v>3:57</v>
       </c>
       <c r="H7" t="str">
-        <v>David Gilmour</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B8" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-15</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:57</v>
+        <v>3:34</v>
       </c>
       <c r="H8" t="str">
-        <v>Far Caspian</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-15</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:34</v>
+        <v>3:48</v>
       </c>
       <c r="H9" t="str">
-        <v>Celine Dion</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-15</v>
@@ -758,10 +758,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:48</v>
+        <v>4:58</v>
       </c>
       <c r="H10" t="str">
-        <v>Harry Styles</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-15</v>
@@ -796,10 +796,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:58</v>
+        <v>2:33</v>
       </c>
       <c r="H11" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Ellise</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B12" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-15</v>
@@ -834,10 +834,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:33</v>
+        <v>5:01</v>
       </c>
       <c r="H12" t="str">
-        <v>Ellise</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B13" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-15</v>
@@ -872,10 +872,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>5:01</v>
+        <v>4:56</v>
       </c>
       <c r="H13" t="str">
-        <v>The Doobie Brothers</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B14" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-15</v>
@@ -910,10 +910,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:56</v>
+        <v>2:54</v>
       </c>
       <c r="H14" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B15" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-15</v>
@@ -948,10 +948,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:54</v>
+        <v>2:46</v>
       </c>
       <c r="H15" t="str">
-        <v>Bebe Rexha</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-15</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H16" t="str">
-        <v>NathanEvanss</v>
+        <v>R3HAB</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B17" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-15</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:56</v>
+        <v>3:21</v>
       </c>
       <c r="H17" t="str">
-        <v>R3HAB</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B18" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-15</v>
@@ -1062,10 +1062,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:21</v>
+        <v>3:16</v>
       </c>
       <c r="H18" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B19" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-15</v>
@@ -1100,10 +1100,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:16</v>
+        <v>2:41</v>
       </c>
       <c r="H19" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B20" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-15</v>
@@ -1138,10 +1138,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:41</v>
+        <v>2:29</v>
       </c>
       <c r="H20" t="str">
-        <v>Johnny Orlando</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B21" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-15</v>
@@ -1176,10 +1176,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:29</v>
+        <v>2:43</v>
       </c>
       <c r="H21" t="str">
-        <v>Russell Dickerson</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B22" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-15</v>
@@ -1214,10 +1214,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:43</v>
+        <v>3:46</v>
       </c>
       <c r="H22" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-15</v>
@@ -1252,10 +1252,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:46</v>
+        <v>4:01</v>
       </c>
       <c r="H23" t="str">
-        <v>Matt Hansen</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B24" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-15</v>
@@ -1290,10 +1290,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:01</v>
+        <v>3:23</v>
       </c>
       <c r="H24" t="str">
-        <v>Mike Posner</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B25" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-15</v>
@@ -1328,10 +1328,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:23</v>
+        <v>3:39</v>
       </c>
       <c r="H25" t="str">
-        <v>Katelyn Tarver</v>
+        <v>almost monday</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-15</v>
@@ -1366,10 +1366,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H26" t="str">
-        <v>almost monday</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-15</v>
@@ -1404,10 +1404,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:04</v>
+        <v>3:25</v>
       </c>
       <c r="H27" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>vaultboy</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-15</v>
@@ -1442,10 +1442,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:25</v>
+        <v>3:49</v>
       </c>
       <c r="H28" t="str">
-        <v>vaultboy</v>
+        <v>The Warning</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B29" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-15</v>
@@ -1480,10 +1480,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:49</v>
+        <v>2:14</v>
       </c>
       <c r="H29" t="str">
-        <v>The Warning</v>
+        <v>aron!</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-15</v>
@@ -1518,10 +1518,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:14</v>
+        <v>2:43</v>
       </c>
       <c r="H30" t="str">
-        <v>aron!</v>
+        <v>Bazzi</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B31" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-15</v>
@@ -1556,10 +1556,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:43</v>
+        <v>4:43</v>
       </c>
       <c r="H31" t="str">
-        <v>Bazzi</v>
+        <v>Sting</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-15</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>4:43</v>
+        <v>2:44</v>
       </c>
       <c r="H32" t="str">
-        <v>Sting</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-15</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:44</v>
+        <v>4:37</v>
       </c>
       <c r="H33" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B34" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-15</v>
@@ -1670,10 +1670,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:37</v>
+        <v>4:52</v>
       </c>
       <c r="H34" t="str">
-        <v>Jessie Ware</v>
+        <v>Cannons</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B35" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-15</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:52</v>
+        <v>2:13</v>
       </c>
       <c r="H35" t="str">
-        <v>Cannons</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B36" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-15</v>
@@ -1746,10 +1746,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:13</v>
+        <v>3:19</v>
       </c>
       <c r="H36" t="str">
-        <v>Kim Petras</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B37" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-15</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:19</v>
+        <v>2:31</v>
       </c>
       <c r="H37" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-15</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:31</v>
+        <v>2:43</v>
       </c>
       <c r="H38" t="str">
-        <v>Kiana Ledé</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-15</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:43</v>
+        <v>3:10</v>
       </c>
       <c r="H39" t="str">
-        <v>Ringo Starr</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B40" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-15</v>
@@ -1898,10 +1898,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:10</v>
+        <v>3:55</v>
       </c>
       <c r="H40" t="str">
-        <v>Maya Hawke</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B41" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-15</v>
@@ -1936,10 +1936,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:55</v>
+        <v>3:52</v>
       </c>
       <c r="H41" t="str">
-        <v>Armin van Buuren</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B42" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-15</v>
@@ -1974,10 +1974,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:52</v>
+        <v>2:53</v>
       </c>
       <c r="H42" t="str">
-        <v>Demi Lovato</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-15</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:53</v>
+        <v>4:30</v>
       </c>
       <c r="H43" t="str">
-        <v>Peter Gabriel</v>
+        <v>Jessie J</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B44" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-15</v>
@@ -2050,10 +2050,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:30</v>
+        <v>5:18</v>
       </c>
       <c r="H44" t="str">
-        <v>Jessie J</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B45" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-15</v>
@@ -2088,10 +2088,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G45" t="str">
-        <v>5:18</v>
+        <v>7:20</v>
       </c>
       <c r="H45" t="str">
-        <v>Harry Styles</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B46" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-15</v>
@@ -2126,10 +2126,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G46" t="str">
-        <v>7:20</v>
+        <v>3:01</v>
       </c>
       <c r="H46" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B47" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-15</v>
@@ -2164,10 +2164,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:01</v>
+        <v>3:31</v>
       </c>
       <c r="H47" t="str">
-        <v>BRITs</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B48" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-15</v>
@@ -2202,10 +2202,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:31</v>
+        <v>3:00</v>
       </c>
       <c r="H48" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B49" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-15</v>
@@ -2240,10 +2240,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:00</v>
+        <v>3:11</v>
       </c>
       <c r="H49" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B50" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-15</v>
@@ -2278,10 +2278,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:11</v>
+        <v>3:32</v>
       </c>
       <c r="H50" t="str">
-        <v>The Kiffness</v>
+        <v>Lauv</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B51" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-15</v>
@@ -2316,10 +2316,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:32</v>
+        <v>5:03</v>
       </c>
       <c r="H51" t="str">
-        <v>Lauv</v>
+        <v>RAYE</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B52" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-15</v>
@@ -2354,10 +2354,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
-        <v>5:03</v>
+        <v>4:50</v>
       </c>
       <c r="H52" t="str">
-        <v>RAYE</v>
+        <v>Armik</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B53" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-15</v>
@@ -2392,10 +2392,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:50</v>
+        <v>4:53</v>
       </c>
       <c r="H53" t="str">
-        <v>Armik</v>
+        <v>Scorpions</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-15</v>
@@ -2430,10 +2430,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:53</v>
+        <v>3:04</v>
       </c>
       <c r="H54" t="str">
-        <v>Scorpions</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-15</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:04</v>
+        <v>4:32</v>
       </c>
       <c r="H55" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-15</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:32</v>
+        <v>3:47</v>
       </c>
       <c r="H56" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-15</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:47</v>
+        <v>3:40</v>
       </c>
       <c r="H57" t="str">
-        <v>Girl Tones</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-15</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:40</v>
+        <v>4:05</v>
       </c>
       <c r="H58" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>HAUSER</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-15</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:05</v>
+        <v>2:59</v>
       </c>
       <c r="H59" t="str">
-        <v>HAUSER</v>
+        <v>Queen Official</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-15</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:59</v>
+        <v>3:55</v>
       </c>
       <c r="H60" t="str">
-        <v>Queen Official</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-15</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:55</v>
+        <v>5:12</v>
       </c>
       <c r="H61" t="str">
-        <v>Tenille Townes</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-15</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>5:12</v>
+        <v>3:47</v>
       </c>
       <c r="H62" t="str">
-        <v>Self Esteem</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-15</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:47</v>
+        <v>3:18</v>
       </c>
       <c r="H63" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-15</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:18</v>
+        <v>3:50</v>
       </c>
       <c r="H64" t="str">
-        <v>Em Beihold</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-15</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:50</v>
+        <v>3:24</v>
       </c>
       <c r="H65" t="str">
-        <v>Michael Bublé</v>
+        <v>MyKey</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-15</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:24</v>
+        <v>2:36</v>
       </c>
       <c r="H66" t="str">
-        <v>MyKey</v>
+        <v>Max McNown</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-15</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:36</v>
+        <v>3:34</v>
       </c>
       <c r="H67" t="str">
-        <v>Max McNown</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-15</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:34</v>
+        <v>4:03</v>
       </c>
       <c r="H68" t="str">
-        <v>Megan Moroney</v>
+        <v>ERNEST</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-15</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:03</v>
+        <v>3:31</v>
       </c>
       <c r="H69" t="str">
-        <v>ERNEST</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-15</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:31</v>
+        <v>3:22</v>
       </c>
       <c r="H70" t="str">
-        <v>Bruno Mars</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-15</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:22</v>
+        <v>5:49</v>
       </c>
       <c r="H71" t="str">
-        <v>BLACKPINK</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-15</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>5:49</v>
+        <v>3:47</v>
       </c>
       <c r="H72" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-15</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:47</v>
+        <v>2:20</v>
       </c>
       <c r="H73" t="str">
-        <v>Nessa Barrett</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-15</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:20</v>
+        <v>4:18</v>
       </c>
       <c r="H74" t="str">
-        <v>Towa Bird</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-15</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:18</v>
+        <v>2:39</v>
       </c>
       <c r="H75" t="str">
-        <v>Ty Myers</v>
+        <v>kenzie</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-15</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:39</v>
+        <v>3:52</v>
       </c>
       <c r="H76" t="str">
-        <v>kenzie</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-15</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:52</v>
+        <v>4:01</v>
       </c>
       <c r="H77" t="str">
-        <v>Leanna Crawford</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-15</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:01</v>
+        <v>2:54</v>
       </c>
       <c r="H78" t="str">
-        <v>Bryan Adams</v>
+        <v>CHESCA</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-15</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:54</v>
+        <v>4:03</v>
       </c>
       <c r="H79" t="str">
-        <v>CHESCA</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-15</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:03</v>
+        <v>4:50</v>
       </c>
       <c r="H80" t="str">
-        <v>Dermot Kennedy</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-15</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:50</v>
+        <v>3:06</v>
       </c>
       <c r="H81" t="str">
-        <v>earMUSIC</v>
+        <v>Y2K</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-15</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:06</v>
+        <v>2:43</v>
       </c>
       <c r="H82" t="str">
-        <v>Y2K</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-15</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:43</v>
+        <v>6:21</v>
       </c>
       <c r="H83" t="str">
-        <v>Lainey Wilson</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-15</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>6:21</v>
+        <v>2:46</v>
       </c>
       <c r="H84" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-15</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:46</v>
+        <v>2:42</v>
       </c>
       <c r="H85" t="str">
-        <v>Bryan Ferry</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-15</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:42</v>
+        <v>3:04</v>
       </c>
       <c r="H86" t="str">
-        <v>Saint Harison</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-15</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:04</v>
+        <v>2:59</v>
       </c>
       <c r="H87" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-15</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:59</v>
+        <v>2:22</v>
       </c>
       <c r="H88" t="str">
-        <v>Catie Turner</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-15</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:22</v>
+        <v>3:53</v>
       </c>
       <c r="H89" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Roxette</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-15</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:53</v>
+        <v>2:28</v>
       </c>
       <c r="H90" t="str">
-        <v>Roxette</v>
+        <v>Marcin</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-15</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:28</v>
+        <v>2:47</v>
       </c>
       <c r="H91" t="str">
-        <v>Marcin</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-15</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:47</v>
+        <v>3:40</v>
       </c>
       <c r="H92" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Laufey</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-15</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:40</v>
+        <v>2:49</v>
       </c>
       <c r="H93" t="str">
-        <v>Laufey</v>
+        <v>Ava Max</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-15</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:49</v>
+        <v>4:49</v>
       </c>
       <c r="H94" t="str">
-        <v>Ava Max</v>
+        <v>U2</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-15</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:49</v>
+        <v>3:35</v>
       </c>
       <c r="H95" t="str">
-        <v>U2</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-15</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:35</v>
+        <v>2:59</v>
       </c>
       <c r="H96" t="str">
-        <v>Taylor Swift</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-15</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:59</v>
+        <v>4:38</v>
       </c>
       <c r="H97" t="str">
-        <v>Kiana Ledé</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-15</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:38</v>
+        <v>3:46</v>
       </c>
       <c r="H98" t="str">
-        <v>Jessie Ware</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-15</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:46</v>
+        <v>3:08</v>
       </c>
       <c r="H99" t="str">
-        <v>Madison Beer</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-15</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:08</v>
+        <v>5:32</v>
       </c>
       <c r="H100" t="str">
-        <v>Sean Stemaly</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-15</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:32</v>
+        <v>4:39</v>
       </c>
       <c r="H101" t="str">
-        <v>earMUSIC</v>
+        <v>georgemichael</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Porch Light</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-15</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G102" t="str">
-        <v>4:39</v>
+        <v>4:22</v>
       </c>
       <c r="H102" t="str">
-        <v>georgemichael</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
       </c>
       <c r="L102" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Porch Light - Noah Kahan</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Porch Light</v>
+        <v>Dry Spell</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
+        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-15</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Great Divide</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G103" t="str">
-        <v>4:22</v>
+        <v>3:17</v>
       </c>
       <c r="H103" t="str">
-        <v>Noah Kahan</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
+        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
       </c>
       <c r="L103" t="str">
-        <v>Porch Light - Noah Kahan</v>
+        <v>Dry Spell - Kacey Musgraves</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Dry Spell</v>
+        <v>The Visitor</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
+        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-15</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Middle of Nowhere</v>
+        <v>The Visitor - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:17</v>
+        <v>3:48</v>
       </c>
       <c r="H104" t="str">
-        <v>Kacey Musgraves</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
+        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
       </c>
       <c r="L104" t="str">
-        <v>Dry Spell - Kacey Musgraves</v>
+        <v>The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>The Visitor</v>
+        <v>I Ain't No Cowboy</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
+        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-15</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Visitor - Single</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G105" t="str">
-        <v>3:48</v>
+        <v>3:13</v>
       </c>
       <c r="H105" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
+        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
       </c>
       <c r="L105" t="str">
-        <v>The Visitor - SIENNA SPIRO</v>
+        <v>I Ain't No Cowboy - Luke Combs</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>I Ain't No Cowboy</v>
+        <v>Can't Sit Still</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
+        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-15</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Way I Am</v>
+        <v>Can't Sit Still - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:13</v>
+        <v>3:35</v>
       </c>
       <c r="H106" t="str">
-        <v>Luke Combs</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
+        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
       </c>
       <c r="L106" t="str">
-        <v>I Ain't No Cowboy - Luke Combs</v>
+        <v>Can't Sit Still - Lainey Wilson</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Can't Sit Still</v>
+        <v>All I Did Was Dream of You (feat. The Marías)</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
+        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-15</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Can't Sit Still - Single</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:35</v>
+        <v>3:43</v>
       </c>
       <c r="H107" t="str">
-        <v>Lainey Wilson</v>
+        <v>beabadoobee</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
+        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
       </c>
       <c r="L107" t="str">
-        <v>Can't Sit Still - Lainey Wilson</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías)</v>
+        <v>Blow My Mind</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
+        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-15</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
+        <v>Sexistential</v>
       </c>
       <c r="G108" t="str">
-        <v>3:43</v>
+        <v>2:57</v>
       </c>
       <c r="H108" t="str">
-        <v>beabadoobee</v>
+        <v>Robyn</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
+        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
       </c>
       <c r="L108" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
+        <v>Blow My Mind - Robyn</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Blow My Mind</v>
+        <v>SATA</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
+        <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-15</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Sexistential</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G109" t="str">
-        <v>2:57</v>
+        <v>3:02</v>
       </c>
       <c r="H109" t="str">
-        <v>Robyn</v>
+        <v>John Summit</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
+        <v>https://music.apple.com/us/album/sata/1874015470</v>
       </c>
       <c r="L109" t="str">
-        <v>Blow My Mind - Robyn</v>
+        <v>SATA - John Summit</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SATA</v>
+        <v>Una Aventura</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/sata/1874015489</v>
+        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-15</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>Una Aventura - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:02</v>
+        <v>3:00</v>
       </c>
       <c r="H110" t="str">
-        <v>John Summit</v>
+        <v>Ozuna</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/sata/1874015470</v>
+        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
       </c>
       <c r="L110" t="str">
-        <v>SATA - John Summit</v>
+        <v>Una Aventura - Ozuna</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Una Aventura</v>
+        <v>Home (feat. Hikaru Utada)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
+        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-15</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Una Aventura - Single</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G111" t="str">
-        <v>3:00</v>
+        <v>3:44</v>
       </c>
       <c r="H111" t="str">
-        <v>Ozuna</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
+        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
       </c>
       <c r="L111" t="str">
-        <v>Una Aventura - Ozuna</v>
+        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>dirty wedding dress</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-15</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Whatever's Clever!</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G112" t="str">
-        <v>3:44</v>
+        <v>4:49</v>
       </c>
       <c r="H112" t="str">
-        <v>Charlie Puth</v>
+        <v>Bleachers</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
       </c>
       <c r="L112" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>dirty wedding dress - Bleachers</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>dirty wedding dress</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-15</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G113" t="str">
-        <v>4:49</v>
+        <v>3:07</v>
       </c>
       <c r="H113" t="str">
-        <v>Bleachers</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L113" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-15</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Age of the Ram</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:07</v>
+        <v>3:13</v>
       </c>
       <c r="H114" t="str">
-        <v>Charley Crockett</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L114" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Trade Places</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-15</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>Monica</v>
       </c>
       <c r="G115" t="str">
-        <v>3:13</v>
+        <v>3:02</v>
       </c>
       <c r="H115" t="str">
-        <v>Grupo Frontera</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L115" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Trade Places</v>
+        <v>Motion Party</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-15</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Monica</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:02</v>
+        <v>1:35</v>
       </c>
       <c r="H116" t="str">
-        <v>Jack Harlow</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L116" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Motion Party</v>
+        <v>Woman</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-15</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Motion Party - Single</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>1:35</v>
+        <v>2:46</v>
       </c>
       <c r="H117" t="str">
-        <v>Bossman Dlow</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L117" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Woman</v>
+        <v>Sunburn</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-15</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Woman - Single</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:46</v>
+        <v>3:05</v>
       </c>
       <c r="H118" t="str">
-        <v>Kane Brown</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L118" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Sunburn</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-15</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Sunburn - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G119" t="str">
-        <v>3:05</v>
+        <v>2:54</v>
       </c>
       <c r="H119" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L119" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Que Te Costó</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-15</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Metamorfosis</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:54</v>
+        <v>2:15</v>
       </c>
       <c r="H120" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L120" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>oooshxt!</v>
+        <v>Cruel World</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-15</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>oooshxt! - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G121" t="str">
-        <v>2:15</v>
+        <v>3:26</v>
       </c>
       <c r="H121" t="str">
-        <v>Samara Cyn</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L121" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Cruel World</v>
+        <v>Star</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-15</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Cruel World</v>
+        <v>Star - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:26</v>
+        <v>3:25</v>
       </c>
       <c r="H122" t="str">
-        <v>Holly Humberstone</v>
+        <v>Iceage</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L122" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Star</v>
+        <v>Get Go</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-15</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Star - Single</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G123" t="str">
-        <v>3:25</v>
+        <v>3:22</v>
       </c>
       <c r="H123" t="str">
-        <v>Iceage</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L123" t="str">
-        <v>Star - Iceage</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Get Go</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-15</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Distracted</v>
       </c>
       <c r="G124" t="str">
-        <v>3:22</v>
+        <v>3:14</v>
       </c>
       <c r="H124" t="str">
-        <v>Arlo Parks</v>
+        <v>Thundercat</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L124" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>ThunderWave</v>
+        <v>Club Song</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-15</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Distracted</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:14</v>
+        <v>2:27</v>
       </c>
       <c r="H125" t="str">
-        <v>Thundercat</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L125" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Club Song</v>
+        <v>Better Man</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-15</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Club Song - Single</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:27</v>
+        <v>2:53</v>
       </c>
       <c r="H126" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>jxdn</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L126" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Better Man</v>
+        <v>sabotage</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-15</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Better Man - Single</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:53</v>
+        <v>2:58</v>
       </c>
       <c r="H127" t="str">
-        <v>jxdn</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L127" t="str">
-        <v>Better Man - jxdn</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>sabotage</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-15</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>sabotage - Single</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:58</v>
+        <v>2:56</v>
       </c>
       <c r="H128" t="str">
-        <v>Natalie Jane</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L128" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>Naked</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-15</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:56</v>
+        <v>3:39</v>
       </c>
       <c r="H129" t="str">
-        <v>WHATMORE</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L129" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Naked</v>
+        <v>Catharina</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-15</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Naked - Single</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:39</v>
+        <v>3:27</v>
       </c>
       <c r="H130" t="str">
-        <v>Kenya Grace</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L130" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Catharina</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-15</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Catharina - Single</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:27</v>
+        <v>3:00</v>
       </c>
       <c r="H131" t="str">
-        <v>Martin Garrix</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L131" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>Trying Times</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-15</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G132" t="str">
-        <v>3:00</v>
+        <v>4:33</v>
       </c>
       <c r="H132" t="str">
-        <v>Chase &amp; Status</v>
+        <v>James Blake</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L132" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Trying Times</v>
+        <v>595</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-15</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Trying Times</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G133" t="str">
-        <v>4:33</v>
+        <v>2:29</v>
       </c>
       <c r="H133" t="str">
-        <v>James Blake</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L133" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>595</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-15</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Soft 2</v>
       </c>
       <c r="G134" t="str">
-        <v>2:29</v>
+        <v>3:50</v>
       </c>
       <c r="H134" t="str">
-        <v>Violet Grohl</v>
+        <v>LANY</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L134" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>CALL ME</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-15</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Soft 2</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:50</v>
+        <v>2:10</v>
       </c>
       <c r="H135" t="str">
-        <v>LANY</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L135" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>CALL ME</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-15</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>CALL ME - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G136" t="str">
-        <v>2:10</v>
+        <v>2:00</v>
       </c>
       <c r="H136" t="str">
-        <v>ALTÉGO</v>
+        <v>Nasty C</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L136" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Mi Amor</v>
+        <v>BOBA</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-15</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Free (Deluxe)</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:00</v>
+        <v>3:00</v>
       </c>
       <c r="H137" t="str">
-        <v>Nasty C</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L137" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>BOBA</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-15</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>BOBA - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G138" t="str">
-        <v>3:00</v>
+        <v>2:38</v>
       </c>
       <c r="H138" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L138" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Video Shoot</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-15</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Skeletor</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:38</v>
+        <v>2:06</v>
       </c>
       <c r="H139" t="str">
-        <v>Chief Keef</v>
+        <v>Shenseea</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L139" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Just Believe</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-15</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:06</v>
+        <v>2:41</v>
       </c>
       <c r="H140" t="str">
-        <v>Shenseea</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L140" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Just Believe</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-15</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Just Believe - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G141" t="str">
-        <v>2:41</v>
+        <v>2:57</v>
       </c>
       <c r="H141" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L141" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Knife In The Heart</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-15</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>The Afterparty</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:57</v>
+        <v>3:09</v>
       </c>
       <c r="H142" t="str">
-        <v>Lykke Li</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L142" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>The Way We Touch</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-15</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G143" t="str">
-        <v>3:09</v>
+        <v>4:06</v>
       </c>
       <c r="H143" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L143" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>DANGEROUS</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-15</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Dear God</v>
       </c>
       <c r="G144" t="str">
-        <v>4:06</v>
+        <v>3:33</v>
       </c>
       <c r="H144" t="str">
-        <v>Magnolia Park</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L144" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>When I Wake Up</v>
+        <v>Breathe</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-15</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Dear God</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:33</v>
+        <v>2:56</v>
       </c>
       <c r="H145" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L145" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Breathe</v>
+        <v>Minty</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-15</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Breathe - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G146" t="str">
-        <v>2:56</v>
+        <v>1:47</v>
       </c>
       <c r="H146" t="str">
-        <v>Malcolm Todd</v>
+        <v>MIKE</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L146" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Minty</v>
+        <v>Earth</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-15</v>
@@ -5964,33 +5964,33 @@
         <v>POMPEII // UTILITY</v>
       </c>
       <c r="G147" t="str">
-        <v>1:47</v>
+        <v>1:37</v>
       </c>
       <c r="H147" t="str">
-        <v>MIKE</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L147" t="str">
-        <v>Minty - MIKE</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Earth</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-15</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G148" t="str">
-        <v>1:37</v>
+        <v>3:42</v>
       </c>
       <c r="H148" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L148" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Drink The Water</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-15</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:42</v>
+        <v>4:32</v>
       </c>
       <c r="H149" t="str">
-        <v>Jack Johnson</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L149" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-15</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>4:32</v>
+        <v>3:32</v>
       </c>
       <c r="H150" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L150" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-15</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:32</v>
+        <v>3:08</v>
       </c>
       <c r="H151" t="str">
-        <v>Carly Pearce</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L151" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Muchacho Alegre</v>
+        <v>Real Slow</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-15</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G152" t="str">
-        <v>3:08</v>
+        <v>3:22</v>
       </c>
       <c r="H152" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L152" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Real Slow</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-15</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Work of Heart</v>
+        <v>As Is</v>
       </c>
       <c r="G153" t="str">
-        <v>3:22</v>
+        <v>2:42</v>
       </c>
       <c r="H153" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L153" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Mountain Girl</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-15</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>As Is</v>
+        <v>American Stories</v>
       </c>
       <c r="G154" t="str">
-        <v>2:42</v>
+        <v>3:31</v>
       </c>
       <c r="H154" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>Rostam</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L154" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Like a Spark</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-15</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>American Stories</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G155" t="str">
-        <v>3:31</v>
+        <v>3:29</v>
       </c>
       <c r="H155" t="str">
-        <v>Rostam</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L155" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Cheesecake</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-15</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G156" t="str">
-        <v>3:29</v>
+        <v>3:04</v>
       </c>
       <c r="H156" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L156" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-15</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>KINDA HARD</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:04</v>
+        <v>3:37</v>
       </c>
       <c r="H157" t="str">
-        <v>Bilmuri</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L157" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Freakin’ Out</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-15</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:37</v>
+        <v>3:03</v>
       </c>
       <c r="H158" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L158" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Name in Vein</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-15</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Name in Vein - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G159" t="str">
-        <v>3:03</v>
+        <v>4:05</v>
       </c>
       <c r="H159" t="str">
-        <v>VOILÀ</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L159" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-15</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Into Oblivion</v>
+        <v>Sweat</v>
       </c>
       <c r="G160" t="str">
-        <v>4:05</v>
+        <v>3:34</v>
       </c>
       <c r="H160" t="str">
-        <v>Lamb of God</v>
+        <v>Melanie C</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L160" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Undefeated Champion</v>
+        <v>Pull Up</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-15</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Sweat</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:34</v>
+        <v>2:35</v>
       </c>
       <c r="H161" t="str">
-        <v>Melanie C</v>
+        <v>Collect 200</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L161" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Pull Up</v>
+        <v>Ranjha</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-15</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Pull Up - Single</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:35</v>
+        <v>3:04</v>
       </c>
       <c r="H162" t="str">
-        <v>Collect 200</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L162" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Ranjha</v>
+        <v>zombies in love</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-15</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Ranjha - Single</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:04</v>
+        <v>2:53</v>
       </c>
       <c r="H163" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>paris jackson</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L163" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>zombies in love</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-15</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>zombies in love - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G164" t="str">
-        <v>2:53</v>
+        <v>4:39</v>
       </c>
       <c r="H164" t="str">
-        <v>paris jackson</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L164" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Days Of Us</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-15</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Full Circle</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:39</v>
+        <v>3:15</v>
       </c>
       <c r="H165" t="str">
-        <v>Tom Misch</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L165" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Life Of A Man</v>
+        <v>Ya No</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-15</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:15</v>
+        <v>3:40</v>
       </c>
       <c r="H166" t="str">
-        <v>1Ski OG</v>
+        <v>Marca MP</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L166" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Ya No</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-15</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Ya No - Single</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:40</v>
+        <v>3:48</v>
       </c>
       <c r="H167" t="str">
-        <v>Marca MP</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L167" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Relieve You</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-15</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:48</v>
+        <v>2:19</v>
       </c>
       <c r="H168" t="str">
-        <v>Spacey Jane</v>
+        <v>4Fargo</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L168" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Relieve You</v>
+        <v>Safety</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-15</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Relieve You - Single</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:19</v>
+        <v>3:18</v>
       </c>
       <c r="H169" t="str">
-        <v>4Fargo</v>
+        <v>Lekan</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L169" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Safety</v>
+        <v>Starlet</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-15</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Safety - Single</v>
+        <v>LK99</v>
       </c>
       <c r="G170" t="str">
-        <v>3:18</v>
+        <v>2:56</v>
       </c>
       <c r="H170" t="str">
-        <v>Lekan</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L170" t="str">
-        <v>Safety - Lekan</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Starlet</v>
+        <v>Physical</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-15</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>LK99</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:56</v>
+        <v>3:52</v>
       </c>
       <c r="H171" t="str">
-        <v>Leven Kali</v>
+        <v>Jacquees</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L171" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Physical</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-15</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Physical - Single</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:52</v>
+        <v>4:29</v>
       </c>
       <c r="H172" t="str">
-        <v>Jacquees</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L172" t="str">
-        <v>Physical - Jacquees</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Regalito</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-15</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G173" t="str">
-        <v>4:29</v>
+        <v>2:41</v>
       </c>
       <c r="H173" t="str">
-        <v>Casper Sage</v>
+        <v>Piso 21</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L173" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Regalito</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-15</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>TRESCENDER</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G174" t="str">
-        <v>2:41</v>
+        <v>4:09</v>
       </c>
       <c r="H174" t="str">
-        <v>Piso 21</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L174" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Cruel Streak</v>
+        <v>Die Young</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-15</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G175" t="str">
-        <v>4:09</v>
+        <v>3:52</v>
       </c>
       <c r="H175" t="str">
-        <v>The Black Crowes</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L175" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Die Young</v>
+        <v>Island Girl</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-15</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Little Wide Open</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:52</v>
+        <v>3:27</v>
       </c>
       <c r="H176" t="str">
-        <v>Kevin Morby</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L176" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Island Girl</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-15</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Island Girl - Single</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:27</v>
+        <v>2:20</v>
       </c>
       <c r="H177" t="str">
-        <v>Pia Mia</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L177" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-15</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:20</v>
+        <v>3:22</v>
       </c>
       <c r="H178" t="str">
-        <v>Claudia Valentina</v>
+        <v>Shaggy</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L178" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-15</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:22</v>
+        <v>3:44</v>
       </c>
       <c r="H179" t="str">
-        <v>Shaggy</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L179" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Tommy’s Song</v>
+        <v>Rainbows</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-15</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Lovers - Single</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:44</v>
+        <v>3:25</v>
       </c>
       <c r="H180" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L180" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Rainbows</v>
+        <v>butterflies</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-15</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Rainbows - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G181" t="str">
-        <v>3:25</v>
+        <v>2:48</v>
       </c>
       <c r="H181" t="str">
-        <v>Allison Russell</v>
+        <v>runo plum</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L181" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>butterflies</v>
+        <v>You're Right</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-15</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Bloom Again - EP</v>
+        <v>You're Right - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:48</v>
+        <v>3:00</v>
       </c>
       <c r="H182" t="str">
-        <v>runo plum</v>
+        <v>Emma Harner</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
       </c>
       <c r="L182" t="str">
-        <v>butterflies - runo plum</v>
+        <v>You're Right - Emma Harner</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You're Right</v>
+        <v>Bible Belt</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-15</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>You're Right - Single</v>
+        <v>Bible Belt - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:00</v>
+        <v>3:34</v>
       </c>
       <c r="H183" t="str">
-        <v>Emma Harner</v>
+        <v>Baby Bugs</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
       </c>
       <c r="L183" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>Bible Belt - Baby Bugs</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Bible Belt</v>
+        <v>Daze</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-15</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Bible Belt - Single</v>
+        <v>Daze - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:34</v>
+        <v>3:22</v>
       </c>
       <c r="H184" t="str">
-        <v>Baby Bugs</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
       </c>
       <c r="L184" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>Daze - Olympia Vitalis</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Daze</v>
+        <v>Passionfruit</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-15</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Daze - Single</v>
+        <v>Passionfruit - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:22</v>
+        <v>3:57</v>
       </c>
       <c r="H185" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
       </c>
       <c r="L185" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>Passionfruit - Anish Kumar</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Passionfruit</v>
+        <v>Madan</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-15</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Passionfruit - Single</v>
+        <v>Madan - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:57</v>
+        <v>2:56</v>
       </c>
       <c r="H186" t="str">
-        <v>Anish Kumar</v>
+        <v>Jonas Blue</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
       </c>
       <c r="L186" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>Madan - Jonas Blue</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Madan</v>
+        <v>Bad Bitch</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-15</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Madan - Single</v>
+        <v>Bad Bitch - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:56</v>
+        <v>2:28</v>
       </c>
       <c r="H187" t="str">
-        <v>Jonas Blue</v>
+        <v>41</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
       </c>
       <c r="L187" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Bad Bitch - 41</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Bad Bitch</v>
+        <v>Shame</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-15</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Devotion [Deluxe]</v>
       </c>
       <c r="G188" t="str">
-        <v>2:28</v>
+        <v>3:36</v>
       </c>
       <c r="H188" t="str">
-        <v>41</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
       </c>
       <c r="L188" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Shame - Sunday (1994)</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Shame</v>
+        <v>teach you to love me</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-15</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>teach you to love me - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:36</v>
+        <v>3:09</v>
       </c>
       <c r="H189" t="str">
-        <v>Sunday (1994)</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
       </c>
       <c r="L189" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>teach you to love me - Hailey Picardi</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>teach you to love me</v>
+        <v>The Fix</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-15</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>teach you to love me - Single</v>
+        <v>The Fix - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:09</v>
+        <v>2:42</v>
       </c>
       <c r="H190" t="str">
-        <v>Hailey Picardi</v>
+        <v>Baby J</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
       </c>
       <c r="L190" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>The Fix - Baby J</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>The Fix</v>
+        <v>Hanging on Hope</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-15</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>The Fix - Single</v>
+        <v>Hanging on Hope - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:42</v>
+        <v>3:43</v>
       </c>
       <c r="H191" t="str">
-        <v>Baby J</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
       </c>
       <c r="L191" t="str">
-        <v>The Fix - Baby J</v>
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Hanging on Hope</v>
+        <v>I Know What to Say Now</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-15</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>I Know What to Say Now - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:43</v>
+        <v>3:18</v>
       </c>
       <c r="H192" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Active Child</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
       </c>
       <c r="L192" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>I Know What to Say Now - Active Child</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>I Know What to Say Now</v>
+        <v>Feel Something</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-15</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Feel Something - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:18</v>
+        <v>3:09</v>
       </c>
       <c r="H193" t="str">
-        <v>Active Child</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
       </c>
       <c r="L193" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>Feel Something - Baby Queen</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Feel Something</v>
+        <v>You Or Me</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-15</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Feel Something - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G194" t="str">
-        <v>3:09</v>
+        <v>5:28</v>
       </c>
       <c r="H194" t="str">
-        <v>Baby Queen</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
       </c>
       <c r="L194" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>You Or Me - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>You Or Me</v>
+        <v>Mortercheyn</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-15</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Coronach</v>
       </c>
       <c r="G195" t="str">
-        <v>5:28</v>
+        <v>4:18</v>
       </c>
       <c r="H195" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Hellripper</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
       </c>
       <c r="L195" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>Mortercheyn - Hellripper</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Mortercheyn</v>
+        <v>Rip The God</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-15</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Coronach</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G196" t="str">
-        <v>4:18</v>
+        <v>5:20</v>
       </c>
       <c r="H196" t="str">
-        <v>Hellripper</v>
+        <v>Melvins</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
       </c>
       <c r="L196" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>Rip The God - Melvins</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Rip The God</v>
+        <v>Who We Are</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-15</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Who We Are - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>5:20</v>
+        <v>2:10</v>
       </c>
       <c r="H197" t="str">
-        <v>Melvins</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
       </c>
       <c r="L197" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Who We Are - Kaleena Zanders</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Who We Are</v>
+        <v>Reels in 360</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-15</v>
@@ -7899,68 +7899,30 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Who We Are - Single</v>
+        <v>Dying Is The Internet</v>
       </c>
       <c r="G198" t="str">
-        <v>2:10</v>
+        <v>4:37</v>
       </c>
       <c r="H198" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Simo Cell</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
       <c r="L198" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Reels in 360</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Dying Is The Internet</v>
-      </c>
-      <c r="G199" t="str">
-        <v>4:37</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Simo Cell</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
-      </c>
-      <c r="L199" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week03/titles.xlsx
+++ b/data/global/2026-03-week03/titles.xlsx
@@ -591,7 +591,7 @@
         <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B6" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:12</v>
@@ -629,7 +629,7 @@
         <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B7" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:57</v>
@@ -705,7 +705,7 @@
         <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:48</v>
@@ -857,7 +857,7 @@
         <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B13" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:56</v>
@@ -895,7 +895,7 @@
         <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B14" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>2:54</v>
@@ -933,7 +933,7 @@
         <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:46</v>
@@ -1655,7 +1655,7 @@
         <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B34" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:52</v>
@@ -1693,7 +1693,7 @@
         <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B35" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>2:13</v>
@@ -1731,7 +1731,7 @@
         <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:19</v>
@@ -1883,7 +1883,7 @@
         <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B40" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:55</v>

--- a/data/global/2026-03-week03/titles.xlsx
+++ b/data/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L209"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>שרית חדד - Mamma Mia</v>
       </c>
       <c r="B2" t="str">
-        <v>4 days ago</v>
+        <v>2026-03-15</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410015&amp;sid=64ffd39bf093175dd74966d37c559395</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-15</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>4:09</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Mei Semones</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>שרית חדד - Mamma Mia</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>שראל סופר - מדויק ולא בערך</v>
       </c>
       <c r="B3" t="str">
-        <v>4 days ago</v>
+        <v>2026-03-15</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410014&amp;sid=64ffd39bf093175dd74966d37c559395</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-15</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>2:08</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>The Lemon Twigs</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>שראל סופר - מדויק ולא בערך</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>שמוליק סוכות - אבא טוב</v>
       </c>
       <c r="B4" t="str">
-        <v>4 days ago</v>
+        <v>2026-03-15</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410013&amp;sid=64ffd39bf093175dd74966d37c559395</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-15</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>2:57</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Natalie Jane</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>שמוליק סוכות - אבא טוב</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>שירה ואן ופרן - ייפול עליי</v>
       </c>
       <c r="B5" t="str">
-        <v>4 days ago</v>
+        <v>2026-03-15</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410012&amp;sid=64ffd39bf093175dd74966d37c559395</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-15</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>3:13</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Eurovision Song Contest</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>שירה ואן ופרן - ייפול עליי</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>רון דבני - מה אני אגיד לך</v>
       </c>
       <c r="B6" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-15</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410011&amp;sid=64ffd39bf093175dd74966d37c559395</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-15</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>4:12</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>David Gilmour</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>רון דבני - מה אני אגיד לך</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>נטע ברזילי - גם זה יגיע</v>
       </c>
       <c r="B7" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-15</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410010&amp;sid=64ffd39bf093175dd74966d37c559395</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-15</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>3:57</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Far Caspian</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>נטע ברזילי - גם זה יגיע</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>מאי כהן - אנשים</v>
       </c>
       <c r="B8" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-15</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410009&amp;sid=64ffd39bf093175dd74966d37c559395</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-15</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>3:34</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>Celine Dion</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>מאי כהן - אנשים</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>איציק סנדרוי - תנו לי אוויר</v>
       </c>
       <c r="B9" t="str">
-        <v>9 days ago</v>
+        <v>2026-03-15</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410008&amp;sid=64ffd39bf093175dd74966d37c559395</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-15</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>3:48</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>Harry Styles</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>איציק סנדרוי - תנו לי אוויר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>אהרון סיטבון - ניגון יהודי</v>
       </c>
       <c r="B10" t="str">
-        <v>8 days ago</v>
+        <v>2026-03-15</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410007&amp;sid=64ffd39bf093175dd74966d37c559395</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-15</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>8 days ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>4:58</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>אהרון סיטבון - ניגון יהודי</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>אבישי אזיקרי - לימונדה</v>
       </c>
       <c r="B11" t="str">
-        <v>8 days ago</v>
+        <v>2026-03-15</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410006&amp;sid=64ffd39bf093175dd74966d37c559395</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-15</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>8 days ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>2:33</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>Ellise</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>אבישי אזיקרי - לימונדה</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>אבי אילסון - בזכותם</v>
       </c>
       <c r="B12" t="str">
-        <v>8 days ago</v>
+        <v>2026-03-15</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410005&amp;sid=64ffd39bf093175dd74966d37c559395</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-15</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>8 days ago</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>5:01</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>The Doobie Brothers</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>אבי אילסון - בזכותם</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B13" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-15</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:56</v>
+        <v>4:09</v>
       </c>
       <c r="H13" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-15</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:54</v>
+        <v>2:08</v>
       </c>
       <c r="H14" t="str">
-        <v>Bebe Rexha</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-15</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:46</v>
+        <v>2:57</v>
       </c>
       <c r="H15" t="str">
-        <v>NathanEvanss</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B16" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-15</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:56</v>
+        <v>3:13</v>
       </c>
       <c r="H16" t="str">
-        <v>R3HAB</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B17" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-15</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:21</v>
+        <v>4:12</v>
       </c>
       <c r="H17" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B18" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-15</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:16</v>
+        <v>3:57</v>
       </c>
       <c r="H18" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B19" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-15</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:41</v>
+        <v>3:34</v>
       </c>
       <c r="H19" t="str">
-        <v>Johnny Orlando</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B20" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-15</v>
@@ -1138,10 +1138,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:29</v>
+        <v>3:48</v>
       </c>
       <c r="H20" t="str">
-        <v>Russell Dickerson</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-15</v>
@@ -1176,10 +1176,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:43</v>
+        <v>4:58</v>
       </c>
       <c r="H21" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-15</v>
@@ -1214,10 +1214,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:46</v>
+        <v>2:33</v>
       </c>
       <c r="H22" t="str">
-        <v>Matt Hansen</v>
+        <v>Ellise</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B23" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-15</v>
@@ -1252,10 +1252,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:01</v>
+        <v>5:01</v>
       </c>
       <c r="H23" t="str">
-        <v>Mike Posner</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B24" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-15</v>
@@ -1290,10 +1290,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:23</v>
+        <v>4:56</v>
       </c>
       <c r="H24" t="str">
-        <v>Katelyn Tarver</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B25" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-15</v>
@@ -1328,10 +1328,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:39</v>
+        <v>2:54</v>
       </c>
       <c r="H25" t="str">
-        <v>almost monday</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B26" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-15</v>
@@ -1366,10 +1366,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:04</v>
+        <v>2:46</v>
       </c>
       <c r="H26" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-15</v>
@@ -1404,10 +1404,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:25</v>
+        <v>2:56</v>
       </c>
       <c r="H27" t="str">
-        <v>vaultboy</v>
+        <v>R3HAB</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B28" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-15</v>
@@ -1442,10 +1442,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:49</v>
+        <v>3:21</v>
       </c>
       <c r="H28" t="str">
-        <v>The Warning</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B29" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-15</v>
@@ -1480,10 +1480,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:14</v>
+        <v>3:16</v>
       </c>
       <c r="H29" t="str">
-        <v>aron!</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B30" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-15</v>
@@ -1518,10 +1518,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:43</v>
+        <v>2:41</v>
       </c>
       <c r="H30" t="str">
-        <v>Bazzi</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B31" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-15</v>
@@ -1556,10 +1556,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:43</v>
+        <v>2:29</v>
       </c>
       <c r="H31" t="str">
-        <v>Sting</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B32" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-15</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:44</v>
+        <v>2:43</v>
       </c>
       <c r="H32" t="str">
-        <v>Dean Lewis</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-15</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:37</v>
+        <v>3:46</v>
       </c>
       <c r="H33" t="str">
-        <v>Jessie Ware</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-15</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:52</v>
+        <v>4:01</v>
       </c>
       <c r="H34" t="str">
-        <v>Cannons</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-15</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:13</v>
+        <v>3:23</v>
       </c>
       <c r="H35" t="str">
-        <v>Kim Petras</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B36" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-15</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:19</v>
+        <v>3:39</v>
       </c>
       <c r="H36" t="str">
-        <v>Vanessa Carlton</v>
+        <v>almost monday</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-15</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:31</v>
+        <v>3:04</v>
       </c>
       <c r="H37" t="str">
-        <v>Kiana Ledé</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-15</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:43</v>
+        <v>3:25</v>
       </c>
       <c r="H38" t="str">
-        <v>Ringo Starr</v>
+        <v>vaultboy</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-15</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:10</v>
+        <v>3:49</v>
       </c>
       <c r="H39" t="str">
-        <v>Maya Hawke</v>
+        <v>The Warning</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-15</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:55</v>
+        <v>2:14</v>
       </c>
       <c r="H40" t="str">
-        <v>Armin van Buuren</v>
+        <v>aron!</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-15</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:52</v>
+        <v>2:43</v>
       </c>
       <c r="H41" t="str">
-        <v>Demi Lovato</v>
+        <v>Bazzi</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B42" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-15</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:53</v>
+        <v>4:43</v>
       </c>
       <c r="H42" t="str">
-        <v>Peter Gabriel</v>
+        <v>Sting</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-15</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:30</v>
+        <v>2:44</v>
       </c>
       <c r="H43" t="str">
-        <v>Jessie J</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-15</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>5:18</v>
+        <v>4:37</v>
       </c>
       <c r="H44" t="str">
-        <v>Harry Styles</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B45" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-15</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>7:20</v>
+        <v>4:52</v>
       </c>
       <c r="H45" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Cannons</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B46" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-15</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:01</v>
+        <v>2:13</v>
       </c>
       <c r="H46" t="str">
-        <v>BRITs</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B47" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-15</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:31</v>
+        <v>3:19</v>
       </c>
       <c r="H47" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B48" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-15</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:00</v>
+        <v>2:31</v>
       </c>
       <c r="H48" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B49" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-15</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:11</v>
+        <v>2:43</v>
       </c>
       <c r="H49" t="str">
-        <v>The Kiffness</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-15</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:32</v>
+        <v>3:10</v>
       </c>
       <c r="H50" t="str">
-        <v>Lauv</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-15</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>5:03</v>
+        <v>3:55</v>
       </c>
       <c r="H51" t="str">
-        <v>RAYE</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-15</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:50</v>
+        <v>3:52</v>
       </c>
       <c r="H52" t="str">
-        <v>Armik</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-15</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:53</v>
+        <v>2:53</v>
       </c>
       <c r="H53" t="str">
-        <v>Scorpions</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-15</v>
@@ -2430,10 +2430,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:04</v>
+        <v>4:30</v>
       </c>
       <c r="H54" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Jessie J</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-15</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:32</v>
+        <v>5:18</v>
       </c>
       <c r="H55" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-15</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:47</v>
+        <v>7:20</v>
       </c>
       <c r="H56" t="str">
-        <v>Girl Tones</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-15</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:40</v>
+        <v>3:01</v>
       </c>
       <c r="H57" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>BRITs</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-15</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:05</v>
+        <v>3:31</v>
       </c>
       <c r="H58" t="str">
-        <v>HAUSER</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-15</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:59</v>
+        <v>3:00</v>
       </c>
       <c r="H59" t="str">
-        <v>Queen Official</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-15</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:55</v>
+        <v>3:11</v>
       </c>
       <c r="H60" t="str">
-        <v>Tenille Townes</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-15</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>5:12</v>
+        <v>3:32</v>
       </c>
       <c r="H61" t="str">
-        <v>Self Esteem</v>
+        <v>Lauv</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-15</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:47</v>
+        <v>5:03</v>
       </c>
       <c r="H62" t="str">
-        <v>Jennifer Lopez</v>
+        <v>RAYE</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-15</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:18</v>
+        <v>4:50</v>
       </c>
       <c r="H63" t="str">
-        <v>Em Beihold</v>
+        <v>Armik</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-15</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:50</v>
+        <v>4:53</v>
       </c>
       <c r="H64" t="str">
-        <v>Michael Bublé</v>
+        <v>Scorpions</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-15</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:24</v>
+        <v>3:04</v>
       </c>
       <c r="H65" t="str">
-        <v>MyKey</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-15</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:36</v>
+        <v>4:32</v>
       </c>
       <c r="H66" t="str">
-        <v>Max McNown</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-15</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:34</v>
+        <v>3:47</v>
       </c>
       <c r="H67" t="str">
-        <v>Megan Moroney</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-15</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:03</v>
+        <v>3:40</v>
       </c>
       <c r="H68" t="str">
-        <v>ERNEST</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-15</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:31</v>
+        <v>4:05</v>
       </c>
       <c r="H69" t="str">
-        <v>Bruno Mars</v>
+        <v>HAUSER</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-15</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:22</v>
+        <v>2:59</v>
       </c>
       <c r="H70" t="str">
-        <v>BLACKPINK</v>
+        <v>Queen Official</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-15</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>5:49</v>
+        <v>3:55</v>
       </c>
       <c r="H71" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-15</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:47</v>
+        <v>5:12</v>
       </c>
       <c r="H72" t="str">
-        <v>Nessa Barrett</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-15</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:20</v>
+        <v>3:47</v>
       </c>
       <c r="H73" t="str">
-        <v>Towa Bird</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-15</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:18</v>
+        <v>3:18</v>
       </c>
       <c r="H74" t="str">
-        <v>Ty Myers</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-15</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:39</v>
+        <v>3:50</v>
       </c>
       <c r="H75" t="str">
-        <v>kenzie</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-15</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:52</v>
+        <v>3:24</v>
       </c>
       <c r="H76" t="str">
-        <v>Leanna Crawford</v>
+        <v>MyKey</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-15</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:01</v>
+        <v>2:36</v>
       </c>
       <c r="H77" t="str">
-        <v>Bryan Adams</v>
+        <v>Max McNown</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-15</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:54</v>
+        <v>3:34</v>
       </c>
       <c r="H78" t="str">
-        <v>CHESCA</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-15</v>
@@ -3383,7 +3383,7 @@
         <v>4:03</v>
       </c>
       <c r="H79" t="str">
-        <v>Dermot Kennedy</v>
+        <v>ERNEST</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-15</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:50</v>
+        <v>3:31</v>
       </c>
       <c r="H80" t="str">
-        <v>earMUSIC</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-15</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:06</v>
+        <v>3:22</v>
       </c>
       <c r="H81" t="str">
-        <v>Y2K</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-15</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:43</v>
+        <v>5:49</v>
       </c>
       <c r="H82" t="str">
-        <v>Lainey Wilson</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-15</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>6:21</v>
+        <v>3:47</v>
       </c>
       <c r="H83" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-15</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:46</v>
+        <v>2:20</v>
       </c>
       <c r="H84" t="str">
-        <v>Bryan Ferry</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-15</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:42</v>
+        <v>4:18</v>
       </c>
       <c r="H85" t="str">
-        <v>Saint Harison</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-15</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:04</v>
+        <v>2:39</v>
       </c>
       <c r="H86" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>kenzie</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-15</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:59</v>
+        <v>3:52</v>
       </c>
       <c r="H87" t="str">
-        <v>Catie Turner</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-15</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:22</v>
+        <v>4:01</v>
       </c>
       <c r="H88" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-15</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:53</v>
+        <v>2:54</v>
       </c>
       <c r="H89" t="str">
-        <v>Roxette</v>
+        <v>CHESCA</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-15</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:28</v>
+        <v>4:03</v>
       </c>
       <c r="H90" t="str">
-        <v>Marcin</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-15</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:47</v>
+        <v>4:50</v>
       </c>
       <c r="H91" t="str">
-        <v>Nothing But Thieves</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-15</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:40</v>
+        <v>3:06</v>
       </c>
       <c r="H92" t="str">
-        <v>Laufey</v>
+        <v>Y2K</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-15</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:49</v>
+        <v>2:43</v>
       </c>
       <c r="H93" t="str">
-        <v>Ava Max</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-15</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>4:49</v>
+        <v>6:21</v>
       </c>
       <c r="H94" t="str">
-        <v>U2</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-15</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:35</v>
+        <v>2:46</v>
       </c>
       <c r="H95" t="str">
-        <v>Taylor Swift</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-15</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:59</v>
+        <v>2:42</v>
       </c>
       <c r="H96" t="str">
-        <v>Kiana Ledé</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-15</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:38</v>
+        <v>3:04</v>
       </c>
       <c r="H97" t="str">
-        <v>Jessie Ware</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-15</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:46</v>
+        <v>2:59</v>
       </c>
       <c r="H98" t="str">
-        <v>Madison Beer</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-15</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:08</v>
+        <v>2:22</v>
       </c>
       <c r="H99" t="str">
-        <v>Sean Stemaly</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-15</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:32</v>
+        <v>3:53</v>
       </c>
       <c r="H100" t="str">
-        <v>earMUSIC</v>
+        <v>Roxette</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-15</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:39</v>
+        <v>2:28</v>
       </c>
       <c r="H101" t="str">
-        <v>georgemichael</v>
+        <v>Marcin</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Porch Light</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-15</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>The Great Divide</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>4:22</v>
+        <v>2:47</v>
       </c>
       <c r="H102" t="str">
-        <v>Noah Kahan</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Porch Light - Noah Kahan</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Dry Spell</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-15</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Middle of Nowhere</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:17</v>
+        <v>3:40</v>
       </c>
       <c r="H103" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Laufey</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Dry Spell - Kacey Musgraves</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>The Visitor</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-15</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Visitor - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:48</v>
+        <v>2:49</v>
       </c>
       <c r="H104" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Ava Max</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>The Visitor - SIENNA SPIRO</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>I Ain't No Cowboy</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-15</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Way I Am</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>3:13</v>
+        <v>4:49</v>
       </c>
       <c r="H105" t="str">
-        <v>Luke Combs</v>
+        <v>U2</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>I Ain't No Cowboy - Luke Combs</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Can't Sit Still</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-15</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Can't Sit Still - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G106" t="str">
         <v>3:35</v>
       </c>
       <c r="H106" t="str">
-        <v>Lainey Wilson</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Can't Sit Still - Lainey Wilson</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-15</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:43</v>
+        <v>2:59</v>
       </c>
       <c r="H107" t="str">
-        <v>beabadoobee</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Blow My Mind</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-15</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Sexistential</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:57</v>
+        <v>4:38</v>
       </c>
       <c r="H108" t="str">
-        <v>Robyn</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>Blow My Mind - Robyn</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SATA</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/sata/1874015489</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-15</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:02</v>
+        <v>3:46</v>
       </c>
       <c r="H109" t="str">
-        <v>John Summit</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/sata/1874015470</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>SATA - John Summit</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Una Aventura</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-15</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Una Aventura - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>3:00</v>
+        <v>3:08</v>
       </c>
       <c r="H110" t="str">
-        <v>Ozuna</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>Una Aventura - Ozuna</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-15</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Whatever's Clever!</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G111" t="str">
-        <v>3:44</v>
+        <v>5:32</v>
       </c>
       <c r="H111" t="str">
-        <v>Charlie Puth</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>dirty wedding dress</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-15</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>everyone for ten minutes</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G112" t="str">
-        <v>4:49</v>
+        <v>4:39</v>
       </c>
       <c r="H112" t="str">
-        <v>Bleachers</v>
+        <v>georgemichael</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>Porch Light</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-15</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Age of the Ram</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G113" t="str">
-        <v>3:07</v>
+        <v>4:22</v>
       </c>
       <c r="H113" t="str">
-        <v>Charley Crockett</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
       </c>
       <c r="L113" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>Porch Light - Noah Kahan</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Dry Spell</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-15</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G114" t="str">
-        <v>3:13</v>
+        <v>3:17</v>
       </c>
       <c r="H114" t="str">
-        <v>Grupo Frontera</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
       </c>
       <c r="L114" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Dry Spell - Kacey Musgraves</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Trade Places</v>
+        <v>The Visitor</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-15</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Monica</v>
+        <v>The Visitor - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:02</v>
+        <v>3:48</v>
       </c>
       <c r="H115" t="str">
-        <v>Jack Harlow</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
       </c>
       <c r="L115" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Motion Party</v>
+        <v>I Ain't No Cowboy</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-15</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Motion Party - Single</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G116" t="str">
-        <v>1:35</v>
+        <v>3:13</v>
       </c>
       <c r="H116" t="str">
-        <v>Bossman Dlow</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
       </c>
       <c r="L116" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>I Ain't No Cowboy - Luke Combs</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Woman</v>
+        <v>Can't Sit Still</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-15</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Woman - Single</v>
+        <v>Can't Sit Still - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:46</v>
+        <v>3:35</v>
       </c>
       <c r="H117" t="str">
-        <v>Kane Brown</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
       </c>
       <c r="L117" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>Can't Sit Still - Lainey Wilson</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Sunburn</v>
+        <v>All I Did Was Dream of You (feat. The Marías)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-15</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Sunburn - Single</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:05</v>
+        <v>3:43</v>
       </c>
       <c r="H118" t="str">
-        <v>Tucker Wetmore</v>
+        <v>beabadoobee</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
       </c>
       <c r="L118" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Que Te Costó</v>
+        <v>Blow My Mind</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-15</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Metamorfosis</v>
+        <v>Sexistential</v>
       </c>
       <c r="G119" t="str">
-        <v>2:54</v>
+        <v>2:57</v>
       </c>
       <c r="H119" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Robyn</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
       </c>
       <c r="L119" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>Blow My Mind - Robyn</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>oooshxt!</v>
+        <v>SATA</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-15</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>oooshxt! - Single</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G120" t="str">
-        <v>2:15</v>
+        <v>3:02</v>
       </c>
       <c r="H120" t="str">
-        <v>Samara Cyn</v>
+        <v>John Summit</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/sata/1874015470</v>
       </c>
       <c r="L120" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>SATA - John Summit</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Cruel World</v>
+        <v>Una Aventura</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-15</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Cruel World</v>
+        <v>Una Aventura - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:26</v>
+        <v>3:00</v>
       </c>
       <c r="H121" t="str">
-        <v>Holly Humberstone</v>
+        <v>Ozuna</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
       </c>
       <c r="L121" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>Una Aventura - Ozuna</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Star</v>
+        <v>Home (feat. Hikaru Utada)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-15</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Star - Single</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G122" t="str">
-        <v>3:25</v>
+        <v>3:44</v>
       </c>
       <c r="H122" t="str">
-        <v>Iceage</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
       </c>
       <c r="L122" t="str">
-        <v>Star - Iceage</v>
+        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Get Go</v>
+        <v>dirty wedding dress</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-15</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Ambiguous Desire</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G123" t="str">
-        <v>3:22</v>
+        <v>4:49</v>
       </c>
       <c r="H123" t="str">
-        <v>Arlo Parks</v>
+        <v>Bleachers</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
       </c>
       <c r="L123" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>dirty wedding dress - Bleachers</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>ThunderWave</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-15</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Distracted</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G124" t="str">
-        <v>3:14</v>
+        <v>3:07</v>
       </c>
       <c r="H124" t="str">
-        <v>Thundercat</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L124" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Club Song</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-15</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Club Song - Single</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:27</v>
+        <v>3:13</v>
       </c>
       <c r="H125" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L125" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Better Man</v>
+        <v>Trade Places</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-15</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Better Man - Single</v>
+        <v>Monica</v>
       </c>
       <c r="G126" t="str">
-        <v>2:53</v>
+        <v>3:02</v>
       </c>
       <c r="H126" t="str">
-        <v>jxdn</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L126" t="str">
-        <v>Better Man - jxdn</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>sabotage</v>
+        <v>Motion Party</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-15</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>sabotage - Single</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:58</v>
+        <v>1:35</v>
       </c>
       <c r="H127" t="str">
-        <v>Natalie Jane</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L127" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>Woman</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-15</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:56</v>
+        <v>2:46</v>
       </c>
       <c r="H128" t="str">
-        <v>WHATMORE</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L128" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Naked</v>
+        <v>Sunburn</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-15</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Naked - Single</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:39</v>
+        <v>3:05</v>
       </c>
       <c r="H129" t="str">
-        <v>Kenya Grace</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L129" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Catharina</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-15</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Catharina - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G130" t="str">
-        <v>3:27</v>
+        <v>2:54</v>
       </c>
       <c r="H130" t="str">
-        <v>Martin Garrix</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L130" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-15</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:00</v>
+        <v>2:15</v>
       </c>
       <c r="H131" t="str">
-        <v>Chase &amp; Status</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L131" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Trying Times</v>
+        <v>Cruel World</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-15</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Trying Times</v>
+        <v>Cruel World</v>
       </c>
       <c r="G132" t="str">
-        <v>4:33</v>
+        <v>3:26</v>
       </c>
       <c r="H132" t="str">
-        <v>James Blake</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L132" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>595</v>
+        <v>Star</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-15</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Star - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:29</v>
+        <v>3:25</v>
       </c>
       <c r="H133" t="str">
-        <v>Violet Grohl</v>
+        <v>Iceage</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L133" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>Get Go</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-15</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Soft 2</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G134" t="str">
-        <v>3:50</v>
+        <v>3:22</v>
       </c>
       <c r="H134" t="str">
-        <v>LANY</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L134" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>CALL ME</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-15</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>CALL ME - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G135" t="str">
-        <v>2:10</v>
+        <v>3:14</v>
       </c>
       <c r="H135" t="str">
-        <v>ALTÉGO</v>
+        <v>Thundercat</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L135" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Mi Amor</v>
+        <v>Club Song</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-15</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Free (Deluxe)</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:00</v>
+        <v>2:27</v>
       </c>
       <c r="H136" t="str">
-        <v>Nasty C</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L136" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>BOBA</v>
+        <v>Better Man</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-15</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>BOBA - Single</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:00</v>
+        <v>2:53</v>
       </c>
       <c r="H137" t="str">
-        <v>SOFI TUKKER</v>
+        <v>jxdn</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L137" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Video Shoot</v>
+        <v>sabotage</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-15</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Skeletor</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:38</v>
+        <v>2:58</v>
       </c>
       <c r="H138" t="str">
-        <v>Chief Keef</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L138" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-15</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:06</v>
+        <v>2:56</v>
       </c>
       <c r="H139" t="str">
-        <v>Shenseea</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L139" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Just Believe</v>
+        <v>Naked</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-15</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Just Believe - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:41</v>
+        <v>3:39</v>
       </c>
       <c r="H140" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L140" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Knife In The Heart</v>
+        <v>Catharina</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-15</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>The Afterparty</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:57</v>
+        <v>3:27</v>
       </c>
       <c r="H141" t="str">
-        <v>Lykke Li</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L141" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>The Way We Touch</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-15</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:09</v>
+        <v>3:00</v>
       </c>
       <c r="H142" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L142" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>DANGEROUS</v>
+        <v>Trying Times</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-15</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Trying Times</v>
       </c>
       <c r="G143" t="str">
-        <v>4:06</v>
+        <v>4:33</v>
       </c>
       <c r="H143" t="str">
-        <v>Magnolia Park</v>
+        <v>James Blake</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L143" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>When I Wake Up</v>
+        <v>595</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-15</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Dear God</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G144" t="str">
-        <v>3:33</v>
+        <v>2:29</v>
       </c>
       <c r="H144" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L144" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Breathe</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-15</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Breathe - Single</v>
+        <v>Soft 2</v>
       </c>
       <c r="G145" t="str">
-        <v>2:56</v>
+        <v>3:50</v>
       </c>
       <c r="H145" t="str">
-        <v>Malcolm Todd</v>
+        <v>LANY</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L145" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Minty</v>
+        <v>CALL ME</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-15</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>1:47</v>
+        <v>2:10</v>
       </c>
       <c r="H146" t="str">
-        <v>MIKE</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L146" t="str">
-        <v>Minty - MIKE</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Earth</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-15</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G147" t="str">
-        <v>1:37</v>
+        <v>2:00</v>
       </c>
       <c r="H147" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>Nasty C</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L147" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drink The Water</v>
+        <v>BOBA</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-15</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:42</v>
+        <v>3:00</v>
       </c>
       <c r="H148" t="str">
-        <v>Jack Johnson</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L148" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-15</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G149" t="str">
-        <v>4:32</v>
+        <v>2:38</v>
       </c>
       <c r="H149" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L149" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-15</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:32</v>
+        <v>2:06</v>
       </c>
       <c r="H150" t="str">
-        <v>Carly Pearce</v>
+        <v>Shenseea</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L150" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Muchacho Alegre</v>
+        <v>Just Believe</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-15</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:08</v>
+        <v>2:41</v>
       </c>
       <c r="H151" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L151" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Real Slow</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-15</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Work of Heart</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G152" t="str">
-        <v>3:22</v>
+        <v>2:57</v>
       </c>
       <c r="H152" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L152" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Mountain Girl</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-15</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>As Is</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H153" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L153" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Like a Spark</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-15</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>American Stories</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G154" t="str">
-        <v>3:31</v>
+        <v>4:06</v>
       </c>
       <c r="H154" t="str">
-        <v>Rostam</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L154" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Cheesecake</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-15</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>Dear God</v>
       </c>
       <c r="G155" t="str">
-        <v>3:29</v>
+        <v>3:33</v>
       </c>
       <c r="H155" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L155" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Breathe</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-15</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>KINDA HARD</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:04</v>
+        <v>2:56</v>
       </c>
       <c r="H156" t="str">
-        <v>Bilmuri</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L156" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Freakin’ Out</v>
+        <v>Minty</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-15</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G157" t="str">
-        <v>3:37</v>
+        <v>1:47</v>
       </c>
       <c r="H157" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>MIKE</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L157" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Name in Vein</v>
+        <v>Earth</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-15</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Name in Vein - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G158" t="str">
-        <v>3:03</v>
+        <v>1:37</v>
       </c>
       <c r="H158" t="str">
-        <v>VOILÀ</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L158" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-15</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Into Oblivion</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G159" t="str">
-        <v>4:05</v>
+        <v>3:42</v>
       </c>
       <c r="H159" t="str">
-        <v>Lamb of God</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L159" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Undefeated Champion</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-15</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Sweat</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:34</v>
+        <v>4:32</v>
       </c>
       <c r="H160" t="str">
-        <v>Melanie C</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L160" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Pull Up</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-15</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Pull Up - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:35</v>
+        <v>3:32</v>
       </c>
       <c r="H161" t="str">
-        <v>Collect 200</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L161" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Ranjha</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-15</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Ranjha - Single</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:04</v>
+        <v>3:08</v>
       </c>
       <c r="H162" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L162" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>zombies in love</v>
+        <v>Real Slow</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-15</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>zombies in love - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G163" t="str">
-        <v>2:53</v>
+        <v>3:22</v>
       </c>
       <c r="H163" t="str">
-        <v>paris jackson</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L163" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Days Of Us</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-15</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Full Circle</v>
+        <v>As Is</v>
       </c>
       <c r="G164" t="str">
-        <v>4:39</v>
+        <v>2:42</v>
       </c>
       <c r="H164" t="str">
-        <v>Tom Misch</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L164" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Life Of A Man</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-15</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>American Stories</v>
       </c>
       <c r="G165" t="str">
-        <v>3:15</v>
+        <v>3:31</v>
       </c>
       <c r="H165" t="str">
-        <v>1Ski OG</v>
+        <v>Rostam</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L165" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Ya No</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-15</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Ya No - Single</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G166" t="str">
-        <v>3:40</v>
+        <v>3:29</v>
       </c>
       <c r="H166" t="str">
-        <v>Marca MP</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L166" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Do You Really Love Her</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-15</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G167" t="str">
-        <v>3:48</v>
+        <v>3:04</v>
       </c>
       <c r="H167" t="str">
-        <v>Spacey Jane</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L167" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Relieve You</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-15</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Relieve You - Single</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:19</v>
+        <v>3:37</v>
       </c>
       <c r="H168" t="str">
-        <v>4Fargo</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L168" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Safety</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-15</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Safety - Single</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:18</v>
+        <v>3:03</v>
       </c>
       <c r="H169" t="str">
-        <v>Lekan</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L169" t="str">
-        <v>Safety - Lekan</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Starlet</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-15</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>LK99</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G170" t="str">
-        <v>2:56</v>
+        <v>4:05</v>
       </c>
       <c r="H170" t="str">
-        <v>Leven Kali</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L170" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Physical</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-15</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Physical - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G171" t="str">
-        <v>3:52</v>
+        <v>3:34</v>
       </c>
       <c r="H171" t="str">
-        <v>Jacquees</v>
+        <v>Melanie C</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L171" t="str">
-        <v>Physical - Jacquees</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Pull Up</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-15</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:29</v>
+        <v>2:35</v>
       </c>
       <c r="H172" t="str">
-        <v>Casper Sage</v>
+        <v>Collect 200</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L172" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Regalito</v>
+        <v>Ranjha</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-15</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>TRESCENDER</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:41</v>
+        <v>3:04</v>
       </c>
       <c r="H173" t="str">
-        <v>Piso 21</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L173" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Cruel Streak</v>
+        <v>zombies in love</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-15</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>A Pound of Feathers</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>4:09</v>
+        <v>2:53</v>
       </c>
       <c r="H174" t="str">
-        <v>The Black Crowes</v>
+        <v>paris jackson</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L174" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Die Young</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-15</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Little Wide Open</v>
+        <v>Full Circle</v>
       </c>
       <c r="G175" t="str">
-        <v>3:52</v>
+        <v>4:39</v>
       </c>
       <c r="H175" t="str">
-        <v>Kevin Morby</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L175" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Island Girl</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-15</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Island Girl - Single</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:27</v>
+        <v>3:15</v>
       </c>
       <c r="H176" t="str">
-        <v>Pia Mia</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L176" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Ya No</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-15</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:20</v>
+        <v>3:40</v>
       </c>
       <c r="H177" t="str">
-        <v>Claudia Valentina</v>
+        <v>Marca MP</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L177" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-15</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:22</v>
+        <v>3:48</v>
       </c>
       <c r="H178" t="str">
-        <v>Shaggy</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L178" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Tommy’s Song</v>
+        <v>Relieve You</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-15</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Lovers - Single</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:44</v>
+        <v>2:19</v>
       </c>
       <c r="H179" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>4Fargo</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L179" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Rainbows</v>
+        <v>Safety</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-15</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Rainbows - Single</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:25</v>
+        <v>3:18</v>
       </c>
       <c r="H180" t="str">
-        <v>Allison Russell</v>
+        <v>Lekan</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L180" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>butterflies</v>
+        <v>Starlet</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-15</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Bloom Again - EP</v>
+        <v>LK99</v>
       </c>
       <c r="G181" t="str">
-        <v>2:48</v>
+        <v>2:56</v>
       </c>
       <c r="H181" t="str">
-        <v>runo plum</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L181" t="str">
-        <v>butterflies - runo plum</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You're Right</v>
+        <v>Physical</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-15</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>You're Right - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:00</v>
+        <v>3:52</v>
       </c>
       <c r="H182" t="str">
-        <v>Emma Harner</v>
+        <v>Jacquees</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L182" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Bible Belt</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-15</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Bible Belt - Single</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:34</v>
+        <v>4:29</v>
       </c>
       <c r="H183" t="str">
-        <v>Baby Bugs</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L183" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Daze</v>
+        <v>Regalito</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-15</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Daze - Single</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G184" t="str">
-        <v>3:22</v>
+        <v>2:41</v>
       </c>
       <c r="H184" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Piso 21</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L184" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Passionfruit</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-15</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Passionfruit - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G185" t="str">
-        <v>3:57</v>
+        <v>4:09</v>
       </c>
       <c r="H185" t="str">
-        <v>Anish Kumar</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L185" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Madan</v>
+        <v>Die Young</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-15</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Madan - Single</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G186" t="str">
-        <v>2:56</v>
+        <v>3:52</v>
       </c>
       <c r="H186" t="str">
-        <v>Jonas Blue</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L186" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Bad Bitch</v>
+        <v>Island Girl</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-15</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:28</v>
+        <v>3:27</v>
       </c>
       <c r="H187" t="str">
-        <v>41</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L187" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Shame</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-15</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:36</v>
+        <v>2:20</v>
       </c>
       <c r="H188" t="str">
-        <v>Sunday (1994)</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L188" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>teach you to love me</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-15</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>teach you to love me - Single</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:09</v>
+        <v>3:22</v>
       </c>
       <c r="H189" t="str">
-        <v>Hailey Picardi</v>
+        <v>Shaggy</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L189" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>The Fix</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-15</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>The Fix - Single</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:42</v>
+        <v>3:44</v>
       </c>
       <c r="H190" t="str">
-        <v>Baby J</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L190" t="str">
-        <v>The Fix - Baby J</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Hanging on Hope</v>
+        <v>Rainbows</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-15</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:43</v>
+        <v>3:25</v>
       </c>
       <c r="H191" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L191" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>I Know What to Say Now</v>
+        <v>butterflies</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-15</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G192" t="str">
-        <v>3:18</v>
+        <v>2:48</v>
       </c>
       <c r="H192" t="str">
-        <v>Active Child</v>
+        <v>runo plum</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L192" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Feel Something</v>
+        <v>You're Right</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-15</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Feel Something - Single</v>
+        <v>You're Right - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:09</v>
+        <v>3:00</v>
       </c>
       <c r="H193" t="str">
-        <v>Baby Queen</v>
+        <v>Emma Harner</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
       </c>
       <c r="L193" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>You're Right - Emma Harner</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>You Or Me</v>
+        <v>Bible Belt</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-15</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Bible Belt - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>5:28</v>
+        <v>3:34</v>
       </c>
       <c r="H194" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Baby Bugs</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
       </c>
       <c r="L194" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>Bible Belt - Baby Bugs</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Mortercheyn</v>
+        <v>Daze</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-15</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Coronach</v>
+        <v>Daze - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>4:18</v>
+        <v>3:22</v>
       </c>
       <c r="H195" t="str">
-        <v>Hellripper</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
       </c>
       <c r="L195" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>Daze - Olympia Vitalis</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Rip The God</v>
+        <v>Passionfruit</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-15</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Passionfruit - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>5:20</v>
+        <v>3:57</v>
       </c>
       <c r="H196" t="str">
-        <v>Melvins</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
       </c>
       <c r="L196" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Passionfruit - Anish Kumar</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Who We Are</v>
+        <v>Madan</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-15</v>
@@ -7861,68 +7861,486 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Who We Are - Single</v>
+        <v>Madan - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:10</v>
+        <v>2:56</v>
       </c>
       <c r="H197" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Jonas Blue</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
       </c>
       <c r="L197" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
+        <v>Madan - Jonas Blue</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
+        <v>Bad Bitch</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>Bad Bitch - Single</v>
+      </c>
+      <c r="G198" t="str">
+        <v>2:28</v>
+      </c>
+      <c r="H198" t="str">
+        <v>41</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+      </c>
+      <c r="L198" t="str">
+        <v>Bad Bitch - 41</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Shame</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Devotion [Deluxe]</v>
+      </c>
+      <c r="G199" t="str">
+        <v>3:36</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Sunday (1994)</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Shame - Sunday (1994)</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>teach you to love me</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>teach you to love me - Single</v>
+      </c>
+      <c r="G200" t="str">
+        <v>3:09</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Hailey Picardi</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+      </c>
+      <c r="L200" t="str">
+        <v>teach you to love me - Hailey Picardi</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>The Fix</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>The Fix - Single</v>
+      </c>
+      <c r="G201" t="str">
+        <v>2:42</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Baby J</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+      </c>
+      <c r="L201" t="str">
+        <v>The Fix - Baby J</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>Hanging on Hope</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Hanging on Hope - Single</v>
+      </c>
+      <c r="G202" t="str">
+        <v>3:43</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Buffalo Traffic Jam</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>I Know What to Say Now</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>I Know What to Say Now - Single</v>
+      </c>
+      <c r="G203" t="str">
+        <v>3:18</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Active Child</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+      </c>
+      <c r="L203" t="str">
+        <v>I Know What to Say Now - Active Child</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Feel Something</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>Feel Something - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>3:09</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Baby Queen</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Feel Something - Baby Queen</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>You Or Me</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>Good God / Baad Man</v>
+      </c>
+      <c r="G205" t="str">
+        <v>5:28</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Corrosion of Conformity</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+      </c>
+      <c r="L205" t="str">
+        <v>You Or Me - Corrosion of Conformity</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Mortercheyn</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>Coronach</v>
+      </c>
+      <c r="G206" t="str">
+        <v>4:18</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Hellripper</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Mortercheyn - Hellripper</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Rip The God</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>Savage Imperial Death March</v>
+      </c>
+      <c r="G207" t="str">
+        <v>5:20</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Melvins</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+      </c>
+      <c r="L207" t="str">
+        <v>Rip The God - Melvins</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Who We Are</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>Who We Are - Single</v>
+      </c>
+      <c r="G208" t="str">
+        <v>2:10</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Kaleena Zanders</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+      </c>
+      <c r="L208" t="str">
+        <v>Who We Are - Kaleena Zanders</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
         <v>Reels in 360</v>
       </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
-      <c r="D198" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
+      <c r="D209" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
         <v>Dying Is The Internet</v>
       </c>
-      <c r="G198" t="str">
+      <c r="G209" t="str">
         <v>4:37</v>
       </c>
-      <c r="H198" t="str">
+      <c r="H209" t="str">
         <v>Simo Cell</v>
       </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
         <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
-      <c r="K198" t="str">
+      <c r="K209" t="str">
         <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
-      <c r="L198" t="str">
+      <c r="L209" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L209"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week03/titles.xlsx
+++ b/data/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L209"/>
+  <dimension ref="A1:L198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,31 +436,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שרית חדד - Mamma Mia</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-15</v>
+        <v>4 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410015&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>4:09</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Mei Semones</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,36 +469,36 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שרית חדד - Mamma Mia</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שראל סופר - מדויק ולא בערך</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-15</v>
+        <v>4 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410014&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>2:08</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,36 +507,36 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שראל סופר - מדויק ולא בערך</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שמוליק סוכות - אבא טוב</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-15</v>
+        <v>5 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410013&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>2:57</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Natalie Jane</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,36 +545,36 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שמוליק סוכות - אבא טוב</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שירה ואן ופרן - ייפול עליי</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-15</v>
+        <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410012&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>3:13</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,36 +583,36 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שירה ואן ופרן - ייפול עליי</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>רון דבני - מה אני אגיד לך</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-15</v>
+        <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410011&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>4:12</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>David Gilmour</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,36 +621,36 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>רון דבני - מה אני אגיד לך</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>נטע ברזילי - גם זה יגיע</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-15</v>
+        <v>5 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410010&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>3:57</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Far Caspian</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,36 +659,36 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>נטע ברזילי - גם זה יגיע</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>מאי כהן - אנשים</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-15</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410009&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>3:34</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Celine Dion</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,36 +697,36 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>מאי כהן - אנשים</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>איציק סנדרוי - תנו לי אוויר</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-15</v>
+        <v>9 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410008&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>3:48</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Harry Styles</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,36 +735,36 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>איציק סנדרוי - תנו לי אוויר</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אהרון סיטבון - ניגון יהודי</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-15</v>
+        <v>9 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410007&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>4:58</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,36 +773,36 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אהרון סיטבון - ניגון יהודי</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אבישי אזיקרי - לימונדה</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-15</v>
+        <v>9 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410006&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>2:33</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Ellise</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,36 +811,36 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אבישי אזיקרי - לימונדה</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אבי אילסון - בזכותם</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-03-15</v>
+        <v>9 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410005&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>5:01</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>אבי אילסון - בזכותם</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:09</v>
+        <v>4:56</v>
       </c>
       <c r="H13" t="str">
-        <v>Mei Semones</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:08</v>
+        <v>2:54</v>
       </c>
       <c r="H14" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,33 +925,33 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:57</v>
+        <v>2:46</v>
       </c>
       <c r="H15" t="str">
-        <v>Natalie Jane</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,33 +963,33 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H16" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>R3HAB</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,33 +1001,33 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:12</v>
+        <v>3:21</v>
       </c>
       <c r="H17" t="str">
-        <v>David Gilmour</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:57</v>
+        <v>3:16</v>
       </c>
       <c r="H18" t="str">
-        <v>Far Caspian</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:34</v>
+        <v>2:41</v>
       </c>
       <c r="H19" t="str">
-        <v>Celine Dion</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B20" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1138,10 +1138,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:48</v>
+        <v>2:29</v>
       </c>
       <c r="H20" t="str">
-        <v>Harry Styles</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B21" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1176,10 +1176,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:58</v>
+        <v>2:43</v>
       </c>
       <c r="H21" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B22" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1214,10 +1214,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:33</v>
+        <v>3:46</v>
       </c>
       <c r="H22" t="str">
-        <v>Ellise</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1252,10 +1252,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>5:01</v>
+        <v>4:01</v>
       </c>
       <c r="H23" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B24" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1290,10 +1290,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:56</v>
+        <v>3:23</v>
       </c>
       <c r="H24" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B25" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1328,10 +1328,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:54</v>
+        <v>3:39</v>
       </c>
       <c r="H25" t="str">
-        <v>Bebe Rexha</v>
+        <v>almost monday</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,21 +1343,21 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1366,10 +1366,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:46</v>
+        <v>3:04</v>
       </c>
       <c r="H26" t="str">
-        <v>NathanEvanss</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1404,10 +1404,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:56</v>
+        <v>3:25</v>
       </c>
       <c r="H27" t="str">
-        <v>R3HAB</v>
+        <v>vaultboy</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1442,10 +1442,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:21</v>
+        <v>3:49</v>
       </c>
       <c r="H28" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>The Warning</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,21 +1457,21 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B29" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1480,10 +1480,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:16</v>
+        <v>2:14</v>
       </c>
       <c r="H29" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>aron!</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:41</v>
+        <v>2:43</v>
       </c>
       <c r="H30" t="str">
-        <v>Johnny Orlando</v>
+        <v>Bazzi</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B31" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:29</v>
+        <v>4:43</v>
       </c>
       <c r="H31" t="str">
-        <v>Russell Dickerson</v>
+        <v>Sting</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:43</v>
+        <v>2:44</v>
       </c>
       <c r="H32" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:46</v>
+        <v>4:37</v>
       </c>
       <c r="H33" t="str">
-        <v>Matt Hansen</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B34" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:01</v>
+        <v>4:52</v>
       </c>
       <c r="H34" t="str">
-        <v>Mike Posner</v>
+        <v>Cannons</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B35" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:23</v>
+        <v>2:13</v>
       </c>
       <c r="H35" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:39</v>
+        <v>3:19</v>
       </c>
       <c r="H36" t="str">
-        <v>almost monday</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B37" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:04</v>
+        <v>2:31</v>
       </c>
       <c r="H37" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:25</v>
+        <v>2:43</v>
       </c>
       <c r="H38" t="str">
-        <v>vaultboy</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:49</v>
+        <v>3:10</v>
       </c>
       <c r="H39" t="str">
-        <v>The Warning</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>2:14</v>
+        <v>3:55</v>
       </c>
       <c r="H40" t="str">
-        <v>aron!</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:43</v>
+        <v>3:52</v>
       </c>
       <c r="H41" t="str">
-        <v>Bazzi</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B42" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:43</v>
+        <v>2:53</v>
       </c>
       <c r="H42" t="str">
-        <v>Sting</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:44</v>
+        <v>4:30</v>
       </c>
       <c r="H43" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie J</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:37</v>
+        <v>5:18</v>
       </c>
       <c r="H44" t="str">
-        <v>Jessie Ware</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B45" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G45" t="str">
-        <v>4:52</v>
+        <v>7:20</v>
       </c>
       <c r="H45" t="str">
-        <v>Cannons</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B46" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:13</v>
+        <v>3:01</v>
       </c>
       <c r="H46" t="str">
-        <v>Kim Petras</v>
+        <v>BRITs</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B47" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:19</v>
+        <v>3:31</v>
       </c>
       <c r="H47" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B48" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:31</v>
+        <v>3:00</v>
       </c>
       <c r="H48" t="str">
-        <v>Kiana Ledé</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B49" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:43</v>
+        <v>3:11</v>
       </c>
       <c r="H49" t="str">
-        <v>Ringo Starr</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:10</v>
+        <v>3:32</v>
       </c>
       <c r="H50" t="str">
-        <v>Maya Hawke</v>
+        <v>Lauv</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:55</v>
+        <v>5:03</v>
       </c>
       <c r="H51" t="str">
-        <v>Armin van Buuren</v>
+        <v>RAYE</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:52</v>
+        <v>4:50</v>
       </c>
       <c r="H52" t="str">
-        <v>Demi Lovato</v>
+        <v>Armik</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:53</v>
+        <v>4:53</v>
       </c>
       <c r="H53" t="str">
-        <v>Peter Gabriel</v>
+        <v>Scorpions</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,21 +2407,21 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2430,10 +2430,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:30</v>
+        <v>3:04</v>
       </c>
       <c r="H54" t="str">
-        <v>Jessie J</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,21 +2445,21 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>5:18</v>
+        <v>4:32</v>
       </c>
       <c r="H55" t="str">
-        <v>Harry Styles</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,21 +2483,21 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>7:20</v>
+        <v>3:47</v>
       </c>
       <c r="H56" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,21 +2521,21 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:01</v>
+        <v>3:40</v>
       </c>
       <c r="H57" t="str">
-        <v>BRITs</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,21 +2559,21 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:31</v>
+        <v>4:05</v>
       </c>
       <c r="H58" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>HAUSER</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,21 +2597,21 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:00</v>
+        <v>2:59</v>
       </c>
       <c r="H59" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Queen Official</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,21 +2635,21 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:11</v>
+        <v>3:55</v>
       </c>
       <c r="H60" t="str">
-        <v>The Kiffness</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,21 +2673,21 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:32</v>
+        <v>5:12</v>
       </c>
       <c r="H61" t="str">
-        <v>Lauv</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,21 +2711,21 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>5:03</v>
+        <v>3:47</v>
       </c>
       <c r="H62" t="str">
-        <v>RAYE</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,21 +2749,21 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:50</v>
+        <v>3:18</v>
       </c>
       <c r="H63" t="str">
-        <v>Armik</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,21 +2787,21 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:53</v>
+        <v>3:50</v>
       </c>
       <c r="H64" t="str">
-        <v>Scorpions</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,21 +2825,21 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:04</v>
+        <v>3:24</v>
       </c>
       <c r="H65" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>MyKey</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,21 +2863,21 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>4:32</v>
+        <v>2:36</v>
       </c>
       <c r="H66" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Max McNown</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,21 +2901,21 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:47</v>
+        <v>3:34</v>
       </c>
       <c r="H67" t="str">
-        <v>Girl Tones</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,21 +2939,21 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:40</v>
+        <v>4:03</v>
       </c>
       <c r="H68" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>ERNEST</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,21 +2977,21 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:05</v>
+        <v>3:31</v>
       </c>
       <c r="H69" t="str">
-        <v>HAUSER</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,21 +3015,21 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:59</v>
+        <v>3:22</v>
       </c>
       <c r="H70" t="str">
-        <v>Queen Official</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,21 +3053,21 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:55</v>
+        <v>5:49</v>
       </c>
       <c r="H71" t="str">
-        <v>Tenille Townes</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,21 +3091,21 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>5:12</v>
+        <v>3:47</v>
       </c>
       <c r="H72" t="str">
-        <v>Self Esteem</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,21 +3129,21 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:47</v>
+        <v>2:20</v>
       </c>
       <c r="H73" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,21 +3167,21 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:18</v>
+        <v>4:18</v>
       </c>
       <c r="H74" t="str">
-        <v>Em Beihold</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,21 +3205,21 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:50</v>
+        <v>2:39</v>
       </c>
       <c r="H75" t="str">
-        <v>Michael Bublé</v>
+        <v>kenzie</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,21 +3243,21 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:24</v>
+        <v>3:52</v>
       </c>
       <c r="H76" t="str">
-        <v>MyKey</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,21 +3281,21 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:36</v>
+        <v>4:01</v>
       </c>
       <c r="H77" t="str">
-        <v>Max McNown</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,21 +3319,21 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:34</v>
+        <v>2:54</v>
       </c>
       <c r="H78" t="str">
-        <v>Megan Moroney</v>
+        <v>CHESCA</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,21 +3357,21 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3383,7 +3383,7 @@
         <v>4:03</v>
       </c>
       <c r="H79" t="str">
-        <v>ERNEST</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,21 +3395,21 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:31</v>
+        <v>4:50</v>
       </c>
       <c r="H80" t="str">
-        <v>Bruno Mars</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,21 +3433,21 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:22</v>
+        <v>3:06</v>
       </c>
       <c r="H81" t="str">
-        <v>BLACKPINK</v>
+        <v>Y2K</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,21 +3471,21 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>5:49</v>
+        <v>2:43</v>
       </c>
       <c r="H82" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,21 +3509,21 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:47</v>
+        <v>6:21</v>
       </c>
       <c r="H83" t="str">
-        <v>Nessa Barrett</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,21 +3547,21 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:20</v>
+        <v>2:46</v>
       </c>
       <c r="H84" t="str">
-        <v>Towa Bird</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,21 +3585,21 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:18</v>
+        <v>2:42</v>
       </c>
       <c r="H85" t="str">
-        <v>Ty Myers</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,21 +3623,21 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:39</v>
+        <v>3:04</v>
       </c>
       <c r="H86" t="str">
-        <v>kenzie</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,21 +3661,21 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:52</v>
+        <v>2:59</v>
       </c>
       <c r="H87" t="str">
-        <v>Leanna Crawford</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,21 +3699,21 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:01</v>
+        <v>2:22</v>
       </c>
       <c r="H88" t="str">
-        <v>Bryan Adams</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,21 +3737,21 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:54</v>
+        <v>3:53</v>
       </c>
       <c r="H89" t="str">
-        <v>CHESCA</v>
+        <v>Roxette</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,21 +3775,21 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:03</v>
+        <v>2:28</v>
       </c>
       <c r="H90" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Marcin</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,21 +3813,21 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:50</v>
+        <v>2:47</v>
       </c>
       <c r="H91" t="str">
-        <v>earMUSIC</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,21 +3851,21 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:06</v>
+        <v>3:40</v>
       </c>
       <c r="H92" t="str">
-        <v>Y2K</v>
+        <v>Laufey</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,21 +3889,21 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:43</v>
+        <v>2:49</v>
       </c>
       <c r="H93" t="str">
-        <v>Lainey Wilson</v>
+        <v>Ava Max</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,21 +3927,21 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>6:21</v>
+        <v>4:49</v>
       </c>
       <c r="H94" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>U2</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,21 +3965,21 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:46</v>
+        <v>3:35</v>
       </c>
       <c r="H95" t="str">
-        <v>Bryan Ferry</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,21 +4003,21 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:42</v>
+        <v>2:59</v>
       </c>
       <c r="H96" t="str">
-        <v>Saint Harison</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,21 +4041,21 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:04</v>
+        <v>4:38</v>
       </c>
       <c r="H97" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,21 +4079,21 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:59</v>
+        <v>3:46</v>
       </c>
       <c r="H98" t="str">
-        <v>Catie Turner</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,21 +4117,21 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:22</v>
+        <v>3:08</v>
       </c>
       <c r="H99" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,21 +4155,21 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:53</v>
+        <v>5:32</v>
       </c>
       <c r="H100" t="str">
-        <v>Roxette</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,21 +4193,21 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:28</v>
+        <v>4:39</v>
       </c>
       <c r="H101" t="str">
-        <v>Marcin</v>
+        <v>georgemichael</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,4116 +4231,3698 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Porch Light</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G102" t="str">
-        <v>2:47</v>
+        <v>4:22</v>
       </c>
       <c r="H102" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
       </c>
       <c r="L102" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Porch Light - Noah Kahan</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Dry Spell</v>
       </c>
       <c r="B103" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2 weeks ago</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G103" t="str">
-        <v>3:40</v>
+        <v>3:17</v>
       </c>
       <c r="H103" t="str">
-        <v>Laufey</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
       </c>
       <c r="L103" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Dry Spell - Kacey Musgraves</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>The Visitor</v>
       </c>
       <c r="B104" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2 weeks ago</v>
+        <v>The Visitor - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>2:49</v>
+        <v>3:48</v>
       </c>
       <c r="H104" t="str">
-        <v>Ava Max</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
       </c>
       <c r="L104" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>I Ain't No Cowboy</v>
       </c>
       <c r="B105" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>2 weeks ago</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G105" t="str">
-        <v>4:49</v>
+        <v>3:13</v>
       </c>
       <c r="H105" t="str">
-        <v>U2</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
       </c>
       <c r="L105" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>I Ain't No Cowboy - Luke Combs</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Can't Sit Still</v>
       </c>
       <c r="B106" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>2 weeks ago</v>
+        <v>Can't Sit Still - Single</v>
       </c>
       <c r="G106" t="str">
         <v>3:35</v>
       </c>
       <c r="H106" t="str">
-        <v>Taylor Swift</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
       </c>
       <c r="L106" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Can't Sit Still - Lainey Wilson</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>All I Did Was Dream of You (feat. The Marías)</v>
       </c>
       <c r="B107" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>2 weeks ago</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:59</v>
+        <v>3:43</v>
       </c>
       <c r="H107" t="str">
-        <v>Kiana Ledé</v>
+        <v>beabadoobee</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
       </c>
       <c r="L107" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Blow My Mind</v>
       </c>
       <c r="B108" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>2 weeks ago</v>
+        <v>Sexistential</v>
       </c>
       <c r="G108" t="str">
-        <v>4:38</v>
+        <v>2:57</v>
       </c>
       <c r="H108" t="str">
-        <v>Jessie Ware</v>
+        <v>Robyn</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
       </c>
       <c r="L108" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Blow My Mind - Robyn</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>SATA</v>
       </c>
       <c r="B109" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>2 weeks ago</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G109" t="str">
-        <v>3:46</v>
+        <v>3:02</v>
       </c>
       <c r="H109" t="str">
-        <v>Madison Beer</v>
+        <v>John Summit</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/sata/1874015470</v>
       </c>
       <c r="L109" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>SATA - John Summit</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Una Aventura</v>
       </c>
       <c r="B110" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>2 weeks ago</v>
+        <v>Una Aventura - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:08</v>
+        <v>3:00</v>
       </c>
       <c r="H110" t="str">
-        <v>Sean Stemaly</v>
+        <v>Ozuna</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
       </c>
       <c r="L110" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Una Aventura - Ozuna</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Home (feat. Hikaru Utada)</v>
       </c>
       <c r="B111" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>2 weeks ago</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G111" t="str">
-        <v>5:32</v>
+        <v>3:44</v>
       </c>
       <c r="H111" t="str">
-        <v>earMUSIC</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
       </c>
       <c r="L111" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>dirty wedding dress</v>
       </c>
       <c r="B112" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>2 weeks ago</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G112" t="str">
-        <v>4:39</v>
+        <v>4:49</v>
       </c>
       <c r="H112" t="str">
-        <v>georgemichael</v>
+        <v>Bleachers</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
       </c>
       <c r="L112" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>dirty wedding dress - Bleachers</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Porch Light</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>The Great Divide</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G113" t="str">
-        <v>4:22</v>
+        <v>3:07</v>
       </c>
       <c r="H113" t="str">
-        <v>Noah Kahan</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L113" t="str">
-        <v>Porch Light - Noah Kahan</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Dry Spell</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Middle of Nowhere</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:17</v>
+        <v>3:13</v>
       </c>
       <c r="H114" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L114" t="str">
-        <v>Dry Spell - Kacey Musgraves</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>The Visitor</v>
+        <v>Trade Places</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>The Visitor - Single</v>
+        <v>Monica</v>
       </c>
       <c r="G115" t="str">
-        <v>3:48</v>
+        <v>3:02</v>
       </c>
       <c r="H115" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L115" t="str">
-        <v>The Visitor - SIENNA SPIRO</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>I Ain't No Cowboy</v>
+        <v>Motion Party</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>The Way I Am</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:13</v>
+        <v>1:35</v>
       </c>
       <c r="H116" t="str">
-        <v>Luke Combs</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L116" t="str">
-        <v>I Ain't No Cowboy - Luke Combs</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Can't Sit Still</v>
+        <v>Woman</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Can't Sit Still - Single</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:35</v>
+        <v>2:46</v>
       </c>
       <c r="H117" t="str">
-        <v>Lainey Wilson</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L117" t="str">
-        <v>Can't Sit Still - Lainey Wilson</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías)</v>
+        <v>Sunburn</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:43</v>
+        <v>3:05</v>
       </c>
       <c r="H118" t="str">
-        <v>beabadoobee</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L118" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Blow My Mind</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Sexistential</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G119" t="str">
-        <v>2:57</v>
+        <v>2:54</v>
       </c>
       <c r="H119" t="str">
-        <v>Robyn</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L119" t="str">
-        <v>Blow My Mind - Robyn</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>SATA</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/sata/1874015489</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:02</v>
+        <v>2:15</v>
       </c>
       <c r="H120" t="str">
-        <v>John Summit</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/sata/1874015470</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L120" t="str">
-        <v>SATA - John Summit</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Una Aventura</v>
+        <v>Cruel World</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Una Aventura - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G121" t="str">
-        <v>3:00</v>
+        <v>3:26</v>
       </c>
       <c r="H121" t="str">
-        <v>Ozuna</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L121" t="str">
-        <v>Una Aventura - Ozuna</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>Star</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Star - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:44</v>
+        <v>3:25</v>
       </c>
       <c r="H122" t="str">
-        <v>Charlie Puth</v>
+        <v>Iceage</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L122" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>dirty wedding dress</v>
+        <v>Get Go</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G123" t="str">
-        <v>4:49</v>
+        <v>3:22</v>
       </c>
       <c r="H123" t="str">
-        <v>Bleachers</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L123" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Age of the Ram</v>
+        <v>Distracted</v>
       </c>
       <c r="G124" t="str">
-        <v>3:07</v>
+        <v>3:14</v>
       </c>
       <c r="H124" t="str">
-        <v>Charley Crockett</v>
+        <v>Thundercat</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L124" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Club Song</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:13</v>
+        <v>2:27</v>
       </c>
       <c r="H125" t="str">
-        <v>Grupo Frontera</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L125" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Trade Places</v>
+        <v>Better Man</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Monica</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:02</v>
+        <v>2:53</v>
       </c>
       <c r="H126" t="str">
-        <v>Jack Harlow</v>
+        <v>jxdn</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L126" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Motion Party</v>
+        <v>sabotage</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Motion Party - Single</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>1:35</v>
+        <v>2:58</v>
       </c>
       <c r="H127" t="str">
-        <v>Bossman Dlow</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L127" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Woman</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Woman - Single</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H128" t="str">
-        <v>Kane Brown</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L128" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Sunburn</v>
+        <v>Naked</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Sunburn - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:05</v>
+        <v>3:39</v>
       </c>
       <c r="H129" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L129" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Que Te Costó</v>
+        <v>Catharina</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Metamorfosis</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:54</v>
+        <v>3:27</v>
       </c>
       <c r="H130" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L130" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>oooshxt!</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>oooshxt! - Single</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:15</v>
+        <v>3:00</v>
       </c>
       <c r="H131" t="str">
-        <v>Samara Cyn</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L131" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Cruel World</v>
+        <v>Trying Times</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Cruel World</v>
+        <v>Trying Times</v>
       </c>
       <c r="G132" t="str">
-        <v>3:26</v>
+        <v>4:33</v>
       </c>
       <c r="H132" t="str">
-        <v>Holly Humberstone</v>
+        <v>James Blake</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L132" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Star</v>
+        <v>595</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Star - Single</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G133" t="str">
-        <v>3:25</v>
+        <v>2:29</v>
       </c>
       <c r="H133" t="str">
-        <v>Iceage</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L133" t="str">
-        <v>Star - Iceage</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Get Go</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Soft 2</v>
       </c>
       <c r="G134" t="str">
-        <v>3:22</v>
+        <v>3:50</v>
       </c>
       <c r="H134" t="str">
-        <v>Arlo Parks</v>
+        <v>LANY</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L134" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ThunderWave</v>
+        <v>CALL ME</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Distracted</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:14</v>
+        <v>2:10</v>
       </c>
       <c r="H135" t="str">
-        <v>Thundercat</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L135" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Club Song</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Club Song - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G136" t="str">
-        <v>2:27</v>
+        <v>2:00</v>
       </c>
       <c r="H136" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>Nasty C</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L136" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Better Man</v>
+        <v>BOBA</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Better Man - Single</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:53</v>
+        <v>3:00</v>
       </c>
       <c r="H137" t="str">
-        <v>jxdn</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L137" t="str">
-        <v>Better Man - jxdn</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>sabotage</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>sabotage - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G138" t="str">
-        <v>2:58</v>
+        <v>2:38</v>
       </c>
       <c r="H138" t="str">
-        <v>Natalie Jane</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L138" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:56</v>
+        <v>2:06</v>
       </c>
       <c r="H139" t="str">
-        <v>WHATMORE</v>
+        <v>Shenseea</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L139" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Naked</v>
+        <v>Just Believe</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Naked - Single</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:39</v>
+        <v>2:41</v>
       </c>
       <c r="H140" t="str">
-        <v>Kenya Grace</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L140" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Catharina</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Catharina - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G141" t="str">
-        <v>3:27</v>
+        <v>2:57</v>
       </c>
       <c r="H141" t="str">
-        <v>Martin Garrix</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L141" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:00</v>
+        <v>3:09</v>
       </c>
       <c r="H142" t="str">
-        <v>Chase &amp; Status</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L142" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Trying Times</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Trying Times</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G143" t="str">
-        <v>4:33</v>
+        <v>4:06</v>
       </c>
       <c r="H143" t="str">
-        <v>James Blake</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L143" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>595</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Dear God</v>
       </c>
       <c r="G144" t="str">
-        <v>2:29</v>
+        <v>3:33</v>
       </c>
       <c r="H144" t="str">
-        <v>Violet Grohl</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L144" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>Breathe</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Soft 2</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:50</v>
+        <v>2:56</v>
       </c>
       <c r="H145" t="str">
-        <v>LANY</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L145" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>CALL ME</v>
+        <v>Minty</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>CALL ME - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G146" t="str">
-        <v>2:10</v>
+        <v>1:47</v>
       </c>
       <c r="H146" t="str">
-        <v>ALTÉGO</v>
+        <v>MIKE</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L146" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Mi Amor</v>
+        <v>Earth</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Free (Deluxe)</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G147" t="str">
-        <v>2:00</v>
+        <v>1:37</v>
       </c>
       <c r="H147" t="str">
-        <v>Nasty C</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L147" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>BOBA</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>BOBA - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G148" t="str">
-        <v>3:00</v>
+        <v>3:42</v>
       </c>
       <c r="H148" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L148" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Video Shoot</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Skeletor</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:38</v>
+        <v>4:32</v>
       </c>
       <c r="H149" t="str">
-        <v>Chief Keef</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L149" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:06</v>
+        <v>3:32</v>
       </c>
       <c r="H150" t="str">
-        <v>Shenseea</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L150" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Just Believe</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Just Believe - Single</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:41</v>
+        <v>3:08</v>
       </c>
       <c r="H151" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L151" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Knife In The Heart</v>
+        <v>Real Slow</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>The Afterparty</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G152" t="str">
-        <v>2:57</v>
+        <v>3:22</v>
       </c>
       <c r="H152" t="str">
-        <v>Lykke Li</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L152" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>The Way We Touch</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>As Is</v>
       </c>
       <c r="G153" t="str">
-        <v>3:09</v>
+        <v>2:42</v>
       </c>
       <c r="H153" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L153" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>DANGEROUS</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>American Stories</v>
       </c>
       <c r="G154" t="str">
-        <v>4:06</v>
+        <v>3:31</v>
       </c>
       <c r="H154" t="str">
-        <v>Magnolia Park</v>
+        <v>Rostam</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L154" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>When I Wake Up</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Dear God</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G155" t="str">
-        <v>3:33</v>
+        <v>3:29</v>
       </c>
       <c r="H155" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L155" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Breathe</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Breathe - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G156" t="str">
-        <v>2:56</v>
+        <v>3:04</v>
       </c>
       <c r="H156" t="str">
-        <v>Malcolm Todd</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L156" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Minty</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>1:47</v>
+        <v>3:37</v>
       </c>
       <c r="H157" t="str">
-        <v>MIKE</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L157" t="str">
-        <v>Minty - MIKE</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Earth</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>1:37</v>
+        <v>3:03</v>
       </c>
       <c r="H158" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L158" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Drink The Water</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G159" t="str">
-        <v>3:42</v>
+        <v>4:05</v>
       </c>
       <c r="H159" t="str">
-        <v>Jack Johnson</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L159" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G160" t="str">
-        <v>4:32</v>
+        <v>3:34</v>
       </c>
       <c r="H160" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Melanie C</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L160" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>Pull Up</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:32</v>
+        <v>2:35</v>
       </c>
       <c r="H161" t="str">
-        <v>Carly Pearce</v>
+        <v>Collect 200</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L161" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Muchacho Alegre</v>
+        <v>Ranjha</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:08</v>
+        <v>3:04</v>
       </c>
       <c r="H162" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L162" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Real Slow</v>
+        <v>zombies in love</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Work of Heart</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:22</v>
+        <v>2:53</v>
       </c>
       <c r="H163" t="str">
-        <v>Flatland Cavalry</v>
+        <v>paris jackson</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L163" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Mountain Girl</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>As Is</v>
+        <v>Full Circle</v>
       </c>
       <c r="G164" t="str">
-        <v>2:42</v>
+        <v>4:39</v>
       </c>
       <c r="H164" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L164" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Like a Spark</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>American Stories</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:31</v>
+        <v>3:15</v>
       </c>
       <c r="H165" t="str">
-        <v>Rostam</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L165" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cheesecake</v>
+        <v>Ya No</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:29</v>
+        <v>3:40</v>
       </c>
       <c r="H166" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Marca MP</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L166" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>KINDA HARD</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:04</v>
+        <v>3:48</v>
       </c>
       <c r="H167" t="str">
-        <v>Bilmuri</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L167" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Freakin’ Out</v>
+        <v>Relieve You</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:37</v>
+        <v>2:19</v>
       </c>
       <c r="H168" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>4Fargo</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L168" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Name in Vein</v>
+        <v>Safety</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Name in Vein - Single</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:03</v>
+        <v>3:18</v>
       </c>
       <c r="H169" t="str">
-        <v>VOILÀ</v>
+        <v>Lekan</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L169" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Starlet</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Into Oblivion</v>
+        <v>LK99</v>
       </c>
       <c r="G170" t="str">
-        <v>4:05</v>
+        <v>2:56</v>
       </c>
       <c r="H170" t="str">
-        <v>Lamb of God</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L170" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Undefeated Champion</v>
+        <v>Physical</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Sweat</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:34</v>
+        <v>3:52</v>
       </c>
       <c r="H171" t="str">
-        <v>Melanie C</v>
+        <v>Jacquees</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L171" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Pull Up</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Pull Up - Single</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:35</v>
+        <v>4:29</v>
       </c>
       <c r="H172" t="str">
-        <v>Collect 200</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L172" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Ranjha</v>
+        <v>Regalito</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Ranjha - Single</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G173" t="str">
-        <v>3:04</v>
+        <v>2:41</v>
       </c>
       <c r="H173" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>Piso 21</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L173" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>zombies in love</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>zombies in love - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G174" t="str">
-        <v>2:53</v>
+        <v>4:09</v>
       </c>
       <c r="H174" t="str">
-        <v>paris jackson</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L174" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Days Of Us</v>
+        <v>Die Young</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Full Circle</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G175" t="str">
-        <v>4:39</v>
+        <v>3:52</v>
       </c>
       <c r="H175" t="str">
-        <v>Tom Misch</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L175" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Life Of A Man</v>
+        <v>Island Girl</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:15</v>
+        <v>3:27</v>
       </c>
       <c r="H176" t="str">
-        <v>1Ski OG</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L176" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Ya No</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Ya No - Single</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:40</v>
+        <v>2:20</v>
       </c>
       <c r="H177" t="str">
-        <v>Marca MP</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L177" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:48</v>
+        <v>3:22</v>
       </c>
       <c r="H178" t="str">
-        <v>Spacey Jane</v>
+        <v>Shaggy</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L178" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Relieve You</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Relieve You - Single</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:19</v>
+        <v>3:44</v>
       </c>
       <c r="H179" t="str">
-        <v>4Fargo</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L179" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Safety</v>
+        <v>Rainbows</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Safety - Single</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:18</v>
+        <v>3:25</v>
       </c>
       <c r="H180" t="str">
-        <v>Lekan</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L180" t="str">
-        <v>Safety - Lekan</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Starlet</v>
+        <v>butterflies</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>LK99</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G181" t="str">
-        <v>2:56</v>
+        <v>2:48</v>
       </c>
       <c r="H181" t="str">
-        <v>Leven Kali</v>
+        <v>runo plum</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L181" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Physical</v>
+        <v>You're Right</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Physical - Single</v>
+        <v>You're Right - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:52</v>
+        <v>3:00</v>
       </c>
       <c r="H182" t="str">
-        <v>Jacquees</v>
+        <v>Emma Harner</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
       </c>
       <c r="L182" t="str">
-        <v>Physical - Jacquees</v>
+        <v>You're Right - Emma Harner</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Bible Belt</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>Bible Belt - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>4:29</v>
+        <v>3:34</v>
       </c>
       <c r="H183" t="str">
-        <v>Casper Sage</v>
+        <v>Baby Bugs</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
       </c>
       <c r="L183" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Bible Belt - Baby Bugs</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Regalito</v>
+        <v>Daze</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>TRESCENDER</v>
+        <v>Daze - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:41</v>
+        <v>3:22</v>
       </c>
       <c r="H184" t="str">
-        <v>Piso 21</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
       </c>
       <c r="L184" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>Daze - Olympia Vitalis</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Cruel Streak</v>
+        <v>Passionfruit</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Passionfruit - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>4:09</v>
+        <v>3:57</v>
       </c>
       <c r="H185" t="str">
-        <v>The Black Crowes</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
       </c>
       <c r="L185" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Passionfruit - Anish Kumar</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Die Young</v>
+        <v>Madan</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Little Wide Open</v>
+        <v>Madan - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:52</v>
+        <v>2:56</v>
       </c>
       <c r="H186" t="str">
-        <v>Kevin Morby</v>
+        <v>Jonas Blue</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
       </c>
       <c r="L186" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Madan - Jonas Blue</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Island Girl</v>
+        <v>Bad Bitch</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Island Girl - Single</v>
+        <v>Bad Bitch - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:27</v>
+        <v>2:28</v>
       </c>
       <c r="H187" t="str">
-        <v>Pia Mia</v>
+        <v>41</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
       </c>
       <c r="L187" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>Bad Bitch - 41</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Shame</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>Devotion [Deluxe]</v>
       </c>
       <c r="G188" t="str">
-        <v>2:20</v>
+        <v>3:36</v>
       </c>
       <c r="H188" t="str">
-        <v>Claudia Valentina</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
       </c>
       <c r="L188" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Shame - Sunday (1994)</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>teach you to love me</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>teach you to love me - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:22</v>
+        <v>3:09</v>
       </c>
       <c r="H189" t="str">
-        <v>Shaggy</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
       </c>
       <c r="L189" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>teach you to love me - Hailey Picardi</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Tommy’s Song</v>
+        <v>The Fix</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Lovers - Single</v>
+        <v>The Fix - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:44</v>
+        <v>2:42</v>
       </c>
       <c r="H190" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Baby J</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
       </c>
       <c r="L190" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>The Fix - Baby J</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Rainbows</v>
+        <v>Hanging on Hope</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Rainbows - Single</v>
+        <v>Hanging on Hope - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:25</v>
+        <v>3:43</v>
       </c>
       <c r="H191" t="str">
-        <v>Allison Russell</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
       </c>
       <c r="L191" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>butterflies</v>
+        <v>I Know What to Say Now</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Bloom Again - EP</v>
+        <v>I Know What to Say Now - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:48</v>
+        <v>3:18</v>
       </c>
       <c r="H192" t="str">
-        <v>runo plum</v>
+        <v>Active Child</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
       </c>
       <c r="L192" t="str">
-        <v>butterflies - runo plum</v>
+        <v>I Know What to Say Now - Active Child</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>You're Right</v>
+        <v>Feel Something</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>You're Right - Single</v>
+        <v>Feel Something - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:00</v>
+        <v>3:09</v>
       </c>
       <c r="H193" t="str">
-        <v>Emma Harner</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
       </c>
       <c r="L193" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>Feel Something - Baby Queen</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Bible Belt</v>
+        <v>You Or Me</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Bible Belt - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G194" t="str">
-        <v>3:34</v>
+        <v>5:28</v>
       </c>
       <c r="H194" t="str">
-        <v>Baby Bugs</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
       </c>
       <c r="L194" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>You Or Me - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Daze</v>
+        <v>Mortercheyn</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Daze - Single</v>
+        <v>Coronach</v>
       </c>
       <c r="G195" t="str">
-        <v>3:22</v>
+        <v>4:18</v>
       </c>
       <c r="H195" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Hellripper</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
       </c>
       <c r="L195" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>Mortercheyn - Hellripper</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Passionfruit</v>
+        <v>Rip The God</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Passionfruit - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G196" t="str">
-        <v>3:57</v>
+        <v>5:20</v>
       </c>
       <c r="H196" t="str">
-        <v>Anish Kumar</v>
+        <v>Melvins</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
       </c>
       <c r="L196" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>Rip The God - Melvins</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Madan</v>
+        <v>Who We Are</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Madan - Single</v>
+        <v>Who We Are - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:56</v>
+        <v>2:10</v>
       </c>
       <c r="H197" t="str">
-        <v>Jonas Blue</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
       </c>
       <c r="L197" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Who We Are - Kaleena Zanders</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Bad Bitch</v>
+        <v>Reels in 360</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Dying Is The Internet</v>
       </c>
       <c r="G198" t="str">
-        <v>2:28</v>
+        <v>4:37</v>
       </c>
       <c r="H198" t="str">
-        <v>41</v>
+        <v>Simo Cell</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
       <c r="L198" t="str">
-        <v>Bad Bitch - 41</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Shame</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Devotion [Deluxe]</v>
-      </c>
-      <c r="G199" t="str">
-        <v>3:36</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Sunday (1994)</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
-      </c>
-      <c r="L199" t="str">
-        <v>Shame - Sunday (1994)</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>teach you to love me</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>teach you to love me - Single</v>
-      </c>
-      <c r="G200" t="str">
-        <v>3:09</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Hailey Picardi</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
-      </c>
-      <c r="L200" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>The Fix</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>The Fix - Single</v>
-      </c>
-      <c r="G201" t="str">
-        <v>2:42</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Baby J</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
-      </c>
-      <c r="L201" t="str">
-        <v>The Fix - Baby J</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Hanging on Hope</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Hanging on Hope - Single</v>
-      </c>
-      <c r="G202" t="str">
-        <v>3:43</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Buffalo Traffic Jam</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
-      </c>
-      <c r="L202" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>I Know What to Say Now</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>I Know What to Say Now - Single</v>
-      </c>
-      <c r="G203" t="str">
-        <v>3:18</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Active Child</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
-      </c>
-      <c r="L203" t="str">
-        <v>I Know What to Say Now - Active Child</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Feel Something</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Feel Something - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>3:09</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Baby Queen</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
-      </c>
-      <c r="L204" t="str">
-        <v>Feel Something - Baby Queen</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>You Or Me</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Good God / Baad Man</v>
-      </c>
-      <c r="G205" t="str">
-        <v>5:28</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Corrosion of Conformity</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
-      </c>
-      <c r="L205" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>Mortercheyn</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>Coronach</v>
-      </c>
-      <c r="G206" t="str">
-        <v>4:18</v>
-      </c>
-      <c r="H206" t="str">
-        <v>Hellripper</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
-      </c>
-      <c r="L206" t="str">
-        <v>Mortercheyn - Hellripper</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Rip The God</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Savage Imperial Death March</v>
-      </c>
-      <c r="G207" t="str">
-        <v>5:20</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Melvins</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
-      </c>
-      <c r="L207" t="str">
-        <v>Rip The God - Melvins</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>Who We Are</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Who We Are - Single</v>
-      </c>
-      <c r="G208" t="str">
-        <v>2:10</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Kaleena Zanders</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
-      </c>
-      <c r="L208" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>Reels in 360</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>Dying Is The Internet</v>
-      </c>
-      <c r="G209" t="str">
-        <v>4:37</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Simo Cell</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
-      </c>
-      <c r="L209" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L209"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week03/titles.xlsx
+++ b/data/global/2026-03-week03/titles.xlsx
@@ -1009,7 +1009,7 @@
         <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B17" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:21</v>
@@ -1047,7 +1047,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:16</v>
@@ -1085,7 +1085,7 @@
         <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B19" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:41</v>
@@ -1123,7 +1123,7 @@
         <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:29</v>
@@ -1161,7 +1161,7 @@
         <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B21" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:43</v>
@@ -1199,7 +1199,7 @@
         <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:46</v>
@@ -1237,7 +1237,7 @@
         <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>4:01</v>
@@ -1275,7 +1275,7 @@
         <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:23</v>
@@ -1313,7 +1313,7 @@
         <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B25" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:39</v>
@@ -1351,7 +1351,7 @@
         <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:04</v>
@@ -1389,7 +1389,7 @@
         <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:25</v>
@@ -1427,7 +1427,7 @@
         <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:49</v>
@@ -1465,7 +1465,7 @@
         <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:14</v>
@@ -1959,7 +1959,7 @@
         <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B42" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:53</v>
@@ -4201,7 +4201,7 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v>4:39</v>

--- a/data/global/2026-03-week03/titles.xlsx
+++ b/data/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>רון דבני – מה אני אגיד לך</v>
       </c>
       <c r="B2" t="str">
-        <v>4 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%9f-%d7%93%d7%91%d7%a0%d7%99-%d7%9e%d7%94-%d7%90%d7%a0%d7%99-%d7%90%d7%92%d7%99%d7%93-%d7%9c%d7%9a/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-16</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 days ago</v>
+        <v>רון דבני שר שיר מחאה חד, חכם ומטריד, שפועל במסווה של שיר קצבי כמעט קליל, אבל בתוכו יושב טקסט אפל מאוד על כוח, הדחקה, חרדה מחשיפה, והתפוררות של מנגנוני הגנה גבריים. זה בדיוק אחד הכוחות שלו: המוזיקה עולה על “נתיב</v>
       </c>
       <c r="G2" t="str">
-        <v>4:09</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Mei Semones</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>רון דבני – מה אני אגיד לך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B3" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-16</v>
@@ -492,10 +492,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:08</v>
+        <v>4:09</v>
       </c>
       <c r="H3" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-16</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:57</v>
+        <v>2:08</v>
       </c>
       <c r="H4" t="str">
-        <v>Natalie Jane</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-16</v>
@@ -568,10 +568,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:13</v>
+        <v>2:57</v>
       </c>
       <c r="H5" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B6" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-16</v>
@@ -606,10 +606,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:12</v>
+        <v>3:13</v>
       </c>
       <c r="H6" t="str">
-        <v>David Gilmour</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B7" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-16</v>
@@ -644,10 +644,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:57</v>
+        <v>4:12</v>
       </c>
       <c r="H7" t="str">
-        <v>Far Caspian</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-16</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:34</v>
+        <v>3:57</v>
       </c>
       <c r="H8" t="str">
-        <v>Celine Dion</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B9" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-16</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:48</v>
+        <v>3:34</v>
       </c>
       <c r="H9" t="str">
-        <v>Harry Styles</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B10" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-16</v>
@@ -758,10 +758,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:58</v>
+        <v>3:48</v>
       </c>
       <c r="H10" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-16</v>
@@ -796,10 +796,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:33</v>
+        <v>4:58</v>
       </c>
       <c r="H11" t="str">
-        <v>Ellise</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-16</v>
@@ -834,10 +834,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>5:01</v>
+        <v>2:33</v>
       </c>
       <c r="H12" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Ellise</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B13" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-16</v>
@@ -872,10 +872,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:56</v>
+        <v>5:01</v>
       </c>
       <c r="H13" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B14" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-16</v>
@@ -910,10 +910,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:54</v>
+        <v>4:56</v>
       </c>
       <c r="H14" t="str">
-        <v>Bebe Rexha</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B15" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-16</v>
@@ -948,10 +948,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:46</v>
+        <v>2:54</v>
       </c>
       <c r="H15" t="str">
-        <v>NathanEvanss</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B16" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-16</v>
@@ -986,10 +986,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:56</v>
+        <v>2:46</v>
       </c>
       <c r="H16" t="str">
-        <v>R3HAB</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-16</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:21</v>
+        <v>2:56</v>
       </c>
       <c r="H17" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>R3HAB</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B18" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-16</v>
@@ -1062,10 +1062,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:16</v>
+        <v>3:21</v>
       </c>
       <c r="H18" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B19" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-16</v>
@@ -1100,10 +1100,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:41</v>
+        <v>3:16</v>
       </c>
       <c r="H19" t="str">
-        <v>Johnny Orlando</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B20" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-16</v>
@@ -1138,10 +1138,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:29</v>
+        <v>2:41</v>
       </c>
       <c r="H20" t="str">
-        <v>Russell Dickerson</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B21" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-16</v>
@@ -1176,10 +1176,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:43</v>
+        <v>2:29</v>
       </c>
       <c r="H21" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B22" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-16</v>
@@ -1214,10 +1214,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:46</v>
+        <v>2:43</v>
       </c>
       <c r="H22" t="str">
-        <v>Matt Hansen</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B23" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-16</v>
@@ -1252,10 +1252,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:01</v>
+        <v>3:46</v>
       </c>
       <c r="H23" t="str">
-        <v>Mike Posner</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-16</v>
@@ -1290,10 +1290,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:23</v>
+        <v>4:01</v>
       </c>
       <c r="H24" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B25" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-16</v>
@@ -1328,10 +1328,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:39</v>
+        <v>3:23</v>
       </c>
       <c r="H25" t="str">
-        <v>almost monday</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B26" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-16</v>
@@ -1366,10 +1366,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:04</v>
+        <v>3:39</v>
       </c>
       <c r="H26" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>almost monday</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-16</v>
@@ -1404,10 +1404,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:25</v>
+        <v>3:04</v>
       </c>
       <c r="H27" t="str">
-        <v>vaultboy</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-16</v>
@@ -1442,10 +1442,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:49</v>
+        <v>3:25</v>
       </c>
       <c r="H28" t="str">
-        <v>The Warning</v>
+        <v>vaultboy</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B29" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-16</v>
@@ -1480,10 +1480,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:14</v>
+        <v>3:49</v>
       </c>
       <c r="H29" t="str">
-        <v>aron!</v>
+        <v>The Warning</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B30" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-16</v>
@@ -1518,10 +1518,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:43</v>
+        <v>2:14</v>
       </c>
       <c r="H30" t="str">
-        <v>Bazzi</v>
+        <v>aron!</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-16</v>
@@ -1556,10 +1556,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H31" t="str">
-        <v>Sting</v>
+        <v>Bazzi</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B32" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-16</v>
@@ -1594,10 +1594,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:44</v>
+        <v>4:43</v>
       </c>
       <c r="H32" t="str">
-        <v>Dean Lewis</v>
+        <v>Sting</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-16</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:37</v>
+        <v>2:44</v>
       </c>
       <c r="H33" t="str">
-        <v>Jessie Ware</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-16</v>
@@ -1670,10 +1670,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:52</v>
+        <v>4:37</v>
       </c>
       <c r="H34" t="str">
-        <v>Cannons</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B35" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-16</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:13</v>
+        <v>4:52</v>
       </c>
       <c r="H35" t="str">
-        <v>Kim Petras</v>
+        <v>Cannons</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B36" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-16</v>
@@ -1746,10 +1746,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:19</v>
+        <v>2:13</v>
       </c>
       <c r="H36" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B37" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-16</v>
@@ -1784,10 +1784,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:31</v>
+        <v>3:19</v>
       </c>
       <c r="H37" t="str">
-        <v>Kiana Ledé</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B38" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-16</v>
@@ -1822,10 +1822,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:43</v>
+        <v>2:31</v>
       </c>
       <c r="H38" t="str">
-        <v>Ringo Starr</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-16</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:10</v>
+        <v>2:43</v>
       </c>
       <c r="H39" t="str">
-        <v>Maya Hawke</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B40" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-16</v>
@@ -1898,10 +1898,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:55</v>
+        <v>3:10</v>
       </c>
       <c r="H40" t="str">
-        <v>Armin van Buuren</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B41" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-16</v>
@@ -1936,10 +1936,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:52</v>
+        <v>3:55</v>
       </c>
       <c r="H41" t="str">
-        <v>Demi Lovato</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B42" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-16</v>
@@ -1974,10 +1974,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:53</v>
+        <v>3:52</v>
       </c>
       <c r="H42" t="str">
-        <v>Peter Gabriel</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B43" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-16</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:30</v>
+        <v>2:53</v>
       </c>
       <c r="H43" t="str">
-        <v>Jessie J</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B44" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-16</v>
@@ -2050,10 +2050,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G44" t="str">
-        <v>5:18</v>
+        <v>4:30</v>
       </c>
       <c r="H44" t="str">
-        <v>Harry Styles</v>
+        <v>Jessie J</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B45" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-16</v>
@@ -2088,10 +2088,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G45" t="str">
-        <v>7:20</v>
+        <v>5:18</v>
       </c>
       <c r="H45" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B46" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-16</v>
@@ -2126,10 +2126,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:01</v>
+        <v>7:20</v>
       </c>
       <c r="H46" t="str">
-        <v>BRITs</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B47" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-16</v>
@@ -2164,10 +2164,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:31</v>
+        <v>3:01</v>
       </c>
       <c r="H47" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B48" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-16</v>
@@ -2202,10 +2202,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:00</v>
+        <v>3:31</v>
       </c>
       <c r="H48" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B49" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-16</v>
@@ -2240,10 +2240,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:11</v>
+        <v>3:00</v>
       </c>
       <c r="H49" t="str">
-        <v>The Kiffness</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B50" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-16</v>
@@ -2278,10 +2278,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:32</v>
+        <v>3:11</v>
       </c>
       <c r="H50" t="str">
-        <v>Lauv</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B51" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-16</v>
@@ -2316,10 +2316,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
-        <v>5:03</v>
+        <v>3:32</v>
       </c>
       <c r="H51" t="str">
-        <v>RAYE</v>
+        <v>Lauv</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B52" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-16</v>
@@ -2354,10 +2354,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:50</v>
+        <v>5:03</v>
       </c>
       <c r="H52" t="str">
-        <v>Armik</v>
+        <v>RAYE</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B53" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-16</v>
@@ -2392,10 +2392,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:53</v>
+        <v>4:50</v>
       </c>
       <c r="H53" t="str">
-        <v>Scorpions</v>
+        <v>Armik</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-16</v>
@@ -2430,10 +2430,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:04</v>
+        <v>4:53</v>
       </c>
       <c r="H54" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Scorpions</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-16</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:32</v>
+        <v>3:04</v>
       </c>
       <c r="H55" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-16</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:47</v>
+        <v>4:32</v>
       </c>
       <c r="H56" t="str">
-        <v>Girl Tones</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-16</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:40</v>
+        <v>3:47</v>
       </c>
       <c r="H57" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-16</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:05</v>
+        <v>3:40</v>
       </c>
       <c r="H58" t="str">
-        <v>HAUSER</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-16</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:59</v>
+        <v>4:05</v>
       </c>
       <c r="H59" t="str">
-        <v>Queen Official</v>
+        <v>HAUSER</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-16</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:55</v>
+        <v>2:59</v>
       </c>
       <c r="H60" t="str">
-        <v>Tenille Townes</v>
+        <v>Queen Official</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-16</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>5:12</v>
+        <v>3:55</v>
       </c>
       <c r="H61" t="str">
-        <v>Self Esteem</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-16</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:47</v>
+        <v>5:12</v>
       </c>
       <c r="H62" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-16</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:18</v>
+        <v>3:47</v>
       </c>
       <c r="H63" t="str">
-        <v>Em Beihold</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-16</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:50</v>
+        <v>3:18</v>
       </c>
       <c r="H64" t="str">
-        <v>Michael Bublé</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-16</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:24</v>
+        <v>3:50</v>
       </c>
       <c r="H65" t="str">
-        <v>MyKey</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-16</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:36</v>
+        <v>3:24</v>
       </c>
       <c r="H66" t="str">
-        <v>Max McNown</v>
+        <v>MyKey</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-16</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:34</v>
+        <v>2:36</v>
       </c>
       <c r="H67" t="str">
-        <v>Megan Moroney</v>
+        <v>Max McNown</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-16</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:03</v>
+        <v>3:34</v>
       </c>
       <c r="H68" t="str">
-        <v>ERNEST</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-16</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:31</v>
+        <v>4:03</v>
       </c>
       <c r="H69" t="str">
-        <v>Bruno Mars</v>
+        <v>ERNEST</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-16</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:22</v>
+        <v>3:31</v>
       </c>
       <c r="H70" t="str">
-        <v>BLACKPINK</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-16</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>5:49</v>
+        <v>3:22</v>
       </c>
       <c r="H71" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-16</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:47</v>
+        <v>5:49</v>
       </c>
       <c r="H72" t="str">
-        <v>Nessa Barrett</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-16</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:20</v>
+        <v>3:47</v>
       </c>
       <c r="H73" t="str">
-        <v>Towa Bird</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-16</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:18</v>
+        <v>2:20</v>
       </c>
       <c r="H74" t="str">
-        <v>Ty Myers</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-16</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:39</v>
+        <v>4:18</v>
       </c>
       <c r="H75" t="str">
-        <v>kenzie</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-16</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:52</v>
+        <v>2:39</v>
       </c>
       <c r="H76" t="str">
-        <v>Leanna Crawford</v>
+        <v>kenzie</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-16</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:01</v>
+        <v>3:52</v>
       </c>
       <c r="H77" t="str">
-        <v>Bryan Adams</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-16</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:54</v>
+        <v>4:01</v>
       </c>
       <c r="H78" t="str">
-        <v>CHESCA</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-16</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:03</v>
+        <v>2:54</v>
       </c>
       <c r="H79" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CHESCA</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-16</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:50</v>
+        <v>4:03</v>
       </c>
       <c r="H80" t="str">
-        <v>earMUSIC</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-16</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:06</v>
+        <v>4:50</v>
       </c>
       <c r="H81" t="str">
-        <v>Y2K</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-16</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:43</v>
+        <v>3:06</v>
       </c>
       <c r="H82" t="str">
-        <v>Lainey Wilson</v>
+        <v>Y2K</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-16</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>6:21</v>
+        <v>2:43</v>
       </c>
       <c r="H83" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-16</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:46</v>
+        <v>6:21</v>
       </c>
       <c r="H84" t="str">
-        <v>Bryan Ferry</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-16</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H85" t="str">
-        <v>Saint Harison</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-16</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:04</v>
+        <v>2:42</v>
       </c>
       <c r="H86" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-16</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:59</v>
+        <v>3:04</v>
       </c>
       <c r="H87" t="str">
-        <v>Catie Turner</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-16</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:22</v>
+        <v>2:59</v>
       </c>
       <c r="H88" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-16</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:53</v>
+        <v>2:22</v>
       </c>
       <c r="H89" t="str">
-        <v>Roxette</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-16</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:28</v>
+        <v>3:53</v>
       </c>
       <c r="H90" t="str">
-        <v>Marcin</v>
+        <v>Roxette</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-16</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:47</v>
+        <v>2:28</v>
       </c>
       <c r="H91" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Marcin</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-16</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:40</v>
+        <v>2:47</v>
       </c>
       <c r="H92" t="str">
-        <v>Laufey</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-16</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:49</v>
+        <v>3:40</v>
       </c>
       <c r="H93" t="str">
-        <v>Ava Max</v>
+        <v>Laufey</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-16</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>4:49</v>
+        <v>2:49</v>
       </c>
       <c r="H94" t="str">
-        <v>U2</v>
+        <v>Ava Max</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-16</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:35</v>
+        <v>4:49</v>
       </c>
       <c r="H95" t="str">
-        <v>Taylor Swift</v>
+        <v>U2</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-16</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:59</v>
+        <v>3:35</v>
       </c>
       <c r="H96" t="str">
-        <v>Kiana Ledé</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-16</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:38</v>
+        <v>2:59</v>
       </c>
       <c r="H97" t="str">
-        <v>Jessie Ware</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-16</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:46</v>
+        <v>4:38</v>
       </c>
       <c r="H98" t="str">
-        <v>Madison Beer</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-16</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:08</v>
+        <v>3:46</v>
       </c>
       <c r="H99" t="str">
-        <v>Sean Stemaly</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-16</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:32</v>
+        <v>3:08</v>
       </c>
       <c r="H100" t="str">
-        <v>earMUSIC</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-16</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:39</v>
+        <v>5:32</v>
       </c>
       <c r="H101" t="str">
-        <v>georgemichael</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Porch Light</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-16</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>The Great Divide</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>4:22</v>
+        <v>4:39</v>
       </c>
       <c r="H102" t="str">
-        <v>Noah Kahan</v>
+        <v>georgemichael</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Porch Light - Noah Kahan</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Dry Spell</v>
+        <v>Porch Light</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
+        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-16</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Middle of Nowhere</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G103" t="str">
-        <v>3:17</v>
+        <v>4:22</v>
       </c>
       <c r="H103" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
+        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
       </c>
       <c r="L103" t="str">
-        <v>Dry Spell - Kacey Musgraves</v>
+        <v>Porch Light - Noah Kahan</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>The Visitor</v>
+        <v>Dry Spell</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
+        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-16</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Visitor - Single</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G104" t="str">
-        <v>3:48</v>
+        <v>3:17</v>
       </c>
       <c r="H104" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
+        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
       </c>
       <c r="L104" t="str">
-        <v>The Visitor - SIENNA SPIRO</v>
+        <v>Dry Spell - Kacey Musgraves</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>I Ain't No Cowboy</v>
+        <v>The Visitor</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
+        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-16</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Way I Am</v>
+        <v>The Visitor - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:13</v>
+        <v>3:48</v>
       </c>
       <c r="H105" t="str">
-        <v>Luke Combs</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
+        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
       </c>
       <c r="L105" t="str">
-        <v>I Ain't No Cowboy - Luke Combs</v>
+        <v>The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Can't Sit Still</v>
+        <v>I Ain't No Cowboy</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
+        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-16</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Can't Sit Still - Single</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G106" t="str">
-        <v>3:35</v>
+        <v>3:13</v>
       </c>
       <c r="H106" t="str">
-        <v>Lainey Wilson</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
+        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
       </c>
       <c r="L106" t="str">
-        <v>Can't Sit Still - Lainey Wilson</v>
+        <v>I Ain't No Cowboy - Luke Combs</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías)</v>
+        <v>Can't Sit Still</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
+        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-16</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
+        <v>Can't Sit Still - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:43</v>
+        <v>3:35</v>
       </c>
       <c r="H107" t="str">
-        <v>beabadoobee</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
+        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
       </c>
       <c r="L107" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
+        <v>Can't Sit Still - Lainey Wilson</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Blow My Mind</v>
+        <v>All I Did Was Dream of You (feat. The Marías)</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
+        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-16</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Sexistential</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:57</v>
+        <v>3:43</v>
       </c>
       <c r="H108" t="str">
-        <v>Robyn</v>
+        <v>beabadoobee</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
+        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
       </c>
       <c r="L108" t="str">
-        <v>Blow My Mind - Robyn</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SATA</v>
+        <v>Blow My Mind</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/sata/1874015489</v>
+        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-16</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>Sexistential</v>
       </c>
       <c r="G109" t="str">
-        <v>3:02</v>
+        <v>2:57</v>
       </c>
       <c r="H109" t="str">
-        <v>John Summit</v>
+        <v>Robyn</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/sata/1874015470</v>
+        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
       </c>
       <c r="L109" t="str">
-        <v>SATA - John Summit</v>
+        <v>Blow My Mind - Robyn</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Una Aventura</v>
+        <v>SATA</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
+        <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-16</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Una Aventura - Single</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G110" t="str">
-        <v>3:00</v>
+        <v>3:02</v>
       </c>
       <c r="H110" t="str">
-        <v>Ozuna</v>
+        <v>John Summit</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
+        <v>https://music.apple.com/us/album/sata/1874015470</v>
       </c>
       <c r="L110" t="str">
-        <v>Una Aventura - Ozuna</v>
+        <v>SATA - John Summit</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>Una Aventura</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-16</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Una Aventura - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:44</v>
+        <v>3:00</v>
       </c>
       <c r="H111" t="str">
-        <v>Charlie Puth</v>
+        <v>Ozuna</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
       </c>
       <c r="L111" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>Una Aventura - Ozuna</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>dirty wedding dress</v>
+        <v>Home (feat. Hikaru Utada)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-16</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G112" t="str">
-        <v>4:49</v>
+        <v>3:44</v>
       </c>
       <c r="H112" t="str">
-        <v>Bleachers</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
       </c>
       <c r="L112" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>dirty wedding dress</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-16</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Age of the Ram</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G113" t="str">
-        <v>3:07</v>
+        <v>4:49</v>
       </c>
       <c r="H113" t="str">
-        <v>Charley Crockett</v>
+        <v>Bleachers</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
       </c>
       <c r="L113" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>dirty wedding dress - Bleachers</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-16</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G114" t="str">
-        <v>3:13</v>
+        <v>3:07</v>
       </c>
       <c r="H114" t="str">
-        <v>Grupo Frontera</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L114" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Trade Places</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-16</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Monica</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:02</v>
+        <v>3:13</v>
       </c>
       <c r="H115" t="str">
-        <v>Jack Harlow</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L115" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Motion Party</v>
+        <v>Trade Places</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-16</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Motion Party - Single</v>
+        <v>Monica</v>
       </c>
       <c r="G116" t="str">
-        <v>1:35</v>
+        <v>3:02</v>
       </c>
       <c r="H116" t="str">
-        <v>Bossman Dlow</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L116" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Woman</v>
+        <v>Motion Party</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-16</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Woman - Single</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:46</v>
+        <v>1:35</v>
       </c>
       <c r="H117" t="str">
-        <v>Kane Brown</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L117" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Sunburn</v>
+        <v>Woman</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-16</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Sunburn - Single</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:05</v>
+        <v>2:46</v>
       </c>
       <c r="H118" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L118" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Que Te Costó</v>
+        <v>Sunburn</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-16</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Metamorfosis</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H119" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L119" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>oooshxt!</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-16</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>oooshxt! - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G120" t="str">
-        <v>2:15</v>
+        <v>2:54</v>
       </c>
       <c r="H120" t="str">
-        <v>Samara Cyn</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L120" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-16</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:26</v>
+        <v>2:15</v>
       </c>
       <c r="H121" t="str">
-        <v>Holly Humberstone</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L121" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Star</v>
+        <v>Cruel World</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-16</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Star - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G122" t="str">
-        <v>3:25</v>
+        <v>3:26</v>
       </c>
       <c r="H122" t="str">
-        <v>Iceage</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L122" t="str">
-        <v>Star - Iceage</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Get Go</v>
+        <v>Star</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-16</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Star - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:22</v>
+        <v>3:25</v>
       </c>
       <c r="H123" t="str">
-        <v>Arlo Parks</v>
+        <v>Iceage</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L123" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>ThunderWave</v>
+        <v>Get Go</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-16</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Distracted</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G124" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H124" t="str">
-        <v>Thundercat</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L124" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Club Song</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-16</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Club Song - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G125" t="str">
-        <v>2:27</v>
+        <v>3:14</v>
       </c>
       <c r="H125" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>Thundercat</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L125" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Better Man</v>
+        <v>Club Song</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-16</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Better Man - Single</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:53</v>
+        <v>2:27</v>
       </c>
       <c r="H126" t="str">
-        <v>jxdn</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L126" t="str">
-        <v>Better Man - jxdn</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>sabotage</v>
+        <v>Better Man</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-16</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>sabotage - Single</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:58</v>
+        <v>2:53</v>
       </c>
       <c r="H127" t="str">
-        <v>Natalie Jane</v>
+        <v>jxdn</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L127" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>sabotage</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-16</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H128" t="str">
-        <v>WHATMORE</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L128" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Naked</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-16</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Naked - Single</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:39</v>
+        <v>2:56</v>
       </c>
       <c r="H129" t="str">
-        <v>Kenya Grace</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L129" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Catharina</v>
+        <v>Naked</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-16</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Catharina - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:27</v>
+        <v>3:39</v>
       </c>
       <c r="H130" t="str">
-        <v>Martin Garrix</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L130" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>Catharina</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-16</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:00</v>
+        <v>3:27</v>
       </c>
       <c r="H131" t="str">
-        <v>Chase &amp; Status</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L131" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-16</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:33</v>
+        <v>3:00</v>
       </c>
       <c r="H132" t="str">
-        <v>James Blake</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L132" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>595</v>
+        <v>Trying Times</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-16</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Trying Times</v>
       </c>
       <c r="G133" t="str">
-        <v>2:29</v>
+        <v>4:33</v>
       </c>
       <c r="H133" t="str">
-        <v>Violet Grohl</v>
+        <v>James Blake</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L133" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>595</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-16</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Soft 2</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G134" t="str">
-        <v>3:50</v>
+        <v>2:29</v>
       </c>
       <c r="H134" t="str">
-        <v>LANY</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L134" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>CALL ME</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-16</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>CALL ME - Single</v>
+        <v>Soft 2</v>
       </c>
       <c r="G135" t="str">
-        <v>2:10</v>
+        <v>3:50</v>
       </c>
       <c r="H135" t="str">
-        <v>ALTÉGO</v>
+        <v>LANY</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L135" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Mi Amor</v>
+        <v>CALL ME</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-16</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Free (Deluxe)</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:00</v>
+        <v>2:10</v>
       </c>
       <c r="H136" t="str">
-        <v>Nasty C</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L136" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>BOBA</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-16</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>BOBA - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G137" t="str">
-        <v>3:00</v>
+        <v>2:00</v>
       </c>
       <c r="H137" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Nasty C</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L137" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Video Shoot</v>
+        <v>BOBA</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-16</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Skeletor</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:38</v>
+        <v>3:00</v>
       </c>
       <c r="H138" t="str">
-        <v>Chief Keef</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L138" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-16</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G139" t="str">
-        <v>2:06</v>
+        <v>2:38</v>
       </c>
       <c r="H139" t="str">
-        <v>Shenseea</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L139" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Just Believe</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-16</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Just Believe - Single</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:41</v>
+        <v>2:06</v>
       </c>
       <c r="H140" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Shenseea</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L140" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Knife In The Heart</v>
+        <v>Just Believe</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-16</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>The Afterparty</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:57</v>
+        <v>2:41</v>
       </c>
       <c r="H141" t="str">
-        <v>Lykke Li</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L141" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>The Way We Touch</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-16</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G142" t="str">
-        <v>3:09</v>
+        <v>2:57</v>
       </c>
       <c r="H142" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L142" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>DANGEROUS</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-16</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>4:06</v>
+        <v>3:09</v>
       </c>
       <c r="H143" t="str">
-        <v>Magnolia Park</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L143" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>When I Wake Up</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-16</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Dear God</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G144" t="str">
-        <v>3:33</v>
+        <v>4:06</v>
       </c>
       <c r="H144" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L144" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Breathe</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-16</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Breathe - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G145" t="str">
-        <v>2:56</v>
+        <v>3:33</v>
       </c>
       <c r="H145" t="str">
-        <v>Malcolm Todd</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L145" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Minty</v>
+        <v>Breathe</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-16</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>1:47</v>
+        <v>2:56</v>
       </c>
       <c r="H146" t="str">
-        <v>MIKE</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L146" t="str">
-        <v>Minty - MIKE</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Earth</v>
+        <v>Minty</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-16</v>
@@ -5964,33 +5964,33 @@
         <v>POMPEII // UTILITY</v>
       </c>
       <c r="G147" t="str">
-        <v>1:37</v>
+        <v>1:47</v>
       </c>
       <c r="H147" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>MIKE</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L147" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drink The Water</v>
+        <v>Earth</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-16</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G148" t="str">
-        <v>3:42</v>
+        <v>1:37</v>
       </c>
       <c r="H148" t="str">
-        <v>Jack Johnson</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L148" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-16</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G149" t="str">
-        <v>4:32</v>
+        <v>3:42</v>
       </c>
       <c r="H149" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L149" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-16</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:32</v>
+        <v>4:32</v>
       </c>
       <c r="H150" t="str">
-        <v>Carly Pearce</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L150" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Muchacho Alegre</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-16</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:08</v>
+        <v>3:32</v>
       </c>
       <c r="H151" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L151" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Real Slow</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-16</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Work of Heart</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:22</v>
+        <v>3:08</v>
       </c>
       <c r="H152" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L152" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Mountain Girl</v>
+        <v>Real Slow</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-16</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>As Is</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G153" t="str">
-        <v>2:42</v>
+        <v>3:22</v>
       </c>
       <c r="H153" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L153" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Like a Spark</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-16</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>American Stories</v>
+        <v>As Is</v>
       </c>
       <c r="G154" t="str">
-        <v>3:31</v>
+        <v>2:42</v>
       </c>
       <c r="H154" t="str">
-        <v>Rostam</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L154" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Cheesecake</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-16</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>American Stories</v>
       </c>
       <c r="G155" t="str">
-        <v>3:29</v>
+        <v>3:31</v>
       </c>
       <c r="H155" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Rostam</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L155" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-16</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>KINDA HARD</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G156" t="str">
-        <v>3:04</v>
+        <v>3:29</v>
       </c>
       <c r="H156" t="str">
-        <v>Bilmuri</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L156" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Freakin’ Out</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-16</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G157" t="str">
-        <v>3:37</v>
+        <v>3:04</v>
       </c>
       <c r="H157" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L157" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Name in Vein</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-16</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Name in Vein - Single</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:03</v>
+        <v>3:37</v>
       </c>
       <c r="H158" t="str">
-        <v>VOILÀ</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L158" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-16</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Into Oblivion</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>4:05</v>
+        <v>3:03</v>
       </c>
       <c r="H159" t="str">
-        <v>Lamb of God</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L159" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Undefeated Champion</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-16</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Sweat</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G160" t="str">
-        <v>3:34</v>
+        <v>4:05</v>
       </c>
       <c r="H160" t="str">
-        <v>Melanie C</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L160" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Pull Up</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-16</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Pull Up - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G161" t="str">
-        <v>2:35</v>
+        <v>3:34</v>
       </c>
       <c r="H161" t="str">
-        <v>Collect 200</v>
+        <v>Melanie C</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L161" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Ranjha</v>
+        <v>Pull Up</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-16</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Ranjha - Single</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:04</v>
+        <v>2:35</v>
       </c>
       <c r="H162" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>Collect 200</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L162" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>zombies in love</v>
+        <v>Ranjha</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-16</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>zombies in love - Single</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:53</v>
+        <v>3:04</v>
       </c>
       <c r="H163" t="str">
-        <v>paris jackson</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L163" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Days Of Us</v>
+        <v>zombies in love</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-16</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Full Circle</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>4:39</v>
+        <v>2:53</v>
       </c>
       <c r="H164" t="str">
-        <v>Tom Misch</v>
+        <v>paris jackson</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L164" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Life Of A Man</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-16</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G165" t="str">
-        <v>3:15</v>
+        <v>4:39</v>
       </c>
       <c r="H165" t="str">
-        <v>1Ski OG</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L165" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Ya No</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-16</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Ya No - Single</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:40</v>
+        <v>3:15</v>
       </c>
       <c r="H166" t="str">
-        <v>Marca MP</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L166" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Ya No</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-16</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:48</v>
+        <v>3:40</v>
       </c>
       <c r="H167" t="str">
-        <v>Spacey Jane</v>
+        <v>Marca MP</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L167" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Relieve You</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-16</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Relieve You - Single</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:19</v>
+        <v>3:48</v>
       </c>
       <c r="H168" t="str">
-        <v>4Fargo</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L168" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Safety</v>
+        <v>Relieve You</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-16</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Safety - Single</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:18</v>
+        <v>2:19</v>
       </c>
       <c r="H169" t="str">
-        <v>Lekan</v>
+        <v>4Fargo</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L169" t="str">
-        <v>Safety - Lekan</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Starlet</v>
+        <v>Safety</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-16</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>LK99</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:56</v>
+        <v>3:18</v>
       </c>
       <c r="H170" t="str">
-        <v>Leven Kali</v>
+        <v>Lekan</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L170" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Physical</v>
+        <v>Starlet</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-16</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Physical - Single</v>
+        <v>LK99</v>
       </c>
       <c r="G171" t="str">
-        <v>3:52</v>
+        <v>2:56</v>
       </c>
       <c r="H171" t="str">
-        <v>Jacquees</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L171" t="str">
-        <v>Physical - Jacquees</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Physical</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-16</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:29</v>
+        <v>3:52</v>
       </c>
       <c r="H172" t="str">
-        <v>Casper Sage</v>
+        <v>Jacquees</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L172" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Regalito</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-16</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>TRESCENDER</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:41</v>
+        <v>4:29</v>
       </c>
       <c r="H173" t="str">
-        <v>Piso 21</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L173" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Cruel Streak</v>
+        <v>Regalito</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-16</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>A Pound of Feathers</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G174" t="str">
-        <v>4:09</v>
+        <v>2:41</v>
       </c>
       <c r="H174" t="str">
-        <v>The Black Crowes</v>
+        <v>Piso 21</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L174" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Die Young</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-16</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Little Wide Open</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G175" t="str">
-        <v>3:52</v>
+        <v>4:09</v>
       </c>
       <c r="H175" t="str">
-        <v>Kevin Morby</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L175" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Island Girl</v>
+        <v>Die Young</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-16</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Island Girl - Single</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G176" t="str">
-        <v>3:27</v>
+        <v>3:52</v>
       </c>
       <c r="H176" t="str">
-        <v>Pia Mia</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L176" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Island Girl</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-16</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:20</v>
+        <v>3:27</v>
       </c>
       <c r="H177" t="str">
-        <v>Claudia Valentina</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L177" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-16</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:22</v>
+        <v>2:20</v>
       </c>
       <c r="H178" t="str">
-        <v>Shaggy</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L178" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Tommy’s Song</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-16</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Lovers - Single</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:44</v>
+        <v>3:22</v>
       </c>
       <c r="H179" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Shaggy</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L179" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Rainbows</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-16</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Rainbows - Single</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:25</v>
+        <v>3:44</v>
       </c>
       <c r="H180" t="str">
-        <v>Allison Russell</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L180" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>butterflies</v>
+        <v>Rainbows</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-16</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:48</v>
+        <v>3:25</v>
       </c>
       <c r="H181" t="str">
-        <v>runo plum</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L181" t="str">
-        <v>butterflies - runo plum</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You're Right</v>
+        <v>butterflies</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-16</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>You're Right - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G182" t="str">
-        <v>3:00</v>
+        <v>2:48</v>
       </c>
       <c r="H182" t="str">
-        <v>Emma Harner</v>
+        <v>runo plum</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L182" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Bible Belt</v>
+        <v>You're Right</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-16</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Bible Belt - Single</v>
+        <v>You're Right - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H183" t="str">
-        <v>Baby Bugs</v>
+        <v>Emma Harner</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
       </c>
       <c r="L183" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>You're Right - Emma Harner</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Daze</v>
+        <v>Bible Belt</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-16</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Daze - Single</v>
+        <v>Bible Belt - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:22</v>
+        <v>3:34</v>
       </c>
       <c r="H184" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Baby Bugs</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
       </c>
       <c r="L184" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>Bible Belt - Baby Bugs</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Passionfruit</v>
+        <v>Daze</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-16</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Passionfruit - Single</v>
+        <v>Daze - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:57</v>
+        <v>3:22</v>
       </c>
       <c r="H185" t="str">
-        <v>Anish Kumar</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
       </c>
       <c r="L185" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>Daze - Olympia Vitalis</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Madan</v>
+        <v>Passionfruit</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-16</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Madan - Single</v>
+        <v>Passionfruit - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:56</v>
+        <v>3:57</v>
       </c>
       <c r="H186" t="str">
-        <v>Jonas Blue</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
       </c>
       <c r="L186" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Passionfruit - Anish Kumar</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Bad Bitch</v>
+        <v>Madan</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-16</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Madan - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:28</v>
+        <v>2:56</v>
       </c>
       <c r="H187" t="str">
-        <v>41</v>
+        <v>Jonas Blue</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
       </c>
       <c r="L187" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Madan - Jonas Blue</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Shame</v>
+        <v>Bad Bitch</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-16</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>Bad Bitch - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:36</v>
+        <v>2:28</v>
       </c>
       <c r="H188" t="str">
-        <v>Sunday (1994)</v>
+        <v>41</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
       </c>
       <c r="L188" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>Bad Bitch - 41</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>teach you to love me</v>
+        <v>Shame</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-16</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>teach you to love me - Single</v>
+        <v>Devotion [Deluxe]</v>
       </c>
       <c r="G189" t="str">
-        <v>3:09</v>
+        <v>3:36</v>
       </c>
       <c r="H189" t="str">
-        <v>Hailey Picardi</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
       </c>
       <c r="L189" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>Shame - Sunday (1994)</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>The Fix</v>
+        <v>teach you to love me</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-16</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>The Fix - Single</v>
+        <v>teach you to love me - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H190" t="str">
-        <v>Baby J</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
       </c>
       <c r="L190" t="str">
-        <v>The Fix - Baby J</v>
+        <v>teach you to love me - Hailey Picardi</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Hanging on Hope</v>
+        <v>The Fix</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-16</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>The Fix - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:43</v>
+        <v>2:42</v>
       </c>
       <c r="H191" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Baby J</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
       </c>
       <c r="L191" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>The Fix - Baby J</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>I Know What to Say Now</v>
+        <v>Hanging on Hope</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-16</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Hanging on Hope - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:18</v>
+        <v>3:43</v>
       </c>
       <c r="H192" t="str">
-        <v>Active Child</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
       </c>
       <c r="L192" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Feel Something</v>
+        <v>I Know What to Say Now</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-16</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Feel Something - Single</v>
+        <v>I Know What to Say Now - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:09</v>
+        <v>3:18</v>
       </c>
       <c r="H193" t="str">
-        <v>Baby Queen</v>
+        <v>Active Child</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
       </c>
       <c r="L193" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>I Know What to Say Now - Active Child</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>You Or Me</v>
+        <v>Feel Something</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-16</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Feel Something - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>5:28</v>
+        <v>3:09</v>
       </c>
       <c r="H194" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
       </c>
       <c r="L194" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>Feel Something - Baby Queen</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Mortercheyn</v>
+        <v>You Or Me</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-16</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Coronach</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G195" t="str">
-        <v>4:18</v>
+        <v>5:28</v>
       </c>
       <c r="H195" t="str">
-        <v>Hellripper</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
       </c>
       <c r="L195" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>You Or Me - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Rip The God</v>
+        <v>Mortercheyn</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-16</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Coronach</v>
       </c>
       <c r="G196" t="str">
-        <v>5:20</v>
+        <v>4:18</v>
       </c>
       <c r="H196" t="str">
-        <v>Melvins</v>
+        <v>Hellripper</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
       </c>
       <c r="L196" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Mortercheyn - Hellripper</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Who We Are</v>
+        <v>Rip The God</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-16</v>
@@ -7861,68 +7861,106 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Who We Are - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G197" t="str">
-        <v>2:10</v>
+        <v>5:20</v>
       </c>
       <c r="H197" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Melvins</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
       </c>
       <c r="L197" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
+        <v>Rip The God - Melvins</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
+        <v>Who We Are</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>Who We Are - Single</v>
+      </c>
+      <c r="G198" t="str">
+        <v>2:10</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Kaleena Zanders</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+      </c>
+      <c r="L198" t="str">
+        <v>Who We Are - Kaleena Zanders</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
         <v>Reels in 360</v>
       </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
-      <c r="D198" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
+      <c r="D199" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
         <v>Dying Is The Internet</v>
       </c>
-      <c r="G198" t="str">
+      <c r="G199" t="str">
         <v>4:37</v>
       </c>
-      <c r="H198" t="str">
+      <c r="H199" t="str">
         <v>Simo Cell</v>
       </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
         <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
-      <c r="K198" t="str">
+      <c r="K199" t="str">
         <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
-      <c r="L198" t="str">
+      <c r="L199" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week03/titles.xlsx
+++ b/data/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רון דבני – מה אני אגיד לך</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-16</v>
+        <v>5 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%9f-%d7%93%d7%91%d7%a0%d7%99-%d7%9e%d7%94-%d7%90%d7%a0%d7%99-%d7%90%d7%92%d7%99%d7%93-%d7%9c%d7%9a/</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-16</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>רון דבני שר שיר מחאה חד, חכם ומטריד, שפועל במסווה של שיר קצבי כמעט קליל, אבל בתוכו יושב טקסט אפל מאוד על כוח, הדחקה, חרדה מחשיפה, והתפוררות של מנגנוני הגנה גבריים. זה בדיוק אחד הכוחות שלו: המוזיקה עולה על “נתיב</v>
+        <v>5 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>4:09</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Mei Semones</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רון דבני – מה אני אגיד לך</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-16</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:09</v>
+        <v>2:08</v>
       </c>
       <c r="H3" t="str">
-        <v>Mei Semones</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-16</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:08</v>
+        <v>2:57</v>
       </c>
       <c r="H4" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B5" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-16</v>
@@ -568,10 +568,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:57</v>
+        <v>3:13</v>
       </c>
       <c r="H5" t="str">
-        <v>Natalie Jane</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B6" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-16</v>
@@ -606,10 +606,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:13</v>
+        <v>4:12</v>
       </c>
       <c r="H6" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B7" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-16</v>
@@ -644,10 +644,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:12</v>
+        <v>3:57</v>
       </c>
       <c r="H7" t="str">
-        <v>David Gilmour</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-16</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:57</v>
+        <v>3:34</v>
       </c>
       <c r="H8" t="str">
-        <v>Far Caspian</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-16</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:34</v>
+        <v>3:48</v>
       </c>
       <c r="H9" t="str">
-        <v>Celine Dion</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-16</v>
@@ -758,10 +758,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:48</v>
+        <v>4:58</v>
       </c>
       <c r="H10" t="str">
-        <v>Harry Styles</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-16</v>
@@ -796,10 +796,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:58</v>
+        <v>2:33</v>
       </c>
       <c r="H11" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Ellise</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B12" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-16</v>
@@ -834,10 +834,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:33</v>
+        <v>5:01</v>
       </c>
       <c r="H12" t="str">
-        <v>Ellise</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B13" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-16</v>
@@ -872,10 +872,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>5:01</v>
+        <v>4:56</v>
       </c>
       <c r="H13" t="str">
-        <v>The Doobie Brothers</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B14" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-16</v>
@@ -910,10 +910,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:56</v>
+        <v>2:54</v>
       </c>
       <c r="H14" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B15" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-16</v>
@@ -948,10 +948,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:54</v>
+        <v>2:46</v>
       </c>
       <c r="H15" t="str">
-        <v>Bebe Rexha</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-16</v>
@@ -986,10 +986,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H16" t="str">
-        <v>NathanEvanss</v>
+        <v>R3HAB</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B17" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-16</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:56</v>
+        <v>3:21</v>
       </c>
       <c r="H17" t="str">
-        <v>R3HAB</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B18" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-16</v>
@@ -1062,10 +1062,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:21</v>
+        <v>3:16</v>
       </c>
       <c r="H18" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B19" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-16</v>
@@ -1100,10 +1100,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:16</v>
+        <v>2:41</v>
       </c>
       <c r="H19" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B20" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-16</v>
@@ -1138,10 +1138,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:41</v>
+        <v>2:29</v>
       </c>
       <c r="H20" t="str">
-        <v>Johnny Orlando</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B21" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-16</v>
@@ -1176,10 +1176,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:29</v>
+        <v>2:43</v>
       </c>
       <c r="H21" t="str">
-        <v>Russell Dickerson</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B22" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-16</v>
@@ -1214,10 +1214,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:43</v>
+        <v>3:46</v>
       </c>
       <c r="H22" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-16</v>
@@ -1252,10 +1252,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:46</v>
+        <v>4:01</v>
       </c>
       <c r="H23" t="str">
-        <v>Matt Hansen</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B24" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-16</v>
@@ -1290,10 +1290,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:01</v>
+        <v>3:23</v>
       </c>
       <c r="H24" t="str">
-        <v>Mike Posner</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B25" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-16</v>
@@ -1328,10 +1328,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:23</v>
+        <v>3:39</v>
       </c>
       <c r="H25" t="str">
-        <v>Katelyn Tarver</v>
+        <v>almost monday</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-16</v>
@@ -1366,10 +1366,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H26" t="str">
-        <v>almost monday</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-16</v>
@@ -1404,10 +1404,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:04</v>
+        <v>3:25</v>
       </c>
       <c r="H27" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>vaultboy</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-16</v>
@@ -1442,10 +1442,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:25</v>
+        <v>3:49</v>
       </c>
       <c r="H28" t="str">
-        <v>vaultboy</v>
+        <v>The Warning</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B29" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-16</v>
@@ -1480,10 +1480,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:49</v>
+        <v>2:14</v>
       </c>
       <c r="H29" t="str">
-        <v>The Warning</v>
+        <v>aron!</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-16</v>
@@ -1518,10 +1518,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:14</v>
+        <v>2:43</v>
       </c>
       <c r="H30" t="str">
-        <v>aron!</v>
+        <v>Bazzi</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B31" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-16</v>
@@ -1556,10 +1556,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:43</v>
+        <v>4:43</v>
       </c>
       <c r="H31" t="str">
-        <v>Bazzi</v>
+        <v>Sting</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-16</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>4:43</v>
+        <v>2:44</v>
       </c>
       <c r="H32" t="str">
-        <v>Sting</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-16</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:44</v>
+        <v>4:37</v>
       </c>
       <c r="H33" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B34" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-16</v>
@@ -1670,10 +1670,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:37</v>
+        <v>4:52</v>
       </c>
       <c r="H34" t="str">
-        <v>Jessie Ware</v>
+        <v>Cannons</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B35" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-16</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:52</v>
+        <v>2:13</v>
       </c>
       <c r="H35" t="str">
-        <v>Cannons</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B36" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-16</v>
@@ -1746,10 +1746,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:13</v>
+        <v>3:19</v>
       </c>
       <c r="H36" t="str">
-        <v>Kim Petras</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B37" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-16</v>
@@ -1784,10 +1784,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:19</v>
+        <v>2:31</v>
       </c>
       <c r="H37" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-16</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:31</v>
+        <v>2:43</v>
       </c>
       <c r="H38" t="str">
-        <v>Kiana Ledé</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-16</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:43</v>
+        <v>3:10</v>
       </c>
       <c r="H39" t="str">
-        <v>Ringo Starr</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B40" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-16</v>
@@ -1898,10 +1898,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:10</v>
+        <v>3:55</v>
       </c>
       <c r="H40" t="str">
-        <v>Maya Hawke</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B41" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-16</v>
@@ -1936,10 +1936,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:55</v>
+        <v>3:52</v>
       </c>
       <c r="H41" t="str">
-        <v>Armin van Buuren</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B42" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-16</v>
@@ -1974,10 +1974,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:52</v>
+        <v>2:53</v>
       </c>
       <c r="H42" t="str">
-        <v>Demi Lovato</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-16</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:53</v>
+        <v>4:30</v>
       </c>
       <c r="H43" t="str">
-        <v>Peter Gabriel</v>
+        <v>Jessie J</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B44" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-16</v>
@@ -2050,10 +2050,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:30</v>
+        <v>5:18</v>
       </c>
       <c r="H44" t="str">
-        <v>Jessie J</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B45" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-16</v>
@@ -2088,10 +2088,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G45" t="str">
-        <v>5:18</v>
+        <v>7:20</v>
       </c>
       <c r="H45" t="str">
-        <v>Harry Styles</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B46" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-16</v>
@@ -2126,10 +2126,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G46" t="str">
-        <v>7:20</v>
+        <v>3:01</v>
       </c>
       <c r="H46" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B47" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-16</v>
@@ -2164,10 +2164,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:01</v>
+        <v>3:31</v>
       </c>
       <c r="H47" t="str">
-        <v>BRITs</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B48" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-16</v>
@@ -2202,10 +2202,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:31</v>
+        <v>3:00</v>
       </c>
       <c r="H48" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B49" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-16</v>
@@ -2240,10 +2240,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:00</v>
+        <v>3:11</v>
       </c>
       <c r="H49" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B50" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-16</v>
@@ -2278,10 +2278,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:11</v>
+        <v>3:32</v>
       </c>
       <c r="H50" t="str">
-        <v>The Kiffness</v>
+        <v>Lauv</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B51" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-16</v>
@@ -2316,10 +2316,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:32</v>
+        <v>5:03</v>
       </c>
       <c r="H51" t="str">
-        <v>Lauv</v>
+        <v>RAYE</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B52" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-16</v>
@@ -2354,10 +2354,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
-        <v>5:03</v>
+        <v>4:50</v>
       </c>
       <c r="H52" t="str">
-        <v>RAYE</v>
+        <v>Armik</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B53" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-16</v>
@@ -2392,10 +2392,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:50</v>
+        <v>4:53</v>
       </c>
       <c r="H53" t="str">
-        <v>Armik</v>
+        <v>Scorpions</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-16</v>
@@ -2430,10 +2430,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:53</v>
+        <v>3:04</v>
       </c>
       <c r="H54" t="str">
-        <v>Scorpions</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-16</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:04</v>
+        <v>4:32</v>
       </c>
       <c r="H55" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-16</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:32</v>
+        <v>3:47</v>
       </c>
       <c r="H56" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-16</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:47</v>
+        <v>3:40</v>
       </c>
       <c r="H57" t="str">
-        <v>Girl Tones</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-16</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:40</v>
+        <v>4:05</v>
       </c>
       <c r="H58" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>HAUSER</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-16</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:05</v>
+        <v>2:59</v>
       </c>
       <c r="H59" t="str">
-        <v>HAUSER</v>
+        <v>Queen Official</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-16</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:59</v>
+        <v>3:55</v>
       </c>
       <c r="H60" t="str">
-        <v>Queen Official</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-16</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:55</v>
+        <v>5:12</v>
       </c>
       <c r="H61" t="str">
-        <v>Tenille Townes</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-16</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>5:12</v>
+        <v>3:47</v>
       </c>
       <c r="H62" t="str">
-        <v>Self Esteem</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-16</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:47</v>
+        <v>3:18</v>
       </c>
       <c r="H63" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-16</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:18</v>
+        <v>3:50</v>
       </c>
       <c r="H64" t="str">
-        <v>Em Beihold</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-16</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:50</v>
+        <v>3:24</v>
       </c>
       <c r="H65" t="str">
-        <v>Michael Bublé</v>
+        <v>MyKey</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-16</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:24</v>
+        <v>2:36</v>
       </c>
       <c r="H66" t="str">
-        <v>MyKey</v>
+        <v>Max McNown</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-16</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:36</v>
+        <v>3:34</v>
       </c>
       <c r="H67" t="str">
-        <v>Max McNown</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-16</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:34</v>
+        <v>4:03</v>
       </c>
       <c r="H68" t="str">
-        <v>Megan Moroney</v>
+        <v>ERNEST</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-16</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:03</v>
+        <v>3:31</v>
       </c>
       <c r="H69" t="str">
-        <v>ERNEST</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-16</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:31</v>
+        <v>3:22</v>
       </c>
       <c r="H70" t="str">
-        <v>Bruno Mars</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-16</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:22</v>
+        <v>5:49</v>
       </c>
       <c r="H71" t="str">
-        <v>BLACKPINK</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-16</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>5:49</v>
+        <v>3:47</v>
       </c>
       <c r="H72" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-16</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:47</v>
+        <v>2:20</v>
       </c>
       <c r="H73" t="str">
-        <v>Nessa Barrett</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-16</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:20</v>
+        <v>4:18</v>
       </c>
       <c r="H74" t="str">
-        <v>Towa Bird</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-16</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:18</v>
+        <v>2:39</v>
       </c>
       <c r="H75" t="str">
-        <v>Ty Myers</v>
+        <v>kenzie</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-16</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:39</v>
+        <v>3:52</v>
       </c>
       <c r="H76" t="str">
-        <v>kenzie</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-16</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:52</v>
+        <v>4:01</v>
       </c>
       <c r="H77" t="str">
-        <v>Leanna Crawford</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-16</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:01</v>
+        <v>2:54</v>
       </c>
       <c r="H78" t="str">
-        <v>Bryan Adams</v>
+        <v>CHESCA</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-16</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:54</v>
+        <v>4:03</v>
       </c>
       <c r="H79" t="str">
-        <v>CHESCA</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-16</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:03</v>
+        <v>4:50</v>
       </c>
       <c r="H80" t="str">
-        <v>Dermot Kennedy</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-16</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:50</v>
+        <v>3:06</v>
       </c>
       <c r="H81" t="str">
-        <v>earMUSIC</v>
+        <v>Y2K</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-16</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:06</v>
+        <v>2:43</v>
       </c>
       <c r="H82" t="str">
-        <v>Y2K</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-16</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:43</v>
+        <v>6:21</v>
       </c>
       <c r="H83" t="str">
-        <v>Lainey Wilson</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-16</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>6:21</v>
+        <v>2:46</v>
       </c>
       <c r="H84" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-16</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:46</v>
+        <v>2:42</v>
       </c>
       <c r="H85" t="str">
-        <v>Bryan Ferry</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-16</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:42</v>
+        <v>3:04</v>
       </c>
       <c r="H86" t="str">
-        <v>Saint Harison</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-16</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:04</v>
+        <v>2:59</v>
       </c>
       <c r="H87" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-16</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:59</v>
+        <v>2:22</v>
       </c>
       <c r="H88" t="str">
-        <v>Catie Turner</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-16</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:22</v>
+        <v>3:53</v>
       </c>
       <c r="H89" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Roxette</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-16</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:53</v>
+        <v>2:28</v>
       </c>
       <c r="H90" t="str">
-        <v>Roxette</v>
+        <v>Marcin</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-16</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:28</v>
+        <v>2:47</v>
       </c>
       <c r="H91" t="str">
-        <v>Marcin</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-16</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:47</v>
+        <v>3:40</v>
       </c>
       <c r="H92" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Laufey</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-16</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:40</v>
+        <v>2:49</v>
       </c>
       <c r="H93" t="str">
-        <v>Laufey</v>
+        <v>Ava Max</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-16</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:49</v>
+        <v>4:49</v>
       </c>
       <c r="H94" t="str">
-        <v>Ava Max</v>
+        <v>U2</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-16</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:49</v>
+        <v>3:35</v>
       </c>
       <c r="H95" t="str">
-        <v>U2</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-16</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:35</v>
+        <v>2:59</v>
       </c>
       <c r="H96" t="str">
-        <v>Taylor Swift</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-16</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:59</v>
+        <v>4:38</v>
       </c>
       <c r="H97" t="str">
-        <v>Kiana Ledé</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-16</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:38</v>
+        <v>3:46</v>
       </c>
       <c r="H98" t="str">
-        <v>Jessie Ware</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-16</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:46</v>
+        <v>3:08</v>
       </c>
       <c r="H99" t="str">
-        <v>Madison Beer</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-16</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:08</v>
+        <v>5:32</v>
       </c>
       <c r="H100" t="str">
-        <v>Sean Stemaly</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-16</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:32</v>
+        <v>4:39</v>
       </c>
       <c r="H101" t="str">
-        <v>earMUSIC</v>
+        <v>georgemichael</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Porch Light</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-16</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G102" t="str">
-        <v>4:39</v>
+        <v>4:22</v>
       </c>
       <c r="H102" t="str">
-        <v>georgemichael</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
       </c>
       <c r="L102" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Porch Light - Noah Kahan</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Porch Light</v>
+        <v>Dry Spell</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
+        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-16</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Great Divide</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G103" t="str">
-        <v>4:22</v>
+        <v>3:17</v>
       </c>
       <c r="H103" t="str">
-        <v>Noah Kahan</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
+        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
       </c>
       <c r="L103" t="str">
-        <v>Porch Light - Noah Kahan</v>
+        <v>Dry Spell - Kacey Musgraves</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Dry Spell</v>
+        <v>The Visitor</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
+        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-16</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Middle of Nowhere</v>
+        <v>The Visitor - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:17</v>
+        <v>3:48</v>
       </c>
       <c r="H104" t="str">
-        <v>Kacey Musgraves</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
+        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
       </c>
       <c r="L104" t="str">
-        <v>Dry Spell - Kacey Musgraves</v>
+        <v>The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>The Visitor</v>
+        <v>I Ain't No Cowboy</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
+        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-16</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Visitor - Single</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G105" t="str">
-        <v>3:48</v>
+        <v>3:13</v>
       </c>
       <c r="H105" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
+        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
       </c>
       <c r="L105" t="str">
-        <v>The Visitor - SIENNA SPIRO</v>
+        <v>I Ain't No Cowboy - Luke Combs</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>I Ain't No Cowboy</v>
+        <v>Can't Sit Still</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
+        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-16</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Way I Am</v>
+        <v>Can't Sit Still - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:13</v>
+        <v>3:35</v>
       </c>
       <c r="H106" t="str">
-        <v>Luke Combs</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
+        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
       </c>
       <c r="L106" t="str">
-        <v>I Ain't No Cowboy - Luke Combs</v>
+        <v>Can't Sit Still - Lainey Wilson</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Can't Sit Still</v>
+        <v>All I Did Was Dream of You (feat. The Marías)</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
+        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-16</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Can't Sit Still - Single</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:35</v>
+        <v>3:43</v>
       </c>
       <c r="H107" t="str">
-        <v>Lainey Wilson</v>
+        <v>beabadoobee</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
+        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
       </c>
       <c r="L107" t="str">
-        <v>Can't Sit Still - Lainey Wilson</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías)</v>
+        <v>Blow My Mind</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
+        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-16</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
+        <v>Sexistential</v>
       </c>
       <c r="G108" t="str">
-        <v>3:43</v>
+        <v>2:57</v>
       </c>
       <c r="H108" t="str">
-        <v>beabadoobee</v>
+        <v>Robyn</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
+        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
       </c>
       <c r="L108" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
+        <v>Blow My Mind - Robyn</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Blow My Mind</v>
+        <v>SATA</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
+        <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-16</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Sexistential</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G109" t="str">
-        <v>2:57</v>
+        <v>3:02</v>
       </c>
       <c r="H109" t="str">
-        <v>Robyn</v>
+        <v>John Summit</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
+        <v>https://music.apple.com/us/album/sata/1874015470</v>
       </c>
       <c r="L109" t="str">
-        <v>Blow My Mind - Robyn</v>
+        <v>SATA - John Summit</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SATA</v>
+        <v>Una Aventura</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/sata/1874015489</v>
+        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-16</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>Una Aventura - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:02</v>
+        <v>3:00</v>
       </c>
       <c r="H110" t="str">
-        <v>John Summit</v>
+        <v>Ozuna</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/sata/1874015470</v>
+        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
       </c>
       <c r="L110" t="str">
-        <v>SATA - John Summit</v>
+        <v>Una Aventura - Ozuna</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Una Aventura</v>
+        <v>Home (feat. Hikaru Utada)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
+        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-16</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Una Aventura - Single</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G111" t="str">
-        <v>3:00</v>
+        <v>3:44</v>
       </c>
       <c r="H111" t="str">
-        <v>Ozuna</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
+        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
       </c>
       <c r="L111" t="str">
-        <v>Una Aventura - Ozuna</v>
+        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>dirty wedding dress</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-16</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Whatever's Clever!</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G112" t="str">
-        <v>3:44</v>
+        <v>4:49</v>
       </c>
       <c r="H112" t="str">
-        <v>Charlie Puth</v>
+        <v>Bleachers</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
       </c>
       <c r="L112" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>dirty wedding dress - Bleachers</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>dirty wedding dress</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-16</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G113" t="str">
-        <v>4:49</v>
+        <v>3:07</v>
       </c>
       <c r="H113" t="str">
-        <v>Bleachers</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L113" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-16</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Age of the Ram</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:07</v>
+        <v>3:13</v>
       </c>
       <c r="H114" t="str">
-        <v>Charley Crockett</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L114" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Trade Places</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-16</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>Monica</v>
       </c>
       <c r="G115" t="str">
-        <v>3:13</v>
+        <v>3:02</v>
       </c>
       <c r="H115" t="str">
-        <v>Grupo Frontera</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L115" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Trade Places</v>
+        <v>Motion Party</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-16</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Monica</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:02</v>
+        <v>1:35</v>
       </c>
       <c r="H116" t="str">
-        <v>Jack Harlow</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L116" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Motion Party</v>
+        <v>Woman</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-16</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Motion Party - Single</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>1:35</v>
+        <v>2:46</v>
       </c>
       <c r="H117" t="str">
-        <v>Bossman Dlow</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L117" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Woman</v>
+        <v>Sunburn</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-16</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Woman - Single</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:46</v>
+        <v>3:05</v>
       </c>
       <c r="H118" t="str">
-        <v>Kane Brown</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L118" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Sunburn</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-16</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Sunburn - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G119" t="str">
-        <v>3:05</v>
+        <v>2:54</v>
       </c>
       <c r="H119" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L119" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Que Te Costó</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-16</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Metamorfosis</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:54</v>
+        <v>2:15</v>
       </c>
       <c r="H120" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L120" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>oooshxt!</v>
+        <v>Cruel World</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-16</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>oooshxt! - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G121" t="str">
-        <v>2:15</v>
+        <v>3:26</v>
       </c>
       <c r="H121" t="str">
-        <v>Samara Cyn</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L121" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Cruel World</v>
+        <v>Star</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-16</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Cruel World</v>
+        <v>Star - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:26</v>
+        <v>3:25</v>
       </c>
       <c r="H122" t="str">
-        <v>Holly Humberstone</v>
+        <v>Iceage</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L122" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Star</v>
+        <v>Get Go</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-16</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Star - Single</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G123" t="str">
-        <v>3:25</v>
+        <v>3:22</v>
       </c>
       <c r="H123" t="str">
-        <v>Iceage</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L123" t="str">
-        <v>Star - Iceage</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Get Go</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-16</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Distracted</v>
       </c>
       <c r="G124" t="str">
-        <v>3:22</v>
+        <v>3:14</v>
       </c>
       <c r="H124" t="str">
-        <v>Arlo Parks</v>
+        <v>Thundercat</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L124" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>ThunderWave</v>
+        <v>Club Song</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-16</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Distracted</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:14</v>
+        <v>2:27</v>
       </c>
       <c r="H125" t="str">
-        <v>Thundercat</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L125" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Club Song</v>
+        <v>Better Man</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-16</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Club Song - Single</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:27</v>
+        <v>2:53</v>
       </c>
       <c r="H126" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>jxdn</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L126" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Better Man</v>
+        <v>sabotage</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-16</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Better Man - Single</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:53</v>
+        <v>2:58</v>
       </c>
       <c r="H127" t="str">
-        <v>jxdn</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L127" t="str">
-        <v>Better Man - jxdn</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>sabotage</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-16</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>sabotage - Single</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:58</v>
+        <v>2:56</v>
       </c>
       <c r="H128" t="str">
-        <v>Natalie Jane</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L128" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>Naked</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-16</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:56</v>
+        <v>3:39</v>
       </c>
       <c r="H129" t="str">
-        <v>WHATMORE</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L129" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Naked</v>
+        <v>Catharina</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-16</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Naked - Single</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:39</v>
+        <v>3:27</v>
       </c>
       <c r="H130" t="str">
-        <v>Kenya Grace</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L130" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Catharina</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-16</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Catharina - Single</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:27</v>
+        <v>3:00</v>
       </c>
       <c r="H131" t="str">
-        <v>Martin Garrix</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L131" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>Trying Times</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-16</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G132" t="str">
-        <v>3:00</v>
+        <v>4:33</v>
       </c>
       <c r="H132" t="str">
-        <v>Chase &amp; Status</v>
+        <v>James Blake</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L132" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Trying Times</v>
+        <v>595</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-16</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Trying Times</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G133" t="str">
-        <v>4:33</v>
+        <v>2:29</v>
       </c>
       <c r="H133" t="str">
-        <v>James Blake</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L133" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>595</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-16</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Soft 2</v>
       </c>
       <c r="G134" t="str">
-        <v>2:29</v>
+        <v>3:50</v>
       </c>
       <c r="H134" t="str">
-        <v>Violet Grohl</v>
+        <v>LANY</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L134" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>CALL ME</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-16</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Soft 2</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:50</v>
+        <v>2:10</v>
       </c>
       <c r="H135" t="str">
-        <v>LANY</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L135" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>CALL ME</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-16</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>CALL ME - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G136" t="str">
-        <v>2:10</v>
+        <v>2:00</v>
       </c>
       <c r="H136" t="str">
-        <v>ALTÉGO</v>
+        <v>Nasty C</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L136" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Mi Amor</v>
+        <v>BOBA</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-16</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Free (Deluxe)</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:00</v>
+        <v>3:00</v>
       </c>
       <c r="H137" t="str">
-        <v>Nasty C</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L137" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>BOBA</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-16</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>BOBA - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G138" t="str">
-        <v>3:00</v>
+        <v>2:38</v>
       </c>
       <c r="H138" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L138" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Video Shoot</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-16</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Skeletor</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:38</v>
+        <v>2:06</v>
       </c>
       <c r="H139" t="str">
-        <v>Chief Keef</v>
+        <v>Shenseea</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L139" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Just Believe</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-16</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:06</v>
+        <v>2:41</v>
       </c>
       <c r="H140" t="str">
-        <v>Shenseea</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L140" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Just Believe</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-16</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Just Believe - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G141" t="str">
-        <v>2:41</v>
+        <v>2:57</v>
       </c>
       <c r="H141" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L141" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Knife In The Heart</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-16</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>The Afterparty</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:57</v>
+        <v>3:09</v>
       </c>
       <c r="H142" t="str">
-        <v>Lykke Li</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L142" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>The Way We Touch</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-16</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G143" t="str">
-        <v>3:09</v>
+        <v>4:06</v>
       </c>
       <c r="H143" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L143" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>DANGEROUS</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-16</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Dear God</v>
       </c>
       <c r="G144" t="str">
-        <v>4:06</v>
+        <v>3:33</v>
       </c>
       <c r="H144" t="str">
-        <v>Magnolia Park</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L144" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>When I Wake Up</v>
+        <v>Breathe</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-16</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Dear God</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:33</v>
+        <v>2:56</v>
       </c>
       <c r="H145" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L145" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Breathe</v>
+        <v>Minty</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-16</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Breathe - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G146" t="str">
-        <v>2:56</v>
+        <v>1:47</v>
       </c>
       <c r="H146" t="str">
-        <v>Malcolm Todd</v>
+        <v>MIKE</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L146" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Minty</v>
+        <v>Earth</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-16</v>
@@ -5964,33 +5964,33 @@
         <v>POMPEII // UTILITY</v>
       </c>
       <c r="G147" t="str">
-        <v>1:47</v>
+        <v>1:37</v>
       </c>
       <c r="H147" t="str">
-        <v>MIKE</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L147" t="str">
-        <v>Minty - MIKE</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Earth</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-16</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G148" t="str">
-        <v>1:37</v>
+        <v>3:42</v>
       </c>
       <c r="H148" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L148" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Drink The Water</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-16</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:42</v>
+        <v>4:32</v>
       </c>
       <c r="H149" t="str">
-        <v>Jack Johnson</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L149" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-16</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>4:32</v>
+        <v>3:32</v>
       </c>
       <c r="H150" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L150" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-16</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:32</v>
+        <v>3:08</v>
       </c>
       <c r="H151" t="str">
-        <v>Carly Pearce</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L151" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Muchacho Alegre</v>
+        <v>Real Slow</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-16</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G152" t="str">
-        <v>3:08</v>
+        <v>3:22</v>
       </c>
       <c r="H152" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L152" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Real Slow</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-16</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Work of Heart</v>
+        <v>As Is</v>
       </c>
       <c r="G153" t="str">
-        <v>3:22</v>
+        <v>2:42</v>
       </c>
       <c r="H153" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L153" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Mountain Girl</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-16</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>As Is</v>
+        <v>American Stories</v>
       </c>
       <c r="G154" t="str">
-        <v>2:42</v>
+        <v>3:31</v>
       </c>
       <c r="H154" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>Rostam</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L154" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Like a Spark</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-16</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>American Stories</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G155" t="str">
-        <v>3:31</v>
+        <v>3:29</v>
       </c>
       <c r="H155" t="str">
-        <v>Rostam</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L155" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Cheesecake</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-16</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G156" t="str">
-        <v>3:29</v>
+        <v>3:04</v>
       </c>
       <c r="H156" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L156" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-16</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>KINDA HARD</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:04</v>
+        <v>3:37</v>
       </c>
       <c r="H157" t="str">
-        <v>Bilmuri</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L157" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Freakin’ Out</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-16</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:37</v>
+        <v>3:03</v>
       </c>
       <c r="H158" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L158" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Name in Vein</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-16</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Name in Vein - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G159" t="str">
-        <v>3:03</v>
+        <v>4:05</v>
       </c>
       <c r="H159" t="str">
-        <v>VOILÀ</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L159" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-16</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Into Oblivion</v>
+        <v>Sweat</v>
       </c>
       <c r="G160" t="str">
-        <v>4:05</v>
+        <v>3:34</v>
       </c>
       <c r="H160" t="str">
-        <v>Lamb of God</v>
+        <v>Melanie C</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L160" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Undefeated Champion</v>
+        <v>Pull Up</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-16</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Sweat</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:34</v>
+        <v>2:35</v>
       </c>
       <c r="H161" t="str">
-        <v>Melanie C</v>
+        <v>Collect 200</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L161" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Pull Up</v>
+        <v>Ranjha</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-16</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Pull Up - Single</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:35</v>
+        <v>3:04</v>
       </c>
       <c r="H162" t="str">
-        <v>Collect 200</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L162" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Ranjha</v>
+        <v>zombies in love</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-16</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Ranjha - Single</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:04</v>
+        <v>2:53</v>
       </c>
       <c r="H163" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>paris jackson</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L163" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>zombies in love</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-16</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>zombies in love - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G164" t="str">
-        <v>2:53</v>
+        <v>4:39</v>
       </c>
       <c r="H164" t="str">
-        <v>paris jackson</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L164" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Days Of Us</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-16</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Full Circle</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:39</v>
+        <v>3:15</v>
       </c>
       <c r="H165" t="str">
-        <v>Tom Misch</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L165" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Life Of A Man</v>
+        <v>Ya No</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-16</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:15</v>
+        <v>3:40</v>
       </c>
       <c r="H166" t="str">
-        <v>1Ski OG</v>
+        <v>Marca MP</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L166" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Ya No</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-16</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Ya No - Single</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:40</v>
+        <v>3:48</v>
       </c>
       <c r="H167" t="str">
-        <v>Marca MP</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L167" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Relieve You</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-16</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:48</v>
+        <v>2:19</v>
       </c>
       <c r="H168" t="str">
-        <v>Spacey Jane</v>
+        <v>4Fargo</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L168" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Relieve You</v>
+        <v>Safety</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-16</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Relieve You - Single</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:19</v>
+        <v>3:18</v>
       </c>
       <c r="H169" t="str">
-        <v>4Fargo</v>
+        <v>Lekan</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L169" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Safety</v>
+        <v>Starlet</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-16</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Safety - Single</v>
+        <v>LK99</v>
       </c>
       <c r="G170" t="str">
-        <v>3:18</v>
+        <v>2:56</v>
       </c>
       <c r="H170" t="str">
-        <v>Lekan</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L170" t="str">
-        <v>Safety - Lekan</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Starlet</v>
+        <v>Physical</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-16</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>LK99</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:56</v>
+        <v>3:52</v>
       </c>
       <c r="H171" t="str">
-        <v>Leven Kali</v>
+        <v>Jacquees</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L171" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Physical</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-16</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Physical - Single</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:52</v>
+        <v>4:29</v>
       </c>
       <c r="H172" t="str">
-        <v>Jacquees</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L172" t="str">
-        <v>Physical - Jacquees</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Regalito</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-16</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G173" t="str">
-        <v>4:29</v>
+        <v>2:41</v>
       </c>
       <c r="H173" t="str">
-        <v>Casper Sage</v>
+        <v>Piso 21</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L173" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Regalito</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-16</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>TRESCENDER</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G174" t="str">
-        <v>2:41</v>
+        <v>4:09</v>
       </c>
       <c r="H174" t="str">
-        <v>Piso 21</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L174" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Cruel Streak</v>
+        <v>Die Young</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-16</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G175" t="str">
-        <v>4:09</v>
+        <v>3:52</v>
       </c>
       <c r="H175" t="str">
-        <v>The Black Crowes</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L175" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Die Young</v>
+        <v>Island Girl</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-16</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Little Wide Open</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:52</v>
+        <v>3:27</v>
       </c>
       <c r="H176" t="str">
-        <v>Kevin Morby</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L176" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Island Girl</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-16</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Island Girl - Single</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:27</v>
+        <v>2:20</v>
       </c>
       <c r="H177" t="str">
-        <v>Pia Mia</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L177" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-16</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:20</v>
+        <v>3:22</v>
       </c>
       <c r="H178" t="str">
-        <v>Claudia Valentina</v>
+        <v>Shaggy</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L178" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-16</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:22</v>
+        <v>3:44</v>
       </c>
       <c r="H179" t="str">
-        <v>Shaggy</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L179" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Tommy’s Song</v>
+        <v>Rainbows</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-16</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Lovers - Single</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:44</v>
+        <v>3:25</v>
       </c>
       <c r="H180" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L180" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Rainbows</v>
+        <v>butterflies</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-16</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Rainbows - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G181" t="str">
-        <v>3:25</v>
+        <v>2:48</v>
       </c>
       <c r="H181" t="str">
-        <v>Allison Russell</v>
+        <v>runo plum</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L181" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>butterflies</v>
+        <v>You're Right</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-16</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Bloom Again - EP</v>
+        <v>You're Right - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:48</v>
+        <v>3:00</v>
       </c>
       <c r="H182" t="str">
-        <v>runo plum</v>
+        <v>Emma Harner</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
       </c>
       <c r="L182" t="str">
-        <v>butterflies - runo plum</v>
+        <v>You're Right - Emma Harner</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You're Right</v>
+        <v>Bible Belt</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-16</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>You're Right - Single</v>
+        <v>Bible Belt - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:00</v>
+        <v>3:34</v>
       </c>
       <c r="H183" t="str">
-        <v>Emma Harner</v>
+        <v>Baby Bugs</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
       </c>
       <c r="L183" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>Bible Belt - Baby Bugs</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Bible Belt</v>
+        <v>Daze</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-16</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Bible Belt - Single</v>
+        <v>Daze - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:34</v>
+        <v>3:22</v>
       </c>
       <c r="H184" t="str">
-        <v>Baby Bugs</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
       </c>
       <c r="L184" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>Daze - Olympia Vitalis</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Daze</v>
+        <v>Passionfruit</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-16</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Daze - Single</v>
+        <v>Passionfruit - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:22</v>
+        <v>3:57</v>
       </c>
       <c r="H185" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
       </c>
       <c r="L185" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>Passionfruit - Anish Kumar</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Passionfruit</v>
+        <v>Madan</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-16</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Passionfruit - Single</v>
+        <v>Madan - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:57</v>
+        <v>2:56</v>
       </c>
       <c r="H186" t="str">
-        <v>Anish Kumar</v>
+        <v>Jonas Blue</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
       </c>
       <c r="L186" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>Madan - Jonas Blue</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Madan</v>
+        <v>Bad Bitch</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-16</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Madan - Single</v>
+        <v>Bad Bitch - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:56</v>
+        <v>2:28</v>
       </c>
       <c r="H187" t="str">
-        <v>Jonas Blue</v>
+        <v>41</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
       </c>
       <c r="L187" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Bad Bitch - 41</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Bad Bitch</v>
+        <v>Shame</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-16</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Devotion [Deluxe]</v>
       </c>
       <c r="G188" t="str">
-        <v>2:28</v>
+        <v>3:36</v>
       </c>
       <c r="H188" t="str">
-        <v>41</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
       </c>
       <c r="L188" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Shame - Sunday (1994)</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Shame</v>
+        <v>teach you to love me</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-16</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>teach you to love me - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:36</v>
+        <v>3:09</v>
       </c>
       <c r="H189" t="str">
-        <v>Sunday (1994)</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
       </c>
       <c r="L189" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>teach you to love me - Hailey Picardi</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>teach you to love me</v>
+        <v>The Fix</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-16</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>teach you to love me - Single</v>
+        <v>The Fix - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:09</v>
+        <v>2:42</v>
       </c>
       <c r="H190" t="str">
-        <v>Hailey Picardi</v>
+        <v>Baby J</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
       </c>
       <c r="L190" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>The Fix - Baby J</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>The Fix</v>
+        <v>Hanging on Hope</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-16</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>The Fix - Single</v>
+        <v>Hanging on Hope - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:42</v>
+        <v>3:43</v>
       </c>
       <c r="H191" t="str">
-        <v>Baby J</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
       </c>
       <c r="L191" t="str">
-        <v>The Fix - Baby J</v>
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Hanging on Hope</v>
+        <v>I Know What to Say Now</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-16</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>I Know What to Say Now - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:43</v>
+        <v>3:18</v>
       </c>
       <c r="H192" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Active Child</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
       </c>
       <c r="L192" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>I Know What to Say Now - Active Child</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>I Know What to Say Now</v>
+        <v>Feel Something</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-16</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Feel Something - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:18</v>
+        <v>3:09</v>
       </c>
       <c r="H193" t="str">
-        <v>Active Child</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
       </c>
       <c r="L193" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>Feel Something - Baby Queen</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Feel Something</v>
+        <v>You Or Me</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-16</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Feel Something - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G194" t="str">
-        <v>3:09</v>
+        <v>5:28</v>
       </c>
       <c r="H194" t="str">
-        <v>Baby Queen</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
       </c>
       <c r="L194" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>You Or Me - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>You Or Me</v>
+        <v>Mortercheyn</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-16</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Coronach</v>
       </c>
       <c r="G195" t="str">
-        <v>5:28</v>
+        <v>4:18</v>
       </c>
       <c r="H195" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Hellripper</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
       </c>
       <c r="L195" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>Mortercheyn - Hellripper</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Mortercheyn</v>
+        <v>Rip The God</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-16</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Coronach</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G196" t="str">
-        <v>4:18</v>
+        <v>5:20</v>
       </c>
       <c r="H196" t="str">
-        <v>Hellripper</v>
+        <v>Melvins</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
       </c>
       <c r="L196" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>Rip The God - Melvins</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Rip The God</v>
+        <v>Who We Are</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-16</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Who We Are - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>5:20</v>
+        <v>2:10</v>
       </c>
       <c r="H197" t="str">
-        <v>Melvins</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
       </c>
       <c r="L197" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Who We Are - Kaleena Zanders</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Who We Are</v>
+        <v>Reels in 360</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-16</v>
@@ -7899,68 +7899,30 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Who We Are - Single</v>
+        <v>Dying Is The Internet</v>
       </c>
       <c r="G198" t="str">
-        <v>2:10</v>
+        <v>4:37</v>
       </c>
       <c r="H198" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Simo Cell</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
       <c r="L198" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Reels in 360</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Dying Is The Internet</v>
-      </c>
-      <c r="G199" t="str">
-        <v>4:37</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Simo Cell</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
-      </c>
-      <c r="L199" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week03/titles.xlsx
+++ b/data/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L214"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>שלום ממן - יא רייח</v>
       </c>
       <c r="B2" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410031&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-16</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>4:09</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Mei Semones</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>שלום ממן - יא רייח</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>שלו משען - אגם של טעויות</v>
       </c>
       <c r="B3" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410030&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-16</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>2:08</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>The Lemon Twigs</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>שלו משען - אגם של טעויות</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>שיר מזרחי &amp; משה זאודה - יש לנו כאב</v>
       </c>
       <c r="B4" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410029&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-16</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>2:57</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Natalie Jane</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>שיר מזרחי &amp; משה זאודה - יש לנו כאב</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>קיליאן ג'אמי - צלקת</v>
       </c>
       <c r="B5" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410028&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-16</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>3:13</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Eurovision Song Contest</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>קיליאן ג'אמי - צלקת</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>צחי אלוש - טיקי טקה</v>
       </c>
       <c r="B6" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410027&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-16</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>4:12</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>David Gilmour</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>צחי אלוש - טיקי טקה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>עידן משה - ריגוש וכאב</v>
       </c>
       <c r="B7" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410026&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-16</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>3:57</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Far Caspian</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>עידן משה - ריגוש וכאב</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>עידו כנפי - פרפרים בבטן</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410025&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-16</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>3:34</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>Celine Dion</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>עידו כנפי - פרפרים בבטן</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>סגיב כהן - חסד יסובבנו</v>
       </c>
       <c r="B9" t="str">
-        <v>9 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410024&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-16</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>3:48</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>Harry Styles</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>סגיב כהן - חסד יסובבנו</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>נתנאל מלכה - בלעדייך</v>
       </c>
       <c r="B10" t="str">
-        <v>9 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410023&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-16</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>4:58</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>נתנאל מלכה - בלעדייך</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>מיכה ינון - מחרוזת חזון אחרית הימים 2026</v>
       </c>
       <c r="B11" t="str">
-        <v>9 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410022&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-16</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>2:33</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>Ellise</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>מיכה ינון - מחרוזת חזון אחרית הימים 2026</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>יהורם גאון - עד עולם</v>
       </c>
       <c r="B12" t="str">
-        <v>9 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410021&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-16</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>5:01</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>The Doobie Brothers</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>יהורם גאון - עד עולם</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום</v>
       </c>
       <c r="B13" t="str">
-        <v>9 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410020&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-16</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>4:56</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>גבריאל שרם - שוברת גלים</v>
       </c>
       <c r="B14" t="str">
-        <v>9 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410019&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-16</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>2:54</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>Bebe Rexha</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>גבריאל שרם - שוברת גלים</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>אורי ספז - תפילה שלך</v>
       </c>
       <c r="B15" t="str">
-        <v>9 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410018&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-16</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v>2:46</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>NathanEvanss</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>אורי ספז - תפילה שלך</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>אבי שפרונג - הבית שלי</v>
       </c>
       <c r="B16" t="str">
-        <v>9 days ago</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410017&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-16</v>
@@ -983,16 +983,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="G16" t="str">
-        <v>2:56</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>R3HAB</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>אבי שפרונג - הבית שלי</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B17" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-16</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:21</v>
+        <v>4:09</v>
       </c>
       <c r="H17" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-16</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:16</v>
+        <v>2:08</v>
       </c>
       <c r="H18" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-16</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:41</v>
+        <v>2:57</v>
       </c>
       <c r="H19" t="str">
-        <v>Johnny Orlando</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B20" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-16</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:29</v>
+        <v>3:13</v>
       </c>
       <c r="H20" t="str">
-        <v>Russell Dickerson</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B21" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-16</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:43</v>
+        <v>4:12</v>
       </c>
       <c r="H21" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B22" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-16</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:46</v>
+        <v>3:57</v>
       </c>
       <c r="H22" t="str">
-        <v>Matt Hansen</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B23" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-16</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H23" t="str">
-        <v>Mike Posner</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B24" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-16</v>
@@ -1290,10 +1290,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:23</v>
+        <v>3:48</v>
       </c>
       <c r="H24" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-16</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:39</v>
+        <v>4:58</v>
       </c>
       <c r="H25" t="str">
-        <v>almost monday</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-16</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:04</v>
+        <v>2:33</v>
       </c>
       <c r="H26" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>Ellise</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B27" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-16</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:25</v>
+        <v>5:01</v>
       </c>
       <c r="H27" t="str">
-        <v>vaultboy</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B28" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-16</v>
@@ -1442,10 +1442,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:49</v>
+        <v>4:56</v>
       </c>
       <c r="H28" t="str">
-        <v>The Warning</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B29" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-16</v>
@@ -1480,10 +1480,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:14</v>
+        <v>2:54</v>
       </c>
       <c r="H29" t="str">
-        <v>aron!</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B30" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-16</v>
@@ -1518,10 +1518,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:43</v>
+        <v>2:46</v>
       </c>
       <c r="H30" t="str">
-        <v>Bazzi</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-16</v>
@@ -1556,10 +1556,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:43</v>
+        <v>2:56</v>
       </c>
       <c r="H31" t="str">
-        <v>Sting</v>
+        <v>R3HAB</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B32" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-16</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:44</v>
+        <v>3:21</v>
       </c>
       <c r="H32" t="str">
-        <v>Dean Lewis</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-16</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:37</v>
+        <v>3:16</v>
       </c>
       <c r="H33" t="str">
-        <v>Jessie Ware</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B34" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-16</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:52</v>
+        <v>2:41</v>
       </c>
       <c r="H34" t="str">
-        <v>Cannons</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-16</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:13</v>
+        <v>2:29</v>
       </c>
       <c r="H35" t="str">
-        <v>Kim Petras</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B36" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-16</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:19</v>
+        <v>2:43</v>
       </c>
       <c r="H36" t="str">
-        <v>Vanessa Carlton</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-16</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:31</v>
+        <v>3:46</v>
       </c>
       <c r="H37" t="str">
-        <v>Kiana Ledé</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-16</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:43</v>
+        <v>4:01</v>
       </c>
       <c r="H38" t="str">
-        <v>Ringo Starr</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-16</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:10</v>
+        <v>3:23</v>
       </c>
       <c r="H39" t="str">
-        <v>Maya Hawke</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B40" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-16</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:55</v>
+        <v>3:39</v>
       </c>
       <c r="H40" t="str">
-        <v>Armin van Buuren</v>
+        <v>almost monday</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-16</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:52</v>
+        <v>3:04</v>
       </c>
       <c r="H41" t="str">
-        <v>Demi Lovato</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-16</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:53</v>
+        <v>3:25</v>
       </c>
       <c r="H42" t="str">
-        <v>Peter Gabriel</v>
+        <v>vaultboy</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-16</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:30</v>
+        <v>3:49</v>
       </c>
       <c r="H43" t="str">
-        <v>Jessie J</v>
+        <v>The Warning</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-16</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>5:18</v>
+        <v>2:14</v>
       </c>
       <c r="H44" t="str">
-        <v>Harry Styles</v>
+        <v>aron!</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-16</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>7:20</v>
+        <v>2:43</v>
       </c>
       <c r="H45" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Bazzi</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B46" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-16</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:01</v>
+        <v>4:43</v>
       </c>
       <c r="H46" t="str">
-        <v>BRITs</v>
+        <v>Sting</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-16</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:31</v>
+        <v>2:44</v>
       </c>
       <c r="H47" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-16</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:00</v>
+        <v>4:37</v>
       </c>
       <c r="H48" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B49" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-16</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:11</v>
+        <v>4:52</v>
       </c>
       <c r="H49" t="str">
-        <v>The Kiffness</v>
+        <v>Cannons</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B50" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-16</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:32</v>
+        <v>2:13</v>
       </c>
       <c r="H50" t="str">
-        <v>Lauv</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-16</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>5:03</v>
+        <v>3:19</v>
       </c>
       <c r="H51" t="str">
-        <v>RAYE</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-16</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:50</v>
+        <v>2:31</v>
       </c>
       <c r="H52" t="str">
-        <v>Armik</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-16</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:53</v>
+        <v>2:43</v>
       </c>
       <c r="H53" t="str">
-        <v>Scorpions</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-16</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:04</v>
+        <v>3:10</v>
       </c>
       <c r="H54" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-16</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:32</v>
+        <v>3:55</v>
       </c>
       <c r="H55" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-16</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:47</v>
+        <v>3:52</v>
       </c>
       <c r="H56" t="str">
-        <v>Girl Tones</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-16</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:40</v>
+        <v>2:53</v>
       </c>
       <c r="H57" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-16</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:05</v>
+        <v>4:30</v>
       </c>
       <c r="H58" t="str">
-        <v>HAUSER</v>
+        <v>Jessie J</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-16</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:59</v>
+        <v>5:18</v>
       </c>
       <c r="H59" t="str">
-        <v>Queen Official</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-16</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:55</v>
+        <v>7:20</v>
       </c>
       <c r="H60" t="str">
-        <v>Tenille Townes</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-16</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>5:12</v>
+        <v>3:01</v>
       </c>
       <c r="H61" t="str">
-        <v>Self Esteem</v>
+        <v>BRITs</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-16</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:47</v>
+        <v>3:31</v>
       </c>
       <c r="H62" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-16</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:18</v>
+        <v>3:00</v>
       </c>
       <c r="H63" t="str">
-        <v>Em Beihold</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-16</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:50</v>
+        <v>3:11</v>
       </c>
       <c r="H64" t="str">
-        <v>Michael Bublé</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-16</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H65" t="str">
-        <v>MyKey</v>
+        <v>Lauv</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-16</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:36</v>
+        <v>5:03</v>
       </c>
       <c r="H66" t="str">
-        <v>Max McNown</v>
+        <v>RAYE</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-16</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:34</v>
+        <v>4:50</v>
       </c>
       <c r="H67" t="str">
-        <v>Megan Moroney</v>
+        <v>Armik</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-16</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:03</v>
+        <v>4:53</v>
       </c>
       <c r="H68" t="str">
-        <v>ERNEST</v>
+        <v>Scorpions</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-16</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:31</v>
+        <v>3:04</v>
       </c>
       <c r="H69" t="str">
-        <v>Bruno Mars</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-16</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:22</v>
+        <v>4:32</v>
       </c>
       <c r="H70" t="str">
-        <v>BLACKPINK</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-16</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>5:49</v>
+        <v>3:47</v>
       </c>
       <c r="H71" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-16</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:47</v>
+        <v>3:40</v>
       </c>
       <c r="H72" t="str">
-        <v>Nessa Barrett</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-16</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:20</v>
+        <v>4:05</v>
       </c>
       <c r="H73" t="str">
-        <v>Towa Bird</v>
+        <v>HAUSER</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-16</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:18</v>
+        <v>2:59</v>
       </c>
       <c r="H74" t="str">
-        <v>Ty Myers</v>
+        <v>Queen Official</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-16</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:39</v>
+        <v>3:55</v>
       </c>
       <c r="H75" t="str">
-        <v>kenzie</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-16</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:52</v>
+        <v>5:12</v>
       </c>
       <c r="H76" t="str">
-        <v>Leanna Crawford</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-16</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:01</v>
+        <v>3:47</v>
       </c>
       <c r="H77" t="str">
-        <v>Bryan Adams</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-16</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:54</v>
+        <v>3:18</v>
       </c>
       <c r="H78" t="str">
-        <v>CHESCA</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-16</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:03</v>
+        <v>3:50</v>
       </c>
       <c r="H79" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-16</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:50</v>
+        <v>3:24</v>
       </c>
       <c r="H80" t="str">
-        <v>earMUSIC</v>
+        <v>MyKey</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-16</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:06</v>
+        <v>2:36</v>
       </c>
       <c r="H81" t="str">
-        <v>Y2K</v>
+        <v>Max McNown</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-16</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:43</v>
+        <v>3:34</v>
       </c>
       <c r="H82" t="str">
-        <v>Lainey Wilson</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-16</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>6:21</v>
+        <v>4:03</v>
       </c>
       <c r="H83" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>ERNEST</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-16</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:46</v>
+        <v>3:31</v>
       </c>
       <c r="H84" t="str">
-        <v>Bryan Ferry</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-16</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:42</v>
+        <v>3:22</v>
       </c>
       <c r="H85" t="str">
-        <v>Saint Harison</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-16</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:04</v>
+        <v>5:49</v>
       </c>
       <c r="H86" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-16</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:59</v>
+        <v>3:47</v>
       </c>
       <c r="H87" t="str">
-        <v>Catie Turner</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-16</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:22</v>
+        <v>2:20</v>
       </c>
       <c r="H88" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-16</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:53</v>
+        <v>4:18</v>
       </c>
       <c r="H89" t="str">
-        <v>Roxette</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-16</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:28</v>
+        <v>2:39</v>
       </c>
       <c r="H90" t="str">
-        <v>Marcin</v>
+        <v>kenzie</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-16</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:47</v>
+        <v>3:52</v>
       </c>
       <c r="H91" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-16</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:40</v>
+        <v>4:01</v>
       </c>
       <c r="H92" t="str">
-        <v>Laufey</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-16</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:49</v>
+        <v>2:54</v>
       </c>
       <c r="H93" t="str">
-        <v>Ava Max</v>
+        <v>CHESCA</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-16</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>4:49</v>
+        <v>4:03</v>
       </c>
       <c r="H94" t="str">
-        <v>U2</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-16</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:35</v>
+        <v>4:50</v>
       </c>
       <c r="H95" t="str">
-        <v>Taylor Swift</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-16</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:59</v>
+        <v>3:06</v>
       </c>
       <c r="H96" t="str">
-        <v>Kiana Ledé</v>
+        <v>Y2K</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-16</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:38</v>
+        <v>2:43</v>
       </c>
       <c r="H97" t="str">
-        <v>Jessie Ware</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-16</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:46</v>
+        <v>6:21</v>
       </c>
       <c r="H98" t="str">
-        <v>Madison Beer</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-16</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:08</v>
+        <v>2:46</v>
       </c>
       <c r="H99" t="str">
-        <v>Sean Stemaly</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-16</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:32</v>
+        <v>2:42</v>
       </c>
       <c r="H100" t="str">
-        <v>earMUSIC</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-16</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:39</v>
+        <v>3:04</v>
       </c>
       <c r="H101" t="str">
-        <v>georgemichael</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Porch Light</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-16</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>The Great Divide</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>4:22</v>
+        <v>2:59</v>
       </c>
       <c r="H102" t="str">
-        <v>Noah Kahan</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Porch Light - Noah Kahan</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Dry Spell</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-16</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Middle of Nowhere</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:17</v>
+        <v>2:22</v>
       </c>
       <c r="H103" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Dry Spell - Kacey Musgraves</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>The Visitor</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-16</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Visitor - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:48</v>
+        <v>3:53</v>
       </c>
       <c r="H104" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Roxette</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>The Visitor - SIENNA SPIRO</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>I Ain't No Cowboy</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-16</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Way I Am</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>3:13</v>
+        <v>2:28</v>
       </c>
       <c r="H105" t="str">
-        <v>Luke Combs</v>
+        <v>Marcin</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>I Ain't No Cowboy - Luke Combs</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Can't Sit Still</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-16</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Can't Sit Still - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:35</v>
+        <v>2:47</v>
       </c>
       <c r="H106" t="str">
-        <v>Lainey Wilson</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Can't Sit Still - Lainey Wilson</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-16</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:43</v>
+        <v>3:40</v>
       </c>
       <c r="H107" t="str">
-        <v>beabadoobee</v>
+        <v>Laufey</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Blow My Mind</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-16</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Sexistential</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:57</v>
+        <v>2:49</v>
       </c>
       <c r="H108" t="str">
-        <v>Robyn</v>
+        <v>Ava Max</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>Blow My Mind - Robyn</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SATA</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/sata/1874015489</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-16</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:02</v>
+        <v>4:49</v>
       </c>
       <c r="H109" t="str">
-        <v>John Summit</v>
+        <v>U2</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/sata/1874015470</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>SATA - John Summit</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Una Aventura</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-16</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Una Aventura - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>3:00</v>
+        <v>3:35</v>
       </c>
       <c r="H110" t="str">
-        <v>Ozuna</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>Una Aventura - Ozuna</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-16</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Whatever's Clever!</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G111" t="str">
-        <v>3:44</v>
+        <v>2:59</v>
       </c>
       <c r="H111" t="str">
-        <v>Charlie Puth</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>dirty wedding dress</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-16</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>everyone for ten minutes</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G112" t="str">
-        <v>4:49</v>
+        <v>4:38</v>
       </c>
       <c r="H112" t="str">
-        <v>Bleachers</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-16</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Age of the Ram</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G113" t="str">
-        <v>3:07</v>
+        <v>3:46</v>
       </c>
       <c r="H113" t="str">
-        <v>Charley Crockett</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v/>
       </c>
       <c r="L113" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-16</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G114" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H114" t="str">
-        <v>Grupo Frontera</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v/>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v/>
       </c>
       <c r="L114" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Trade Places</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-16</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Monica</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G115" t="str">
-        <v>3:02</v>
+        <v>5:32</v>
       </c>
       <c r="H115" t="str">
-        <v>Jack Harlow</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v/>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v/>
       </c>
       <c r="L115" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Motion Party</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-16</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Motion Party - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G116" t="str">
-        <v>1:35</v>
+        <v>4:39</v>
       </c>
       <c r="H116" t="str">
-        <v>Bossman Dlow</v>
+        <v>georgemichael</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v/>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v/>
       </c>
       <c r="L116" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Woman</v>
+        <v>Riptides</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-16</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Woman - Single</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G117" t="str">
-        <v>2:46</v>
+        <v>3:17</v>
       </c>
       <c r="H117" t="str">
-        <v>Kane Brown</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L117" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Sunburn</v>
+        <v>Porch Light</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-16</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Sunburn - Single</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G118" t="str">
-        <v>3:05</v>
+        <v>4:22</v>
       </c>
       <c r="H118" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
       </c>
       <c r="L118" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Porch Light - Noah Kahan</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Que Te Costó</v>
+        <v>Dry Spell</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-16</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Metamorfosis</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G119" t="str">
-        <v>2:54</v>
+        <v>3:17</v>
       </c>
       <c r="H119" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
       </c>
       <c r="L119" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>Dry Spell - Kacey Musgraves</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>oooshxt!</v>
+        <v>The Visitor</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-16</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>oooshxt! - Single</v>
+        <v>The Visitor - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:15</v>
+        <v>3:48</v>
       </c>
       <c r="H120" t="str">
-        <v>Samara Cyn</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
       </c>
       <c r="L120" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Cruel World</v>
+        <v>I Ain't No Cowboy</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-16</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Cruel World</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G121" t="str">
-        <v>3:26</v>
+        <v>3:13</v>
       </c>
       <c r="H121" t="str">
-        <v>Holly Humberstone</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
       </c>
       <c r="L121" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>I Ain't No Cowboy - Luke Combs</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Star</v>
+        <v>Can't Sit Still</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-16</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Star - Single</v>
+        <v>Can't Sit Still - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:25</v>
+        <v>3:35</v>
       </c>
       <c r="H122" t="str">
-        <v>Iceage</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
       </c>
       <c r="L122" t="str">
-        <v>Star - Iceage</v>
+        <v>Can't Sit Still - Lainey Wilson</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Get Go</v>
+        <v>All I Did Was Dream of You (feat. The Marías)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-16</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Ambiguous Desire</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:22</v>
+        <v>3:43</v>
       </c>
       <c r="H123" t="str">
-        <v>Arlo Parks</v>
+        <v>beabadoobee</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
       </c>
       <c r="L123" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>ThunderWave</v>
+        <v>Blow My Mind</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-16</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Distracted</v>
+        <v>Sexistential</v>
       </c>
       <c r="G124" t="str">
-        <v>3:14</v>
+        <v>2:57</v>
       </c>
       <c r="H124" t="str">
-        <v>Thundercat</v>
+        <v>Robyn</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
       </c>
       <c r="L124" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Blow My Mind - Robyn</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Club Song</v>
+        <v>SATA</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-16</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Club Song - Single</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G125" t="str">
-        <v>2:27</v>
+        <v>3:02</v>
       </c>
       <c r="H125" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>John Summit</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/sata/1874015470</v>
       </c>
       <c r="L125" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>SATA - John Summit</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Better Man</v>
+        <v>Una Aventura</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-16</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Better Man - Single</v>
+        <v>Una Aventura - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:53</v>
+        <v>3:00</v>
       </c>
       <c r="H126" t="str">
-        <v>jxdn</v>
+        <v>Ozuna</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
       </c>
       <c r="L126" t="str">
-        <v>Better Man - jxdn</v>
+        <v>Una Aventura - Ozuna</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>sabotage</v>
+        <v>Home (feat. Hikaru Utada)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-16</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>sabotage - Single</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G127" t="str">
-        <v>2:58</v>
+        <v>3:44</v>
       </c>
       <c r="H127" t="str">
-        <v>Natalie Jane</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
       </c>
       <c r="L127" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>dirty wedding dress</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-16</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G128" t="str">
-        <v>2:56</v>
+        <v>4:49</v>
       </c>
       <c r="H128" t="str">
-        <v>WHATMORE</v>
+        <v>Bleachers</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
       </c>
       <c r="L128" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>dirty wedding dress - Bleachers</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Naked</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-16</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Naked - Single</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G129" t="str">
-        <v>3:39</v>
+        <v>3:07</v>
       </c>
       <c r="H129" t="str">
-        <v>Kenya Grace</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L129" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Catharina</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-16</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Catharina - Single</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:27</v>
+        <v>3:13</v>
       </c>
       <c r="H130" t="str">
-        <v>Martin Garrix</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L130" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>Trade Places</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-16</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>Monica</v>
       </c>
       <c r="G131" t="str">
-        <v>3:00</v>
+        <v>3:02</v>
       </c>
       <c r="H131" t="str">
-        <v>Chase &amp; Status</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L131" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Trying Times</v>
+        <v>Motion Party</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-16</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Trying Times</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:33</v>
+        <v>1:35</v>
       </c>
       <c r="H132" t="str">
-        <v>James Blake</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L132" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>595</v>
+        <v>Woman</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-16</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:29</v>
+        <v>2:46</v>
       </c>
       <c r="H133" t="str">
-        <v>Violet Grohl</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L133" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>Sunburn</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-16</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Soft 2</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:50</v>
+        <v>3:05</v>
       </c>
       <c r="H134" t="str">
-        <v>LANY</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L134" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>CALL ME</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-16</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>CALL ME - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G135" t="str">
-        <v>2:10</v>
+        <v>2:54</v>
       </c>
       <c r="H135" t="str">
-        <v>ALTÉGO</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L135" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Mi Amor</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-16</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Free (Deluxe)</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:00</v>
+        <v>2:15</v>
       </c>
       <c r="H136" t="str">
-        <v>Nasty C</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L136" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>BOBA</v>
+        <v>Cruel World</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-16</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>BOBA - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G137" t="str">
-        <v>3:00</v>
+        <v>3:26</v>
       </c>
       <c r="H137" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L137" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Video Shoot</v>
+        <v>Star</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-16</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Skeletor</v>
+        <v>Star - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:38</v>
+        <v>3:25</v>
       </c>
       <c r="H138" t="str">
-        <v>Chief Keef</v>
+        <v>Iceage</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L138" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Get Go</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-16</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G139" t="str">
-        <v>2:06</v>
+        <v>3:22</v>
       </c>
       <c r="H139" t="str">
-        <v>Shenseea</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L139" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Just Believe</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-16</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Just Believe - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G140" t="str">
-        <v>2:41</v>
+        <v>3:14</v>
       </c>
       <c r="H140" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Thundercat</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L140" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Knife In The Heart</v>
+        <v>Club Song</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-16</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>The Afterparty</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:57</v>
+        <v>2:27</v>
       </c>
       <c r="H141" t="str">
-        <v>Lykke Li</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L141" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>The Way We Touch</v>
+        <v>Better Man</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-16</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:09</v>
+        <v>2:53</v>
       </c>
       <c r="H142" t="str">
-        <v>Charlotte Cardin</v>
+        <v>jxdn</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L142" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>DANGEROUS</v>
+        <v>sabotage</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-16</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>4:06</v>
+        <v>2:58</v>
       </c>
       <c r="H143" t="str">
-        <v>Magnolia Park</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L143" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>When I Wake Up</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-16</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Dear God</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:33</v>
+        <v>2:56</v>
       </c>
       <c r="H144" t="str">
-        <v>The Pretty Reckless</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L144" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Breathe</v>
+        <v>Naked</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-16</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Breathe - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:56</v>
+        <v>3:39</v>
       </c>
       <c r="H145" t="str">
-        <v>Malcolm Todd</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L145" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Minty</v>
+        <v>Catharina</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-16</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>1:47</v>
+        <v>3:27</v>
       </c>
       <c r="H146" t="str">
-        <v>MIKE</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L146" t="str">
-        <v>Minty - MIKE</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Earth</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-16</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>1:37</v>
+        <v>3:00</v>
       </c>
       <c r="H147" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L147" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drink The Water</v>
+        <v>Trying Times</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-16</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Trying Times</v>
       </c>
       <c r="G148" t="str">
-        <v>3:42</v>
+        <v>4:33</v>
       </c>
       <c r="H148" t="str">
-        <v>Jack Johnson</v>
+        <v>James Blake</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L148" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>595</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-16</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G149" t="str">
-        <v>4:32</v>
+        <v>2:29</v>
       </c>
       <c r="H149" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L149" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-16</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>Soft 2</v>
       </c>
       <c r="G150" t="str">
-        <v>3:32</v>
+        <v>3:50</v>
       </c>
       <c r="H150" t="str">
-        <v>Carly Pearce</v>
+        <v>LANY</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L150" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Muchacho Alegre</v>
+        <v>CALL ME</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-16</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:08</v>
+        <v>2:10</v>
       </c>
       <c r="H151" t="str">
-        <v>Luis R Conriquez</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L151" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Real Slow</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-16</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Work of Heart</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G152" t="str">
-        <v>3:22</v>
+        <v>2:00</v>
       </c>
       <c r="H152" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Nasty C</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L152" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Mountain Girl</v>
+        <v>BOBA</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-16</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>As Is</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:42</v>
+        <v>3:00</v>
       </c>
       <c r="H153" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L153" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Like a Spark</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-16</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>American Stories</v>
+        <v>Skeletor</v>
       </c>
       <c r="G154" t="str">
-        <v>3:31</v>
+        <v>2:38</v>
       </c>
       <c r="H154" t="str">
-        <v>Rostam</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L154" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Cheesecake</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-16</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:29</v>
+        <v>2:06</v>
       </c>
       <c r="H155" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Shenseea</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L155" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Just Believe</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-16</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>KINDA HARD</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:04</v>
+        <v>2:41</v>
       </c>
       <c r="H156" t="str">
-        <v>Bilmuri</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L156" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Freakin’ Out</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-16</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G157" t="str">
-        <v>3:37</v>
+        <v>2:57</v>
       </c>
       <c r="H157" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L157" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Name in Vein</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-16</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Name in Vein - Single</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:03</v>
+        <v>3:09</v>
       </c>
       <c r="H158" t="str">
-        <v>VOILÀ</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L158" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-16</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Into Oblivion</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G159" t="str">
-        <v>4:05</v>
+        <v>4:06</v>
       </c>
       <c r="H159" t="str">
-        <v>Lamb of God</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L159" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Undefeated Champion</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-16</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Sweat</v>
+        <v>Dear God</v>
       </c>
       <c r="G160" t="str">
-        <v>3:34</v>
+        <v>3:33</v>
       </c>
       <c r="H160" t="str">
-        <v>Melanie C</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L160" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Pull Up</v>
+        <v>Breathe</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-16</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Pull Up - Single</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:35</v>
+        <v>2:56</v>
       </c>
       <c r="H161" t="str">
-        <v>Collect 200</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L161" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Ranjha</v>
+        <v>Minty</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-16</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Ranjha - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G162" t="str">
-        <v>3:04</v>
+        <v>1:47</v>
       </c>
       <c r="H162" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>MIKE</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L162" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>zombies in love</v>
+        <v>Earth</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-16</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>zombies in love - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G163" t="str">
-        <v>2:53</v>
+        <v>1:37</v>
       </c>
       <c r="H163" t="str">
-        <v>paris jackson</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L163" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Days Of Us</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-16</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Full Circle</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G164" t="str">
-        <v>4:39</v>
+        <v>3:42</v>
       </c>
       <c r="H164" t="str">
-        <v>Tom Misch</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L164" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Life Of A Man</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-16</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:15</v>
+        <v>4:32</v>
       </c>
       <c r="H165" t="str">
-        <v>1Ski OG</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L165" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Ya No</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-16</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Ya No - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:40</v>
+        <v>3:32</v>
       </c>
       <c r="H166" t="str">
-        <v>Marca MP</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L166" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-16</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:48</v>
+        <v>3:08</v>
       </c>
       <c r="H167" t="str">
-        <v>Spacey Jane</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L167" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Relieve You</v>
+        <v>Real Slow</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-16</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Relieve You - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G168" t="str">
-        <v>2:19</v>
+        <v>3:22</v>
       </c>
       <c r="H168" t="str">
-        <v>4Fargo</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L168" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Safety</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-16</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Safety - Single</v>
+        <v>As Is</v>
       </c>
       <c r="G169" t="str">
-        <v>3:18</v>
+        <v>2:42</v>
       </c>
       <c r="H169" t="str">
-        <v>Lekan</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L169" t="str">
-        <v>Safety - Lekan</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Starlet</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-16</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>LK99</v>
+        <v>American Stories</v>
       </c>
       <c r="G170" t="str">
-        <v>2:56</v>
+        <v>3:31</v>
       </c>
       <c r="H170" t="str">
-        <v>Leven Kali</v>
+        <v>Rostam</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L170" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Physical</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-16</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Physical - Single</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G171" t="str">
-        <v>3:52</v>
+        <v>3:29</v>
       </c>
       <c r="H171" t="str">
-        <v>Jacquees</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L171" t="str">
-        <v>Physical - Jacquees</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-16</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G172" t="str">
-        <v>4:29</v>
+        <v>3:04</v>
       </c>
       <c r="H172" t="str">
-        <v>Casper Sage</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L172" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Regalito</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-16</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>TRESCENDER</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:41</v>
+        <v>3:37</v>
       </c>
       <c r="H173" t="str">
-        <v>Piso 21</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L173" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Cruel Streak</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-16</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>4:09</v>
+        <v>3:03</v>
       </c>
       <c r="H174" t="str">
-        <v>The Black Crowes</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L174" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Die Young</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-16</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Little Wide Open</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G175" t="str">
-        <v>3:52</v>
+        <v>4:05</v>
       </c>
       <c r="H175" t="str">
-        <v>Kevin Morby</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L175" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Island Girl</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-16</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Island Girl - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G176" t="str">
-        <v>3:27</v>
+        <v>3:34</v>
       </c>
       <c r="H176" t="str">
-        <v>Pia Mia</v>
+        <v>Melanie C</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L176" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Pull Up</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-16</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:20</v>
+        <v>2:35</v>
       </c>
       <c r="H177" t="str">
-        <v>Claudia Valentina</v>
+        <v>Collect 200</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L177" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>Ranjha</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-16</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:22</v>
+        <v>3:04</v>
       </c>
       <c r="H178" t="str">
-        <v>Shaggy</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L178" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Tommy’s Song</v>
+        <v>zombies in love</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-16</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Lovers - Single</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:44</v>
+        <v>2:53</v>
       </c>
       <c r="H179" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>paris jackson</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L179" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Rainbows</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-16</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Rainbows - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G180" t="str">
-        <v>3:25</v>
+        <v>4:39</v>
       </c>
       <c r="H180" t="str">
-        <v>Allison Russell</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L180" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>butterflies</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-16</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:48</v>
+        <v>3:15</v>
       </c>
       <c r="H181" t="str">
-        <v>runo plum</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L181" t="str">
-        <v>butterflies - runo plum</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You're Right</v>
+        <v>Ya No</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-16</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>You're Right - Single</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:00</v>
+        <v>3:40</v>
       </c>
       <c r="H182" t="str">
-        <v>Emma Harner</v>
+        <v>Marca MP</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L182" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Bible Belt</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-16</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Bible Belt - Single</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:34</v>
+        <v>3:48</v>
       </c>
       <c r="H183" t="str">
-        <v>Baby Bugs</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L183" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Daze</v>
+        <v>Relieve You</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-16</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Daze - Single</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:22</v>
+        <v>2:19</v>
       </c>
       <c r="H184" t="str">
-        <v>Olympia Vitalis</v>
+        <v>4Fargo</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L184" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Passionfruit</v>
+        <v>Safety</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-16</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Passionfruit - Single</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:57</v>
+        <v>3:18</v>
       </c>
       <c r="H185" t="str">
-        <v>Anish Kumar</v>
+        <v>Lekan</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L185" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Madan</v>
+        <v>Starlet</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-16</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Madan - Single</v>
+        <v>LK99</v>
       </c>
       <c r="G186" t="str">
         <v>2:56</v>
       </c>
       <c r="H186" t="str">
-        <v>Jonas Blue</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L186" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Bad Bitch</v>
+        <v>Physical</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-16</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:28</v>
+        <v>3:52</v>
       </c>
       <c r="H187" t="str">
-        <v>41</v>
+        <v>Jacquees</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L187" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Shame</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-16</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:36</v>
+        <v>4:29</v>
       </c>
       <c r="H188" t="str">
-        <v>Sunday (1994)</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L188" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>teach you to love me</v>
+        <v>Regalito</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-16</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>teach you to love me - Single</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G189" t="str">
-        <v>3:09</v>
+        <v>2:41</v>
       </c>
       <c r="H189" t="str">
-        <v>Hailey Picardi</v>
+        <v>Piso 21</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L189" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>The Fix</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-16</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>The Fix - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G190" t="str">
-        <v>2:42</v>
+        <v>4:09</v>
       </c>
       <c r="H190" t="str">
-        <v>Baby J</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L190" t="str">
-        <v>The Fix - Baby J</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Hanging on Hope</v>
+        <v>Die Young</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-16</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G191" t="str">
-        <v>3:43</v>
+        <v>3:52</v>
       </c>
       <c r="H191" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L191" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>I Know What to Say Now</v>
+        <v>Island Girl</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-16</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:18</v>
+        <v>3:27</v>
       </c>
       <c r="H192" t="str">
-        <v>Active Child</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L192" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Feel Something</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-16</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Feel Something - Single</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:09</v>
+        <v>2:20</v>
       </c>
       <c r="H193" t="str">
-        <v>Baby Queen</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L193" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>You Or Me</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-16</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>5:28</v>
+        <v>3:22</v>
       </c>
       <c r="H194" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Shaggy</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L194" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Mortercheyn</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-16</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Coronach</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>4:18</v>
+        <v>3:44</v>
       </c>
       <c r="H195" t="str">
-        <v>Hellripper</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L195" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Rip The God</v>
+        <v>Rainbows</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-16</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>5:20</v>
+        <v>3:25</v>
       </c>
       <c r="H196" t="str">
-        <v>Melvins</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L196" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Who We Are</v>
+        <v>butterflies</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-16</v>
@@ -7861,68 +7861,676 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Who We Are - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G197" t="str">
-        <v>2:10</v>
+        <v>2:48</v>
       </c>
       <c r="H197" t="str">
-        <v>Kaleena Zanders</v>
+        <v>runo plum</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L197" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
+        <v>You're Right</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>You're Right - Single</v>
+      </c>
+      <c r="G198" t="str">
+        <v>3:00</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Emma Harner</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+      </c>
+      <c r="L198" t="str">
+        <v>You're Right - Emma Harner</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Bible Belt</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Bible Belt - Single</v>
+      </c>
+      <c r="G199" t="str">
+        <v>3:34</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Baby Bugs</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Bible Belt - Baby Bugs</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>Daze</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>Daze - Single</v>
+      </c>
+      <c r="G200" t="str">
+        <v>3:22</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Olympia Vitalis</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
+      </c>
+      <c r="L200" t="str">
+        <v>Daze - Olympia Vitalis</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Passionfruit</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Passionfruit - Single</v>
+      </c>
+      <c r="G201" t="str">
+        <v>3:57</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Anish Kumar</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Passionfruit - Anish Kumar</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>Madan</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Madan - Single</v>
+      </c>
+      <c r="G202" t="str">
+        <v>2:56</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Jonas Blue</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Madan - Jonas Blue</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Bad Bitch</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>Bad Bitch - Single</v>
+      </c>
+      <c r="G203" t="str">
+        <v>2:28</v>
+      </c>
+      <c r="H203" t="str">
+        <v>41</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Bad Bitch - 41</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Shame</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>Devotion [Deluxe]</v>
+      </c>
+      <c r="G204" t="str">
+        <v>3:36</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Sunday (1994)</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Shame - Sunday (1994)</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>teach you to love me</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>teach you to love me - Single</v>
+      </c>
+      <c r="G205" t="str">
+        <v>3:09</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Hailey Picardi</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+      </c>
+      <c r="L205" t="str">
+        <v>teach you to love me - Hailey Picardi</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>The Fix</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>The Fix - Single</v>
+      </c>
+      <c r="G206" t="str">
+        <v>2:42</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Baby J</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+      </c>
+      <c r="L206" t="str">
+        <v>The Fix - Baby J</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Hanging on Hope</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>Hanging on Hope - Single</v>
+      </c>
+      <c r="G207" t="str">
+        <v>3:43</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Buffalo Traffic Jam</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+      </c>
+      <c r="L207" t="str">
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>I Know What to Say Now</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>I Know What to Say Now - Single</v>
+      </c>
+      <c r="G208" t="str">
+        <v>3:18</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Active Child</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+      </c>
+      <c r="L208" t="str">
+        <v>I Know What to Say Now - Active Child</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>Feel Something</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v>Feel Something - Single</v>
+      </c>
+      <c r="G209" t="str">
+        <v>3:09</v>
+      </c>
+      <c r="H209" t="str">
+        <v>Baby Queen</v>
+      </c>
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+      </c>
+      <c r="K209" t="str">
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+      </c>
+      <c r="L209" t="str">
+        <v>Feel Something - Baby Queen</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>You Or Me</v>
+      </c>
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v>Good God / Baad Man</v>
+      </c>
+      <c r="G210" t="str">
+        <v>5:28</v>
+      </c>
+      <c r="H210" t="str">
+        <v>Corrosion of Conformity</v>
+      </c>
+      <c r="I210" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J210" t="str">
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+      </c>
+      <c r="K210" t="str">
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+      </c>
+      <c r="L210" t="str">
+        <v>You Or Me - Corrosion of Conformity</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Mortercheyn</v>
+      </c>
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" t="str">
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v>Coronach</v>
+      </c>
+      <c r="G211" t="str">
+        <v>4:18</v>
+      </c>
+      <c r="H211" t="str">
+        <v>Hellripper</v>
+      </c>
+      <c r="I211" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J211" t="str">
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+      </c>
+      <c r="K211" t="str">
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+      </c>
+      <c r="L211" t="str">
+        <v>Mortercheyn - Hellripper</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Rip The God</v>
+      </c>
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" t="str">
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+      </c>
+      <c r="D212" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v>Savage Imperial Death March</v>
+      </c>
+      <c r="G212" t="str">
+        <v>5:20</v>
+      </c>
+      <c r="H212" t="str">
+        <v>Melvins</v>
+      </c>
+      <c r="I212" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J212" t="str">
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
+      </c>
+      <c r="K212" t="str">
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+      </c>
+      <c r="L212" t="str">
+        <v>Rip The God - Melvins</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Who We Are</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" t="str">
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+      </c>
+      <c r="D213" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v>Who We Are - Single</v>
+      </c>
+      <c r="G213" t="str">
+        <v>2:10</v>
+      </c>
+      <c r="H213" t="str">
+        <v>Kaleena Zanders</v>
+      </c>
+      <c r="I213" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+      </c>
+      <c r="K213" t="str">
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+      </c>
+      <c r="L213" t="str">
+        <v>Who We Are - Kaleena Zanders</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
         <v>Reels in 360</v>
       </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
+      <c r="B214" t="str">
+        <v/>
+      </c>
+      <c r="C214" t="str">
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
-      <c r="D198" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
+      <c r="D214" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
         <v>Dying Is The Internet</v>
       </c>
-      <c r="G198" t="str">
+      <c r="G214" t="str">
         <v>4:37</v>
       </c>
-      <c r="H198" t="str">
+      <c r="H214" t="str">
         <v>Simo Cell</v>
       </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
+      <c r="I214" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J214" t="str">
         <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
-      <c r="K198" t="str">
+      <c r="K214" t="str">
         <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
-      <c r="L198" t="str">
+      <c r="L214" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L214"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week03/titles.xlsx
+++ b/data/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L214"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלום ממן - יא רייח</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-16</v>
+        <v>5 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410031&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-16</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>4:09</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Mei Semones</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלום ממן - יא רייח</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שלו משען - אגם של טעויות</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-16</v>
+        <v>5 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410030&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-16</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>2:08</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שלו משען - אגם של טעויות</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שיר מזרחי &amp; משה זאודה - יש לנו כאב</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-16</v>
+        <v>5 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410029&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-16</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>2:57</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Natalie Jane</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שיר מזרחי &amp; משה זאודה - יש לנו כאב</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>קיליאן ג'אמי - צלקת</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-16</v>
+        <v>6 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410028&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-16</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>3:13</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>קיליאן ג'אמי - צלקת</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>צחי אלוש - טיקי טקה</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-16</v>
+        <v>6 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410027&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-16</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>4:12</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>David Gilmour</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>צחי אלוש - טיקי טקה</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>עידן משה - ריגוש וכאב</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-16</v>
+        <v>6 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410026&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-16</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>3:57</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Far Caspian</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>עידן משה - ריגוש וכאב</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>עידו כנפי - פרפרים בבטן</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-16</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410025&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-16</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>3:34</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Celine Dion</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>עידו כנפי - פרפרים בבטן</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>סגיב כהן - חסד יסובבנו</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-16</v>
+        <v>10 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410024&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-16</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>3:48</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Harry Styles</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>סגיב כהן - חסד יסובבנו</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>נתנאל מלכה - בלעדייך</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-16</v>
+        <v>9 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410023&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-16</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>4:58</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>נתנאל מלכה - בלעדייך</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>מיכה ינון - מחרוזת חזון אחרית הימים 2026</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-16</v>
+        <v>9 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410022&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-16</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>2:33</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Ellise</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>מיכה ינון - מחרוזת חזון אחרית הימים 2026</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>יהורם גאון - עד עולם</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-03-16</v>
+        <v>10 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410021&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-16</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>5:01</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>יהורם גאון - עד עולם</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-03-16</v>
+        <v>10 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410020&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-16</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>4:56</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>גבריאל שרם - שוברת גלים</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-03-16</v>
+        <v>10 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410019&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-16</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>2:54</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>גבריאל שרם - שוברת גלים</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>אורי ספז - תפילה שלך</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-03-16</v>
+        <v>10 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410018&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-16</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>2:46</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>NathanEvanss</v>
       </c>
       <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>אורי ספז - תפילה שלך</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>אבי שפרונג - הבית שלי</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-03-16</v>
+        <v>10 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410017&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-16</v>
@@ -983,16 +983,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>2:56</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>R3HAB</v>
       </c>
       <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>אבי שפרונג - הבית שלי</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-16</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:09</v>
+        <v>3:21</v>
       </c>
       <c r="H17" t="str">
-        <v>Mei Semones</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-16</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:08</v>
+        <v>3:16</v>
       </c>
       <c r="H18" t="str">
-        <v>The Lemon Twigs</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-16</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:57</v>
+        <v>2:41</v>
       </c>
       <c r="H19" t="str">
-        <v>Natalie Jane</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-16</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:13</v>
+        <v>2:29</v>
       </c>
       <c r="H20" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-16</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:12</v>
+        <v>2:43</v>
       </c>
       <c r="H21" t="str">
-        <v>David Gilmour</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-16</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:57</v>
+        <v>3:46</v>
       </c>
       <c r="H22" t="str">
-        <v>Far Caspian</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-16</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:34</v>
+        <v>4:01</v>
       </c>
       <c r="H23" t="str">
-        <v>Celine Dion</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B24" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-16</v>
@@ -1290,10 +1290,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:48</v>
+        <v>3:23</v>
       </c>
       <c r="H24" t="str">
-        <v>Harry Styles</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B25" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-16</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:58</v>
+        <v>3:39</v>
       </c>
       <c r="H25" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>almost monday</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-16</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:33</v>
+        <v>3:04</v>
       </c>
       <c r="H26" t="str">
-        <v>Ellise</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-16</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>5:01</v>
+        <v>3:25</v>
       </c>
       <c r="H27" t="str">
-        <v>The Doobie Brothers</v>
+        <v>vaultboy</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-16</v>
@@ -1442,10 +1442,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:56</v>
+        <v>3:49</v>
       </c>
       <c r="H28" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>The Warning</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B29" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-16</v>
@@ -1480,10 +1480,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:54</v>
+        <v>2:14</v>
       </c>
       <c r="H29" t="str">
-        <v>Bebe Rexha</v>
+        <v>aron!</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-16</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:46</v>
+        <v>2:43</v>
       </c>
       <c r="H30" t="str">
-        <v>NathanEvanss</v>
+        <v>Bazzi</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B31" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-16</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:56</v>
+        <v>4:43</v>
       </c>
       <c r="H31" t="str">
-        <v>R3HAB</v>
+        <v>Sting</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-16</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:21</v>
+        <v>2:44</v>
       </c>
       <c r="H32" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-16</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:16</v>
+        <v>4:37</v>
       </c>
       <c r="H33" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B34" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-16</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:41</v>
+        <v>4:52</v>
       </c>
       <c r="H34" t="str">
-        <v>Johnny Orlando</v>
+        <v>Cannons</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B35" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-16</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:29</v>
+        <v>2:13</v>
       </c>
       <c r="H35" t="str">
-        <v>Russell Dickerson</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-16</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:43</v>
+        <v>3:19</v>
       </c>
       <c r="H36" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B37" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-16</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:46</v>
+        <v>2:31</v>
       </c>
       <c r="H37" t="str">
-        <v>Matt Hansen</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-16</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:01</v>
+        <v>2:43</v>
       </c>
       <c r="H38" t="str">
-        <v>Mike Posner</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-16</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:23</v>
+        <v>3:10</v>
       </c>
       <c r="H39" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B40" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-16</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:39</v>
+        <v>3:55</v>
       </c>
       <c r="H40" t="str">
-        <v>almost monday</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-16</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:04</v>
+        <v>3:52</v>
       </c>
       <c r="H41" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B42" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-16</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:25</v>
+        <v>2:53</v>
       </c>
       <c r="H42" t="str">
-        <v>vaultboy</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-16</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:49</v>
+        <v>4:30</v>
       </c>
       <c r="H43" t="str">
-        <v>The Warning</v>
+        <v>Jessie J</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-16</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:14</v>
+        <v>5:18</v>
       </c>
       <c r="H44" t="str">
-        <v>aron!</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-16</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:43</v>
+        <v>7:20</v>
       </c>
       <c r="H45" t="str">
-        <v>Bazzi</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B46" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-16</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:43</v>
+        <v>3:01</v>
       </c>
       <c r="H46" t="str">
-        <v>Sting</v>
+        <v>BRITs</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-16</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:44</v>
+        <v>3:31</v>
       </c>
       <c r="H47" t="str">
-        <v>Dean Lewis</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B48" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-16</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:37</v>
+        <v>3:00</v>
       </c>
       <c r="H48" t="str">
-        <v>Jessie Ware</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B49" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-16</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:52</v>
+        <v>3:11</v>
       </c>
       <c r="H49" t="str">
-        <v>Cannons</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-16</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:13</v>
+        <v>3:32</v>
       </c>
       <c r="H50" t="str">
-        <v>Kim Petras</v>
+        <v>Lauv</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-16</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:19</v>
+        <v>5:03</v>
       </c>
       <c r="H51" t="str">
-        <v>Vanessa Carlton</v>
+        <v>RAYE</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-16</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:31</v>
+        <v>4:50</v>
       </c>
       <c r="H52" t="str">
-        <v>Kiana Ledé</v>
+        <v>Armik</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-16</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:43</v>
+        <v>4:53</v>
       </c>
       <c r="H53" t="str">
-        <v>Ringo Starr</v>
+        <v>Scorpions</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-16</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:10</v>
+        <v>3:04</v>
       </c>
       <c r="H54" t="str">
-        <v>Maya Hawke</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-16</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:55</v>
+        <v>4:32</v>
       </c>
       <c r="H55" t="str">
-        <v>Armin van Buuren</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-16</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:52</v>
+        <v>3:47</v>
       </c>
       <c r="H56" t="str">
-        <v>Demi Lovato</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-16</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:53</v>
+        <v>3:40</v>
       </c>
       <c r="H57" t="str">
-        <v>Peter Gabriel</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-16</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:30</v>
+        <v>4:05</v>
       </c>
       <c r="H58" t="str">
-        <v>Jessie J</v>
+        <v>HAUSER</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-16</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>5:18</v>
+        <v>2:59</v>
       </c>
       <c r="H59" t="str">
-        <v>Harry Styles</v>
+        <v>Queen Official</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-16</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>7:20</v>
+        <v>3:55</v>
       </c>
       <c r="H60" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-16</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:01</v>
+        <v>5:12</v>
       </c>
       <c r="H61" t="str">
-        <v>BRITs</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-16</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:31</v>
+        <v>3:47</v>
       </c>
       <c r="H62" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-16</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:00</v>
+        <v>3:18</v>
       </c>
       <c r="H63" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-16</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:11</v>
+        <v>3:50</v>
       </c>
       <c r="H64" t="str">
-        <v>The Kiffness</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-16</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:32</v>
+        <v>3:24</v>
       </c>
       <c r="H65" t="str">
-        <v>Lauv</v>
+        <v>MyKey</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-16</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>5:03</v>
+        <v>2:36</v>
       </c>
       <c r="H66" t="str">
-        <v>RAYE</v>
+        <v>Max McNown</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-16</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:50</v>
+        <v>3:34</v>
       </c>
       <c r="H67" t="str">
-        <v>Armik</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-16</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:53</v>
+        <v>4:03</v>
       </c>
       <c r="H68" t="str">
-        <v>Scorpions</v>
+        <v>ERNEST</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-16</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:04</v>
+        <v>3:31</v>
       </c>
       <c r="H69" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-16</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:32</v>
+        <v>3:22</v>
       </c>
       <c r="H70" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-16</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:47</v>
+        <v>5:49</v>
       </c>
       <c r="H71" t="str">
-        <v>Girl Tones</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-16</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:40</v>
+        <v>3:47</v>
       </c>
       <c r="H72" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-16</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>4:05</v>
+        <v>2:20</v>
       </c>
       <c r="H73" t="str">
-        <v>HAUSER</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-16</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:59</v>
+        <v>4:18</v>
       </c>
       <c r="H74" t="str">
-        <v>Queen Official</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-16</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:55</v>
+        <v>2:39</v>
       </c>
       <c r="H75" t="str">
-        <v>Tenille Townes</v>
+        <v>kenzie</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-16</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>5:12</v>
+        <v>3:52</v>
       </c>
       <c r="H76" t="str">
-        <v>Self Esteem</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-16</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:47</v>
+        <v>4:01</v>
       </c>
       <c r="H77" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-16</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:18</v>
+        <v>2:54</v>
       </c>
       <c r="H78" t="str">
-        <v>Em Beihold</v>
+        <v>CHESCA</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-16</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:50</v>
+        <v>4:03</v>
       </c>
       <c r="H79" t="str">
-        <v>Michael Bublé</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-16</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:24</v>
+        <v>4:50</v>
       </c>
       <c r="H80" t="str">
-        <v>MyKey</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-16</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:36</v>
+        <v>3:06</v>
       </c>
       <c r="H81" t="str">
-        <v>Max McNown</v>
+        <v>Y2K</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-16</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:34</v>
+        <v>2:43</v>
       </c>
       <c r="H82" t="str">
-        <v>Megan Moroney</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-16</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:03</v>
+        <v>6:21</v>
       </c>
       <c r="H83" t="str">
-        <v>ERNEST</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-16</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:31</v>
+        <v>2:46</v>
       </c>
       <c r="H84" t="str">
-        <v>Bruno Mars</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-16</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:22</v>
+        <v>2:42</v>
       </c>
       <c r="H85" t="str">
-        <v>BLACKPINK</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-16</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>5:49</v>
+        <v>3:04</v>
       </c>
       <c r="H86" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-16</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:47</v>
+        <v>2:59</v>
       </c>
       <c r="H87" t="str">
-        <v>Nessa Barrett</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-16</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:20</v>
+        <v>2:22</v>
       </c>
       <c r="H88" t="str">
-        <v>Towa Bird</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-16</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:18</v>
+        <v>3:53</v>
       </c>
       <c r="H89" t="str">
-        <v>Ty Myers</v>
+        <v>Roxette</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-16</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:39</v>
+        <v>2:28</v>
       </c>
       <c r="H90" t="str">
-        <v>kenzie</v>
+        <v>Marcin</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-16</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:52</v>
+        <v>2:47</v>
       </c>
       <c r="H91" t="str">
-        <v>Leanna Crawford</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-16</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:01</v>
+        <v>3:40</v>
       </c>
       <c r="H92" t="str">
-        <v>Bryan Adams</v>
+        <v>Laufey</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-16</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:54</v>
+        <v>2:49</v>
       </c>
       <c r="H93" t="str">
-        <v>CHESCA</v>
+        <v>Ava Max</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-16</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>4:03</v>
+        <v>4:49</v>
       </c>
       <c r="H94" t="str">
-        <v>Dermot Kennedy</v>
+        <v>U2</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-16</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:50</v>
+        <v>3:35</v>
       </c>
       <c r="H95" t="str">
-        <v>earMUSIC</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-16</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:06</v>
+        <v>2:59</v>
       </c>
       <c r="H96" t="str">
-        <v>Y2K</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-16</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:43</v>
+        <v>4:38</v>
       </c>
       <c r="H97" t="str">
-        <v>Lainey Wilson</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-16</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>6:21</v>
+        <v>3:46</v>
       </c>
       <c r="H98" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-16</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:46</v>
+        <v>3:08</v>
       </c>
       <c r="H99" t="str">
-        <v>Bryan Ferry</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-16</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:42</v>
+        <v>5:32</v>
       </c>
       <c r="H100" t="str">
-        <v>Saint Harison</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-16</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:04</v>
+        <v>4:39</v>
       </c>
       <c r="H101" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>georgemichael</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Riptides</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-16</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G102" t="str">
-        <v>2:59</v>
+        <v>3:17</v>
       </c>
       <c r="H102" t="str">
-        <v>Catie Turner</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L102" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
+        <v>Porch Light</v>
       </c>
       <c r="B103" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-16</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2 weeks ago</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G103" t="str">
-        <v>2:22</v>
+        <v>4:22</v>
       </c>
       <c r="H103" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
       </c>
       <c r="L103" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
+        <v>Porch Light - Noah Kahan</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Dry Spell</v>
       </c>
       <c r="B104" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-16</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2 weeks ago</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G104" t="str">
-        <v>3:53</v>
+        <v>3:17</v>
       </c>
       <c r="H104" t="str">
-        <v>Roxette</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
       </c>
       <c r="L104" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Dry Spell - Kacey Musgraves</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>The Visitor</v>
       </c>
       <c r="B105" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-16</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>2 weeks ago</v>
+        <v>The Visitor - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:28</v>
+        <v>3:48</v>
       </c>
       <c r="H105" t="str">
-        <v>Marcin</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
       </c>
       <c r="L105" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>I Ain't No Cowboy</v>
       </c>
       <c r="B106" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-16</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>2 weeks ago</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G106" t="str">
-        <v>2:47</v>
+        <v>3:13</v>
       </c>
       <c r="H106" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
       </c>
       <c r="L106" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>I Ain't No Cowboy - Luke Combs</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Can't Sit Still</v>
       </c>
       <c r="B107" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-16</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>2 weeks ago</v>
+        <v>Can't Sit Still - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:40</v>
+        <v>3:35</v>
       </c>
       <c r="H107" t="str">
-        <v>Laufey</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
       </c>
       <c r="L107" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Can't Sit Still - Lainey Wilson</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>All I Did Was Dream of You (feat. The Marías)</v>
       </c>
       <c r="B108" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-16</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>2 weeks ago</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:49</v>
+        <v>3:43</v>
       </c>
       <c r="H108" t="str">
-        <v>Ava Max</v>
+        <v>beabadoobee</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
       </c>
       <c r="L108" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Blow My Mind</v>
       </c>
       <c r="B109" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-16</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>2 weeks ago</v>
+        <v>Sexistential</v>
       </c>
       <c r="G109" t="str">
-        <v>4:49</v>
+        <v>2:57</v>
       </c>
       <c r="H109" t="str">
-        <v>U2</v>
+        <v>Robyn</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
       </c>
       <c r="L109" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Blow My Mind - Robyn</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>SATA</v>
       </c>
       <c r="B110" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-16</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>3 weeks ago</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G110" t="str">
-        <v>3:35</v>
+        <v>3:02</v>
       </c>
       <c r="H110" t="str">
-        <v>Taylor Swift</v>
+        <v>John Summit</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/sata/1874015470</v>
       </c>
       <c r="L110" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>SATA - John Summit</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Una Aventura</v>
       </c>
       <c r="B111" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-16</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>2 weeks ago</v>
+        <v>Una Aventura - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>2:59</v>
+        <v>3:00</v>
       </c>
       <c r="H111" t="str">
-        <v>Kiana Ledé</v>
+        <v>Ozuna</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
       </c>
       <c r="L111" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Una Aventura - Ozuna</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Home (feat. Hikaru Utada)</v>
       </c>
       <c r="B112" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-16</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>3 weeks ago</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G112" t="str">
-        <v>4:38</v>
+        <v>3:44</v>
       </c>
       <c r="H112" t="str">
-        <v>Jessie Ware</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
       </c>
       <c r="L112" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>dirty wedding dress</v>
       </c>
       <c r="B113" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-16</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>3 weeks ago</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G113" t="str">
-        <v>3:46</v>
+        <v>4:49</v>
       </c>
       <c r="H113" t="str">
-        <v>Madison Beer</v>
+        <v>Bleachers</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
       </c>
       <c r="L113" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>dirty wedding dress - Bleachers</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B114" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-16</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>3 weeks ago</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G114" t="str">
-        <v>3:08</v>
+        <v>3:07</v>
       </c>
       <c r="H114" t="str">
-        <v>Sean Stemaly</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L114" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B115" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-16</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>3 weeks ago</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>5:32</v>
+        <v>3:13</v>
       </c>
       <c r="H115" t="str">
-        <v>earMUSIC</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L115" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Trade Places</v>
       </c>
       <c r="B116" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-16</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>3 weeks ago</v>
+        <v>Monica</v>
       </c>
       <c r="G116" t="str">
-        <v>4:39</v>
+        <v>3:02</v>
       </c>
       <c r="H116" t="str">
-        <v>georgemichael</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L116" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Riptides</v>
+        <v>Motion Party</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-16</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>I Built You a Tower</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:17</v>
+        <v>1:35</v>
       </c>
       <c r="H117" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L117" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Porch Light</v>
+        <v>Woman</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-16</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>The Great Divide</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>4:22</v>
+        <v>2:46</v>
       </c>
       <c r="H118" t="str">
-        <v>Noah Kahan</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L118" t="str">
-        <v>Porch Light - Noah Kahan</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Dry Spell</v>
+        <v>Sunburn</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-16</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Middle of Nowhere</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:17</v>
+        <v>3:05</v>
       </c>
       <c r="H119" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L119" t="str">
-        <v>Dry Spell - Kacey Musgraves</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>The Visitor</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-16</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>The Visitor - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G120" t="str">
-        <v>3:48</v>
+        <v>2:54</v>
       </c>
       <c r="H120" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L120" t="str">
-        <v>The Visitor - SIENNA SPIRO</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>I Ain't No Cowboy</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-16</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>The Way I Am</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:13</v>
+        <v>2:15</v>
       </c>
       <c r="H121" t="str">
-        <v>Luke Combs</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L121" t="str">
-        <v>I Ain't No Cowboy - Luke Combs</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Can't Sit Still</v>
+        <v>Cruel World</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-16</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Can't Sit Still - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G122" t="str">
-        <v>3:35</v>
+        <v>3:26</v>
       </c>
       <c r="H122" t="str">
-        <v>Lainey Wilson</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L122" t="str">
-        <v>Can't Sit Still - Lainey Wilson</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías)</v>
+        <v>Star</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-16</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
+        <v>Star - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:43</v>
+        <v>3:25</v>
       </c>
       <c r="H123" t="str">
-        <v>beabadoobee</v>
+        <v>Iceage</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L123" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Blow My Mind</v>
+        <v>Get Go</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-16</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Sexistential</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G124" t="str">
-        <v>2:57</v>
+        <v>3:22</v>
       </c>
       <c r="H124" t="str">
-        <v>Robyn</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L124" t="str">
-        <v>Blow My Mind - Robyn</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>SATA</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/sata/1874015489</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-16</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>Distracted</v>
       </c>
       <c r="G125" t="str">
-        <v>3:02</v>
+        <v>3:14</v>
       </c>
       <c r="H125" t="str">
-        <v>John Summit</v>
+        <v>Thundercat</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/sata/1874015470</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L125" t="str">
-        <v>SATA - John Summit</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Una Aventura</v>
+        <v>Club Song</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-16</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Una Aventura - Single</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:00</v>
+        <v>2:27</v>
       </c>
       <c r="H126" t="str">
-        <v>Ozuna</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L126" t="str">
-        <v>Una Aventura - Ozuna</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>Better Man</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-16</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:44</v>
+        <v>2:53</v>
       </c>
       <c r="H127" t="str">
-        <v>Charlie Puth</v>
+        <v>jxdn</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L127" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>dirty wedding dress</v>
+        <v>sabotage</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-16</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>everyone for ten minutes</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>4:49</v>
+        <v>2:58</v>
       </c>
       <c r="H128" t="str">
-        <v>Bleachers</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L128" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-16</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Age of the Ram</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:07</v>
+        <v>2:56</v>
       </c>
       <c r="H129" t="str">
-        <v>Charley Crockett</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L129" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Naked</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-16</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:13</v>
+        <v>3:39</v>
       </c>
       <c r="H130" t="str">
-        <v>Grupo Frontera</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L130" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Trade Places</v>
+        <v>Catharina</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-16</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Monica</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:02</v>
+        <v>3:27</v>
       </c>
       <c r="H131" t="str">
-        <v>Jack Harlow</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L131" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Motion Party</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-16</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Motion Party - Single</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>1:35</v>
+        <v>3:00</v>
       </c>
       <c r="H132" t="str">
-        <v>Bossman Dlow</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L132" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Woman</v>
+        <v>Trying Times</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-16</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Woman - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G133" t="str">
-        <v>2:46</v>
+        <v>4:33</v>
       </c>
       <c r="H133" t="str">
-        <v>Kane Brown</v>
+        <v>James Blake</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L133" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Sunburn</v>
+        <v>595</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-16</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Sunburn - Single</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G134" t="str">
-        <v>3:05</v>
+        <v>2:29</v>
       </c>
       <c r="H134" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L134" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Que Te Costó</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-16</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Metamorfosis</v>
+        <v>Soft 2</v>
       </c>
       <c r="G135" t="str">
-        <v>2:54</v>
+        <v>3:50</v>
       </c>
       <c r="H135" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>LANY</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L135" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>oooshxt!</v>
+        <v>CALL ME</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-16</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>oooshxt! - Single</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:15</v>
+        <v>2:10</v>
       </c>
       <c r="H136" t="str">
-        <v>Samara Cyn</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L136" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Cruel World</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-16</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Cruel World</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G137" t="str">
-        <v>3:26</v>
+        <v>2:00</v>
       </c>
       <c r="H137" t="str">
-        <v>Holly Humberstone</v>
+        <v>Nasty C</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L137" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Star</v>
+        <v>BOBA</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-16</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Star - Single</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:25</v>
+        <v>3:00</v>
       </c>
       <c r="H138" t="str">
-        <v>Iceage</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L138" t="str">
-        <v>Star - Iceage</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Get Go</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-16</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Skeletor</v>
       </c>
       <c r="G139" t="str">
-        <v>3:22</v>
+        <v>2:38</v>
       </c>
       <c r="H139" t="str">
-        <v>Arlo Parks</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L139" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>ThunderWave</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-16</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Distracted</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:14</v>
+        <v>2:06</v>
       </c>
       <c r="H140" t="str">
-        <v>Thundercat</v>
+        <v>Shenseea</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L140" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Club Song</v>
+        <v>Just Believe</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-16</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Club Song - Single</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:27</v>
+        <v>2:41</v>
       </c>
       <c r="H141" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L141" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Better Man</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-16</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Better Man - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G142" t="str">
-        <v>2:53</v>
+        <v>2:57</v>
       </c>
       <c r="H142" t="str">
-        <v>jxdn</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L142" t="str">
-        <v>Better Man - jxdn</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>sabotage</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-16</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>sabotage - Single</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:58</v>
+        <v>3:09</v>
       </c>
       <c r="H143" t="str">
-        <v>Natalie Jane</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L143" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-16</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G144" t="str">
-        <v>2:56</v>
+        <v>4:06</v>
       </c>
       <c r="H144" t="str">
-        <v>WHATMORE</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L144" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Naked</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-16</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Naked - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G145" t="str">
-        <v>3:39</v>
+        <v>3:33</v>
       </c>
       <c r="H145" t="str">
-        <v>Kenya Grace</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L145" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Catharina</v>
+        <v>Breathe</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-16</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Catharina - Single</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:27</v>
+        <v>2:56</v>
       </c>
       <c r="H146" t="str">
-        <v>Martin Garrix</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L146" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>Minty</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-16</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G147" t="str">
-        <v>3:00</v>
+        <v>1:47</v>
       </c>
       <c r="H147" t="str">
-        <v>Chase &amp; Status</v>
+        <v>MIKE</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L147" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Trying Times</v>
+        <v>Earth</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-16</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Trying Times</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G148" t="str">
-        <v>4:33</v>
+        <v>1:37</v>
       </c>
       <c r="H148" t="str">
-        <v>James Blake</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L148" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>595</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-16</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Be Sweet To Me</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G149" t="str">
-        <v>2:29</v>
+        <v>3:42</v>
       </c>
       <c r="H149" t="str">
-        <v>Violet Grohl</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L149" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-16</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Soft 2</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:50</v>
+        <v>4:32</v>
       </c>
       <c r="H150" t="str">
-        <v>LANY</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L150" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>CALL ME</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-16</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>CALL ME - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:10</v>
+        <v>3:32</v>
       </c>
       <c r="H151" t="str">
-        <v>ALTÉGO</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L151" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Mi Amor</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-16</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Free (Deluxe)</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:00</v>
+        <v>3:08</v>
       </c>
       <c r="H152" t="str">
-        <v>Nasty C</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L152" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>BOBA</v>
+        <v>Real Slow</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-16</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>BOBA - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G153" t="str">
-        <v>3:00</v>
+        <v>3:22</v>
       </c>
       <c r="H153" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L153" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Video Shoot</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-16</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Skeletor</v>
+        <v>As Is</v>
       </c>
       <c r="G154" t="str">
-        <v>2:38</v>
+        <v>2:42</v>
       </c>
       <c r="H154" t="str">
-        <v>Chief Keef</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L154" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-16</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>American Stories</v>
       </c>
       <c r="G155" t="str">
-        <v>2:06</v>
+        <v>3:31</v>
       </c>
       <c r="H155" t="str">
-        <v>Shenseea</v>
+        <v>Rostam</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L155" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Just Believe</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-16</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Just Believe - Single</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G156" t="str">
-        <v>2:41</v>
+        <v>3:29</v>
       </c>
       <c r="H156" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L156" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Knife In The Heart</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-16</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>The Afterparty</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G157" t="str">
-        <v>2:57</v>
+        <v>3:04</v>
       </c>
       <c r="H157" t="str">
-        <v>Lykke Li</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L157" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>The Way We Touch</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-16</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:09</v>
+        <v>3:37</v>
       </c>
       <c r="H158" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L158" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>DANGEROUS</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-16</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>4:06</v>
+        <v>3:03</v>
       </c>
       <c r="H159" t="str">
-        <v>Magnolia Park</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L159" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>When I Wake Up</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-16</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Dear God</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G160" t="str">
-        <v>3:33</v>
+        <v>4:05</v>
       </c>
       <c r="H160" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L160" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Breathe</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-16</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Breathe - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G161" t="str">
-        <v>2:56</v>
+        <v>3:34</v>
       </c>
       <c r="H161" t="str">
-        <v>Malcolm Todd</v>
+        <v>Melanie C</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L161" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Minty</v>
+        <v>Pull Up</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-16</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>1:47</v>
+        <v>2:35</v>
       </c>
       <c r="H162" t="str">
-        <v>MIKE</v>
+        <v>Collect 200</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L162" t="str">
-        <v>Minty - MIKE</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Earth</v>
+        <v>Ranjha</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-16</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>1:37</v>
+        <v>3:04</v>
       </c>
       <c r="H163" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L163" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Drink The Water</v>
+        <v>zombies in love</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-16</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:42</v>
+        <v>2:53</v>
       </c>
       <c r="H164" t="str">
-        <v>Jack Johnson</v>
+        <v>paris jackson</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L164" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-16</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G165" t="str">
-        <v>4:32</v>
+        <v>4:39</v>
       </c>
       <c r="H165" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L165" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-16</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:32</v>
+        <v>3:15</v>
       </c>
       <c r="H166" t="str">
-        <v>Carly Pearce</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L166" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Muchacho Alegre</v>
+        <v>Ya No</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-16</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:08</v>
+        <v>3:40</v>
       </c>
       <c r="H167" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Marca MP</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L167" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Real Slow</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-16</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Work of Heart</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:22</v>
+        <v>3:48</v>
       </c>
       <c r="H168" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L168" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Mountain Girl</v>
+        <v>Relieve You</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-16</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>As Is</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:42</v>
+        <v>2:19</v>
       </c>
       <c r="H169" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>4Fargo</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L169" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Like a Spark</v>
+        <v>Safety</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-16</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>American Stories</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:31</v>
+        <v>3:18</v>
       </c>
       <c r="H170" t="str">
-        <v>Rostam</v>
+        <v>Lekan</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L170" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Cheesecake</v>
+        <v>Starlet</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-16</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>LK99</v>
       </c>
       <c r="G171" t="str">
-        <v>3:29</v>
+        <v>2:56</v>
       </c>
       <c r="H171" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L171" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Physical</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-16</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>KINDA HARD</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:04</v>
+        <v>3:52</v>
       </c>
       <c r="H172" t="str">
-        <v>Bilmuri</v>
+        <v>Jacquees</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L172" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Freakin’ Out</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-16</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:37</v>
+        <v>4:29</v>
       </c>
       <c r="H173" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L173" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Name in Vein</v>
+        <v>Regalito</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-16</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Name in Vein - Single</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G174" t="str">
-        <v>3:03</v>
+        <v>2:41</v>
       </c>
       <c r="H174" t="str">
-        <v>VOILÀ</v>
+        <v>Piso 21</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L174" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-16</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Into Oblivion</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G175" t="str">
-        <v>4:05</v>
+        <v>4:09</v>
       </c>
       <c r="H175" t="str">
-        <v>Lamb of God</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L175" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Undefeated Champion</v>
+        <v>Die Young</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-16</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Sweat</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G176" t="str">
-        <v>3:34</v>
+        <v>3:52</v>
       </c>
       <c r="H176" t="str">
-        <v>Melanie C</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L176" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Pull Up</v>
+        <v>Island Girl</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-16</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Pull Up - Single</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:35</v>
+        <v>3:27</v>
       </c>
       <c r="H177" t="str">
-        <v>Collect 200</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L177" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Ranjha</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-16</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Ranjha - Single</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:04</v>
+        <v>2:20</v>
       </c>
       <c r="H178" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L178" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>zombies in love</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-16</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>zombies in love - Single</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:53</v>
+        <v>3:22</v>
       </c>
       <c r="H179" t="str">
-        <v>paris jackson</v>
+        <v>Shaggy</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L179" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Days Of Us</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-16</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Full Circle</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>4:39</v>
+        <v>3:44</v>
       </c>
       <c r="H180" t="str">
-        <v>Tom Misch</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L180" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Life Of A Man</v>
+        <v>Rainbows</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-16</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:15</v>
+        <v>3:25</v>
       </c>
       <c r="H181" t="str">
-        <v>1Ski OG</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L181" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Ya No</v>
+        <v>butterflies</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-16</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Ya No - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G182" t="str">
-        <v>3:40</v>
+        <v>2:48</v>
       </c>
       <c r="H182" t="str">
-        <v>Marca MP</v>
+        <v>runo plum</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L182" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Do You Really Love Her</v>
+        <v>You're Right</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-16</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>You're Right - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:48</v>
+        <v>3:00</v>
       </c>
       <c r="H183" t="str">
-        <v>Spacey Jane</v>
+        <v>Emma Harner</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
       </c>
       <c r="L183" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>You're Right - Emma Harner</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Relieve You</v>
+        <v>Bible Belt</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-16</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Relieve You - Single</v>
+        <v>Bible Belt - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:19</v>
+        <v>3:34</v>
       </c>
       <c r="H184" t="str">
-        <v>4Fargo</v>
+        <v>Baby Bugs</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
       </c>
       <c r="L184" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Bible Belt - Baby Bugs</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Safety</v>
+        <v>Daze</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-16</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Safety - Single</v>
+        <v>Daze - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:18</v>
+        <v>3:22</v>
       </c>
       <c r="H185" t="str">
-        <v>Lekan</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
       </c>
       <c r="L185" t="str">
-        <v>Safety - Lekan</v>
+        <v>Daze - Olympia Vitalis</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Starlet</v>
+        <v>Passionfruit</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-16</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>LK99</v>
+        <v>Passionfruit - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:56</v>
+        <v>3:57</v>
       </c>
       <c r="H186" t="str">
-        <v>Leven Kali</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
       </c>
       <c r="L186" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Passionfruit - Anish Kumar</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Physical</v>
+        <v>Madan</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-16</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Physical - Single</v>
+        <v>Madan - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:52</v>
+        <v>2:56</v>
       </c>
       <c r="H187" t="str">
-        <v>Jacquees</v>
+        <v>Jonas Blue</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
       </c>
       <c r="L187" t="str">
-        <v>Physical - Jacquees</v>
+        <v>Madan - Jonas Blue</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Bad Bitch</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-16</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>Bad Bitch - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>4:29</v>
+        <v>2:28</v>
       </c>
       <c r="H188" t="str">
-        <v>Casper Sage</v>
+        <v>41</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
       </c>
       <c r="L188" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Bad Bitch - 41</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Regalito</v>
+        <v>Shame</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-16</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>TRESCENDER</v>
+        <v>Devotion [Deluxe]</v>
       </c>
       <c r="G189" t="str">
-        <v>2:41</v>
+        <v>3:36</v>
       </c>
       <c r="H189" t="str">
-        <v>Piso 21</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
       </c>
       <c r="L189" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>Shame - Sunday (1994)</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Cruel Streak</v>
+        <v>teach you to love me</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-16</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>A Pound of Feathers</v>
+        <v>teach you to love me - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:09</v>
+        <v>3:09</v>
       </c>
       <c r="H190" t="str">
-        <v>The Black Crowes</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
       </c>
       <c r="L190" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>teach you to love me - Hailey Picardi</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Die Young</v>
+        <v>The Fix</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-16</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Little Wide Open</v>
+        <v>The Fix - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:52</v>
+        <v>2:42</v>
       </c>
       <c r="H191" t="str">
-        <v>Kevin Morby</v>
+        <v>Baby J</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
       </c>
       <c r="L191" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>The Fix - Baby J</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Island Girl</v>
+        <v>Hanging on Hope</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-16</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Island Girl - Single</v>
+        <v>Hanging on Hope - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:27</v>
+        <v>3:43</v>
       </c>
       <c r="H192" t="str">
-        <v>Pia Mia</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
       </c>
       <c r="L192" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>GIRLY THINGS</v>
+        <v>I Know What to Say Now</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-16</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>I Know What to Say Now - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:20</v>
+        <v>3:18</v>
       </c>
       <c r="H193" t="str">
-        <v>Claudia Valentina</v>
+        <v>Active Child</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
       </c>
       <c r="L193" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>I Know What to Say Now - Active Child</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>Feel Something</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-16</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>Feel Something - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:22</v>
+        <v>3:09</v>
       </c>
       <c r="H194" t="str">
-        <v>Shaggy</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
       </c>
       <c r="L194" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>Feel Something - Baby Queen</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Tommy’s Song</v>
+        <v>You Or Me</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-16</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Lovers - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G195" t="str">
-        <v>3:44</v>
+        <v>5:28</v>
       </c>
       <c r="H195" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
       </c>
       <c r="L195" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>You Or Me - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Rainbows</v>
+        <v>Mortercheyn</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-16</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Rainbows - Single</v>
+        <v>Coronach</v>
       </c>
       <c r="G196" t="str">
-        <v>3:25</v>
+        <v>4:18</v>
       </c>
       <c r="H196" t="str">
-        <v>Allison Russell</v>
+        <v>Hellripper</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
       </c>
       <c r="L196" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Mortercheyn - Hellripper</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>butterflies</v>
+        <v>Rip The God</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-16</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G197" t="str">
-        <v>2:48</v>
+        <v>5:20</v>
       </c>
       <c r="H197" t="str">
-        <v>runo plum</v>
+        <v>Melvins</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
       </c>
       <c r="L197" t="str">
-        <v>butterflies - runo plum</v>
+        <v>Rip The God - Melvins</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>You're Right</v>
+        <v>Who We Are</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-16</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>You're Right - Single</v>
+        <v>Who We Are - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:00</v>
+        <v>2:10</v>
       </c>
       <c r="H198" t="str">
-        <v>Emma Harner</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
       </c>
       <c r="L198" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>Who We Are - Kaleena Zanders</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Bible Belt</v>
+        <v>Reels in 360</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-16</v>
@@ -7937,600 +7937,30 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Bible Belt - Single</v>
+        <v>Dying Is The Internet</v>
       </c>
       <c r="G199" t="str">
-        <v>3:34</v>
+        <v>4:37</v>
       </c>
       <c r="H199" t="str">
-        <v>Baby Bugs</v>
+        <v>Simo Cell</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
       <c r="L199" t="str">
-        <v>Bible Belt - Baby Bugs</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Daze</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Daze - Single</v>
-      </c>
-      <c r="G200" t="str">
-        <v>3:22</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Olympia Vitalis</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
-      </c>
-      <c r="L200" t="str">
-        <v>Daze - Olympia Vitalis</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Passionfruit</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Passionfruit - Single</v>
-      </c>
-      <c r="G201" t="str">
-        <v>3:57</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Anish Kumar</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
-      </c>
-      <c r="L201" t="str">
-        <v>Passionfruit - Anish Kumar</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Madan</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Madan - Single</v>
-      </c>
-      <c r="G202" t="str">
-        <v>2:56</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Jonas Blue</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
-      </c>
-      <c r="L202" t="str">
-        <v>Madan - Jonas Blue</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Bad Bitch</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Bad Bitch - Single</v>
-      </c>
-      <c r="G203" t="str">
-        <v>2:28</v>
-      </c>
-      <c r="H203" t="str">
-        <v>41</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
-      </c>
-      <c r="L203" t="str">
-        <v>Bad Bitch - 41</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Shame</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Devotion [Deluxe]</v>
-      </c>
-      <c r="G204" t="str">
-        <v>3:36</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Sunday (1994)</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
-      </c>
-      <c r="L204" t="str">
-        <v>Shame - Sunday (1994)</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>teach you to love me</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>teach you to love me - Single</v>
-      </c>
-      <c r="G205" t="str">
-        <v>3:09</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Hailey Picardi</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
-      </c>
-      <c r="L205" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>The Fix</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>The Fix - Single</v>
-      </c>
-      <c r="G206" t="str">
-        <v>2:42</v>
-      </c>
-      <c r="H206" t="str">
-        <v>Baby J</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
-      </c>
-      <c r="L206" t="str">
-        <v>The Fix - Baby J</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Hanging on Hope</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Hanging on Hope - Single</v>
-      </c>
-      <c r="G207" t="str">
-        <v>3:43</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Buffalo Traffic Jam</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
-      </c>
-      <c r="L207" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>I Know What to Say Now</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>I Know What to Say Now - Single</v>
-      </c>
-      <c r="G208" t="str">
-        <v>3:18</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Active Child</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
-      </c>
-      <c r="L208" t="str">
-        <v>I Know What to Say Now - Active Child</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>Feel Something</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>Feel Something - Single</v>
-      </c>
-      <c r="G209" t="str">
-        <v>3:09</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Baby Queen</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
-      </c>
-      <c r="L209" t="str">
-        <v>Feel Something - Baby Queen</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>You Or Me</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>Good God / Baad Man</v>
-      </c>
-      <c r="G210" t="str">
-        <v>5:28</v>
-      </c>
-      <c r="H210" t="str">
-        <v>Corrosion of Conformity</v>
-      </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
-      </c>
-      <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
-      </c>
-      <c r="L210" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>Mortercheyn</v>
-      </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
-      </c>
-      <c r="D211" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" t="str">
-        <v>Coronach</v>
-      </c>
-      <c r="G211" t="str">
-        <v>4:18</v>
-      </c>
-      <c r="H211" t="str">
-        <v>Hellripper</v>
-      </c>
-      <c r="I211" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
-      </c>
-      <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
-      </c>
-      <c r="L211" t="str">
-        <v>Mortercheyn - Hellripper</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>Rip The God</v>
-      </c>
-      <c r="B212" t="str">
-        <v/>
-      </c>
-      <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
-      </c>
-      <c r="D212" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E212" t="str">
-        <v/>
-      </c>
-      <c r="F212" t="str">
-        <v>Savage Imperial Death March</v>
-      </c>
-      <c r="G212" t="str">
-        <v>5:20</v>
-      </c>
-      <c r="H212" t="str">
-        <v>Melvins</v>
-      </c>
-      <c r="I212" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
-      </c>
-      <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
-      </c>
-      <c r="L212" t="str">
-        <v>Rip The God - Melvins</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>Who We Are</v>
-      </c>
-      <c r="B213" t="str">
-        <v/>
-      </c>
-      <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
-      </c>
-      <c r="D213" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E213" t="str">
-        <v/>
-      </c>
-      <c r="F213" t="str">
-        <v>Who We Are - Single</v>
-      </c>
-      <c r="G213" t="str">
-        <v>2:10</v>
-      </c>
-      <c r="H213" t="str">
-        <v>Kaleena Zanders</v>
-      </c>
-      <c r="I213" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
-      </c>
-      <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
-      </c>
-      <c r="L213" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>Reels in 360</v>
-      </c>
-      <c r="B214" t="str">
-        <v/>
-      </c>
-      <c r="C214" t="str">
-        <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
-      </c>
-      <c r="D214" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E214" t="str">
-        <v/>
-      </c>
-      <c r="F214" t="str">
-        <v>Dying Is The Internet</v>
-      </c>
-      <c r="G214" t="str">
-        <v>4:37</v>
-      </c>
-      <c r="H214" t="str">
-        <v>Simo Cell</v>
-      </c>
-      <c r="I214" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J214" t="str">
-        <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
-      </c>
-      <c r="K214" t="str">
-        <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
-      </c>
-      <c r="L214" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L214"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week03/titles.xlsx
+++ b/data/global/2026-03-week03/titles.xlsx
@@ -781,7 +781,7 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:33</v>

--- a/data/global/2026-03-week03/titles.xlsx
+++ b/data/global/2026-03-week03/titles.xlsx
@@ -743,7 +743,7 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>4:58</v>

--- a/data/global/2026-03-week03/titles.xlsx
+++ b/data/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,31 +436,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>יהורם גאון – עד עולם</v>
       </c>
       <c r="B2" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://yosmusic.com/%d7%99%d7%94%d7%95%d7%a8%d7%9d-%d7%92%d7%90%d7%95%d7%9f-%d7%a2%d7%93-%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 days ago</v>
+        <v>השיר ששר יהורם גאון יושב על התפר שבין נוסטלגיה ישראלית קלאסית לבין עדכון עכשווי – וזה מורגש גם ברמת המילים וגם ברמת ההקשר. על פניו זה שיר אהבה בין גבר לאישה – “שלך הנני”, “את לעד תהיי לי”. אבל יש</v>
       </c>
       <c r="G2" t="str">
-        <v>4:09</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Mei Semones</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>יהורם גאון – עד עולם</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B3" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -492,10 +492,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:08</v>
+        <v>4:09</v>
       </c>
       <c r="H3" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B4" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -530,10 +530,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:57</v>
+        <v>2:08</v>
       </c>
       <c r="H4" t="str">
-        <v>Natalie Jane</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -568,10 +568,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:13</v>
+        <v>2:57</v>
       </c>
       <c r="H5" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B6" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -606,10 +606,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:12</v>
+        <v>3:13</v>
       </c>
       <c r="H6" t="str">
-        <v>David Gilmour</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B7" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/wat